--- a/github_activity_report.xlsx
+++ b/github_activity_report.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Failure Alerts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Activity'!$A$1:$Y$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Activity'!$A$1:$Y$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Failure Summary'!$A$1:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failure Alerts'!$A$3:$L$18</definedName>
   </definedNames>
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -540,8 +540,8 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="54" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>4246e5f5bdd0c663224514d45c37457253e6806b</t>
+          <t>aac0b4a033d6b371042ec3f99a213aa53e5d925f</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>test-13</t>
+          <t>test-198</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>2026-04-10T09:35:54Z</t>
+          <t>2026-04-10T09:40:50Z</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>24236579665</v>
+        <v>24236872105</v>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
@@ -2473,85 +2473,67 @@
       <c r="Y20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>ff12234265b7ed9747283a1b59735ea5ddda19b5</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>test-12</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10T09:21:24Z</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>19b0e6e1eadc37093a80d5aa3b43d47cf52cc739</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>chore: update activity report [2026-04-10 09:36 UTC] via push (run 24236579665)</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>github-actions[bot]</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-10T09:36:36Z</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="n">
-        <v>24236015736</v>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr"/>
-      <c r="V21" s="2" t="inlineStr"/>
-      <c r="W21" s="2" t="inlineStr"/>
-      <c r="X21" s="2" t="inlineStr"/>
-      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr"/>
+      <c r="P21" s="7" t="inlineStr"/>
+      <c r="Q21" s="7" t="inlineStr"/>
+      <c r="R21" s="7" t="inlineStr"/>
+      <c r="S21" s="7" t="inlineStr"/>
+      <c r="T21" s="7" t="inlineStr"/>
+      <c r="U21" s="7" t="inlineStr"/>
+      <c r="V21" s="7" t="inlineStr"/>
+      <c r="W21" s="7" t="inlineStr"/>
+      <c r="X21" s="7" t="inlineStr"/>
+      <c r="Y21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2576,12 +2558,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75732834dd766afc090c808510eb71c7693015dd</t>
+          <t>4246e5f5bdd0c663224514d45c37457253e6806b</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>test-8</t>
+          <t>test-13</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2591,7 +2573,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T08:35:13Z</t>
+          <t>2026-04-10T09:35:54Z</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2611,7 +2593,7 @@
         </is>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>24234243976</v>
+        <v>24236579665</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -2657,12 +2639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9d220c5657c48c13ca17102c507b756edbba9215</t>
+          <t>ff12234265b7ed9747283a1b59735ea5ddda19b5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>test-8</t>
+          <t>test-12</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2672,7 +2654,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T08:32:22Z</t>
+          <t>2026-04-10T09:21:24Z</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2692,7 +2674,7 @@
         </is>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>24234135440</v>
+        <v>24236015736</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
@@ -2738,7 +2720,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>981fe60621c98393750f79dd815a0ea7e4aed75e</t>
+          <t>75732834dd766afc090c808510eb71c7693015dd</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2753,7 +2735,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T08:27:06Z</t>
+          <t>2026-04-10T08:35:13Z</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2773,7 +2755,7 @@
         </is>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>24233936358</v>
+        <v>24234243976</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -2819,12 +2801,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3cfdf96375ed8ea8c83b95f26b9c87428b8bc8b9</t>
+          <t>9d220c5657c48c13ca17102c507b756edbba9215</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>test-1</t>
+          <t>test-8</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2834,7 +2816,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T08:18:15Z</t>
+          <t>2026-04-10T08:32:22Z</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2854,7 +2836,7 @@
         </is>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>24233616319</v>
+        <v>24234135440</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -2900,12 +2882,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ad211e0513d37204ee54168120dec41978cc6fb4</t>
+          <t>981fe60621c98393750f79dd815a0ea7e4aed75e</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>new code change</t>
+          <t>test-8</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2915,7 +2897,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-04-06T15:32:05Z</t>
+          <t>2026-04-10T08:27:06Z</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2935,7 +2917,7 @@
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>24038137070</v>
+        <v>24233936358</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -2958,8 +2940,170 @@
       <c r="X26" s="2" t="inlineStr"/>
       <c r="Y26" s="2" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>3cfdf96375ed8ea8c83b95f26b9c87428b8bc8b9</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>test-1</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10T08:18:15Z</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>GitHub Activity Report</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>24233616319</v>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr"/>
+      <c r="Y27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>ad211e0513d37204ee54168120dec41978cc6fb4</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>new code change</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06T15:32:05Z</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>GitHub Activity Report</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>24038137070</v>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr"/>
+      <c r="Y28" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y26"/>
+  <autoFilter ref="A1:Y28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4035,7 +4179,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-10 09:36 UTC</t>
+          <t>Generated: 2026-04-10 09:44 UTC</t>
         </is>
       </c>
     </row>

--- a/github_activity_report.xlsx
+++ b/github_activity_report.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Failure Alerts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Activity'!$A$1:$Y$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Activity'!$A$1:$Y$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Failure Summary'!$A$1:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failure Alerts'!$A$3:$L$18</definedName>
   </definedNames>
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,8 +38,16 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="00276221"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00276221"/>
+    </font>
+    <font>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -73,17 +81,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EEF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,34 +144,34 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -532,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y28"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -712,12 +720,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>21f8e2bcc8765be2c9dd97d0d839686b7afe3de1</t>
+          <t>408ddd043c24815f4498a813c6ca81c4e9688b9b</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>new code change</t>
+          <t>test-198</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -727,12 +735,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-06T12:24:00Z</t>
+          <t>2026-04-10T14:38:25Z</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>git-report-poc2</t>
+          <t>main</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -747,7 +755,7 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>24031673216</v>
+        <v>24248391662</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
@@ -756,14 +764,10 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr"/>
       <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="inlineStr"/>
@@ -771,105 +775,67 @@
       <c r="Y2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>code changed1</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-06T11:54:44Z</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>git-report-poc2</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr"/>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>24030846379</v>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>workflow_dispatch</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>generate_report</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>Run GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>Line 56</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>37f60b0c23d45eef199630a384945ef73970b8d7</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>chore: update activity report [2026-04-10 09:44 UTC] via push (run 24236872105)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>github-actions[bot]</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10T09:44:03Z</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -894,12 +860,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
+          <t>aac0b4a033d6b371042ec3f99a213aa53e5d925f</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>code changed1</t>
+          <t>test-198</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -909,12 +875,12 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>2026-04-06T11:54:44Z</t>
+          <t>2026-04-10T09:40:50Z</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>git-report-poc2</t>
+          <t>main</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr"/>
@@ -925,11 +891,11 @@
       <c r="O4" s="4" t="inlineStr"/>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>GitHub Workflow Report</t>
+          <t>GitHub Activity Report</t>
         </is>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>24030820444</v>
+        <v>24236872105</v>
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
@@ -943,135 +909,77 @@
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>generate_report</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t>Run GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>Line 55</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="inlineStr"/>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr"/>
+      <c r="Y4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>733b89967b9b4731953302840f2ddb2c20bedf56</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>code changed</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-06T10:52:40Z</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>git-report-poc2</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>24029078530</v>
-      </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>generate_report</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>Set up job</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>Line 52</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>19b0e6e1eadc37093a80d5aa3b43d47cf52cc739</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>chore: update activity report [2026-04-10 09:36 UTC] via push (run 24236579665)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>github-actions[bot]</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10T09:36:36Z</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1096,12 +1004,12 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>aedf77ebc8e0433ebbe37ca97908ee5caf3929d6</t>
+          <t>4246e5f5bdd0c663224514d45c37457253e6806b</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>code changd</t>
+          <t>test-13</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -1111,12 +1019,12 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-06T10:44:38Z</t>
+          <t>2026-04-10T09:35:54Z</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>git-report-poc2</t>
+          <t>main</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr"/>
@@ -1127,11 +1035,11 @@
       <c r="O6" s="4" t="inlineStr"/>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>GitHub Workflow Report</t>
+          <t>GitHub Activity Report</t>
         </is>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>24028853853</v>
+        <v>24236579665</v>
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
@@ -1145,34 +1053,14 @@
       </c>
       <c r="T6" s="5" t="inlineStr">
         <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr">
-        <is>
-          <t>Run GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>Line 45</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>Auth/permission error — check that GH_PAT has the required scopes and that repository secrets are correctly configured.</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1197,27 +1085,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>5feb9eb868fd9ff9e4a7150d13cb3252d843c106</t>
+          <t>ff12234265b7ed9747283a1b59735ea5ddda19b5</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Update demo.txt</t>
+          <t>test-12</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>vidyakar-whitedev</t>
+          <t>“Vidyakar”</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-04-06T10:31:56Z</t>
+          <t>2026-04-10T09:21:24Z</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>git-report-poc2</t>
+          <t>main</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr"/>
@@ -1228,11 +1116,11 @@
       <c r="O7" s="4" t="inlineStr"/>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>GitHub Workflow Report</t>
+          <t>GitHub Activity Report</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>24028486557</v>
+        <v>24236015736</v>
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
@@ -1246,34 +1134,14 @@
       </c>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U7" s="4" t="inlineStr">
-        <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="inlineStr">
-        <is>
-          <t>Run GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="X7" s="4" t="inlineStr">
-        <is>
-          <t>Line 39</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr"/>
+      <c r="Y7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1298,12 +1166,12 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2fcbd831207ea4821a39ee88d33aa21454ca19e3</t>
+          <t>75732834dd766afc090c808510eb71c7693015dd</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>code changed@v1</t>
+          <t>test-8</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -1313,12 +1181,12 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>2026-04-06T10:28:57Z</t>
+          <t>2026-04-10T08:35:13Z</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>git-report-poc2</t>
+          <t>main</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr"/>
@@ -1329,11 +1197,11 @@
       <c r="O8" s="4" t="inlineStr"/>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>GitHub Workflow Report</t>
+          <t>GitHub Activity Report</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>24028398959</v>
+        <v>24234243976</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -1347,34 +1215,14 @@
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr">
-        <is>
-          <t>Run GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>Line 29</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="inlineStr">
-        <is>
-          <t>Auth/permission error — check that GH_PAT has the required scopes and that repository secrets are correctly configured.</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr"/>
+      <c r="Y8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1399,12 +1247,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>37ddfe095b13b5e65a98ff2072c4bbb77cde7c1b</t>
+          <t>9d220c5657c48c13ca17102c507b756edbba9215</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>code changed</t>
+          <t>test-8</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1414,12 +1262,12 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-04-06T10:22:31Z</t>
+          <t>2026-04-10T08:32:22Z</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>git-report-poc2</t>
+          <t>main</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr"/>
@@ -1430,11 +1278,11 @@
       <c r="O9" s="4" t="inlineStr"/>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>GitHub Workflow Report</t>
+          <t>GitHub Activity Report</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>24028208740</v>
+        <v>24234135440</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -1448,34 +1296,14 @@
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr">
-        <is>
-          <t>Install dependencies</t>
-        </is>
-      </c>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>Line 22</t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="4" t="inlineStr"/>
+      <c r="Y9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1500,12 +1328,12 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>74dcfb5e2119b07af9671cc4c8396585d44a6fb8</t>
+          <t>981fe60621c98393750f79dd815a0ea7e4aed75e</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>test-8</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1515,12 +1343,12 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>2026-04-06T10:21:05Z</t>
+          <t>2026-04-10T08:27:06Z</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>git-report-poc2</t>
+          <t>main</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr"/>
@@ -1531,11 +1359,11 @@
       <c r="O10" s="4" t="inlineStr"/>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>GitHub Workflow Report</t>
+          <t>GitHub Activity Report</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>24028171694</v>
+        <v>24233936358</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -1549,34 +1377,14 @@
       </c>
       <c r="T10" s="5" t="inlineStr">
         <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr">
-        <is>
-          <t>Install dependencies</t>
-        </is>
-      </c>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>Line 21</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr"/>
+      <c r="V10" s="4" t="inlineStr"/>
+      <c r="W10" s="4" t="inlineStr"/>
+      <c r="X10" s="4" t="inlineStr"/>
+      <c r="Y10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1601,27 +1409,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>5ff73a4b92ec974d47dc4998318d0eb25003ef50</t>
+          <t>3cfdf96375ed8ea8c83b95f26b9c87428b8bc8b9</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Enhance workflow with caching and Node.js versioning</t>
+          <t>test-1</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>vidyakar-whitedev</t>
+          <t>“Vidyakar”</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026-04-06T10:08:38Z</t>
+          <t>2026-04-10T08:18:15Z</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>git-report-poc2</t>
+          <t>main</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr"/>
@@ -1632,11 +1440,11 @@
       <c r="O11" s="4" t="inlineStr"/>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>GitHub Workflow Report</t>
+          <t>GitHub Activity Report</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>24027807973</v>
+        <v>24233616319</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1650,34 +1458,14 @@
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr">
-        <is>
-          <t>Install dependencies</t>
-        </is>
-      </c>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>Line 08</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="inlineStr"/>
+      <c r="W11" s="4" t="inlineStr"/>
+      <c r="X11" s="4" t="inlineStr"/>
+      <c r="Y11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1702,27 +1490,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>ad002901ed69655717989c4485c2df1f343c5b15</t>
+          <t>ad211e0513d37204ee54168120dec41978cc6fb4</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Fix typo in demo.txt</t>
+          <t>new code change</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>vidyakar-whitedev</t>
+          <t>“Vidyakar”</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>2026-04-06T10:06:00Z</t>
+          <t>2026-04-06T15:32:05Z</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>git-report-poc2</t>
+          <t>main</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr"/>
@@ -1733,11 +1521,11 @@
       <c r="O12" s="4" t="inlineStr"/>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>GitHub Workflow Report</t>
+          <t>GitHub Activity Report</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>24027735534</v>
+        <v>24038137070</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1751,34 +1539,14 @@
       </c>
       <c r="T12" s="5" t="inlineStr">
         <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr">
-        <is>
-          <t>Run GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>Line 06</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="inlineStr"/>
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="4" t="inlineStr"/>
+      <c r="Y12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1803,22 +1571,22 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>06a295fe67b6991a6ba3430be5f485beedd7805f</t>
+          <t>21f8e2bcc8765be2c9dd97d0d839686b7afe3de1</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Update workflow_report.yml</t>
+          <t>new code change</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>vidyakar-whitedev</t>
+          <t>“Vidyakar”</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>2026-04-06T10:05:48Z</t>
+          <t>2026-04-06T12:24:00Z</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1834,438 +1602,434 @@
       <c r="O13" s="4" t="inlineStr"/>
       <c r="P13" s="4" t="inlineStr">
         <is>
+          <t>GitHub Activity Report</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>24031673216</v>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr"/>
+      <c r="V13" s="4" t="inlineStr"/>
+      <c r="W13" s="4" t="inlineStr"/>
+      <c r="X13" s="4" t="inlineStr"/>
+      <c r="Y13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>code changed1</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06T11:54:44Z</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr"/>
+      <c r="N14" s="6" t="inlineStr"/>
+      <c r="O14" s="6" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="n">
-        <v>24027729636</v>
-      </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v>24030846379</v>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>workflow_dispatch</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr">
+        <is>
+          <t>generate_report</t>
+        </is>
+      </c>
+      <c r="W14" s="6" t="inlineStr">
+        <is>
+          <t>Run GitHub Activity Report</t>
+        </is>
+      </c>
+      <c r="X14" s="6" t="inlineStr">
+        <is>
+          <t>Line 56</t>
+        </is>
+      </c>
+      <c r="Y14" s="6" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>code changed1</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06T11:54:44Z</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr"/>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>24030820444</v>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="S15" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T13" s="5" t="inlineStr">
+      <c r="T15" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>generate_report</t>
+        </is>
+      </c>
+      <c r="W15" s="6" t="inlineStr">
+        <is>
+          <t>Run GitHub Activity Report</t>
+        </is>
+      </c>
+      <c r="X15" s="6" t="inlineStr">
+        <is>
+          <t>Line 55</t>
+        </is>
+      </c>
+      <c r="Y15" s="6" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>733b89967b9b4731953302840f2ddb2c20bedf56</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>code changed</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:52:40Z</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr"/>
+      <c r="O16" s="6" t="inlineStr"/>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v>24029078530</v>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U16" s="6" t="inlineStr">
+        <is>
+          <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr">
+        <is>
+          <t>generate_report</t>
+        </is>
+      </c>
+      <c r="W16" s="6" t="inlineStr">
+        <is>
+          <t>Set up job</t>
+        </is>
+      </c>
+      <c r="X16" s="6" t="inlineStr">
+        <is>
+          <t>Line 52</t>
+        </is>
+      </c>
+      <c r="Y16" s="6" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>aedf77ebc8e0433ebbe37ca97908ee5caf3929d6</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>code changd</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:44:38Z</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>24028853853</v>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U17" s="6" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="W13" s="4" t="inlineStr">
+      <c r="W17" s="6" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>Line 06</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>372cfe624d49eb38f5e8baab2c748007dc54b018</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Update demo.txt</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-06T10:04:34Z</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>git-report-poc2</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr"/>
-      <c r="P14" s="4" t="inlineStr">
-        <is>
-          <t>GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="n">
-        <v>24027694141</v>
-      </c>
-      <c r="R14" s="4" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S14" s="4" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr">
-        <is>
-          <t>Set up job</t>
-        </is>
-      </c>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>Line 04</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>e7bf9d94f807df2e25e29ad5d30bc78e1b2fbd25</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Update workflow_report.yml</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-06T10:04:22Z</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>git-report-poc2</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
-      <c r="O15" s="4" t="inlineStr"/>
-      <c r="P15" s="4" t="inlineStr">
-        <is>
-          <t>GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="n">
-        <v>24027689526</v>
-      </c>
-      <c r="R15" s="4" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S15" s="4" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="T15" s="5" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr">
-        <is>
-          <t>Set up job</t>
-        </is>
-      </c>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>Line 04</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>3046e3250b6d3bc90634487150d715e566686a47</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Add demo.txt for testing purposes</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-06T10:02:10Z</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>git-report-poc2</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr"/>
-      <c r="O16" s="4" t="inlineStr"/>
-      <c r="P16" s="4" t="inlineStr">
-        <is>
-          <t>.github/workflows/workflow_report.yml</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="n">
-        <v>24027621196</v>
-      </c>
-      <c r="R16" s="4" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S16" s="4" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="T16" s="5" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>Failure (see logs)</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>See GitHub Actions logs</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>32de2be70035a86124e1345187c9ba078e4cf3bf</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Add GitHub Workflow Report YAML configuration</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-06T10:01:02Z</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>git-report-poc2</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="4" t="inlineStr"/>
-      <c r="P17" s="4" t="inlineStr">
-        <is>
-          <t>.github/workflows/workflow_report.yml</t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>24027587697</v>
-      </c>
-      <c r="R17" s="4" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S17" s="4" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="T17" s="5" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>Failure (see logs)</t>
-        </is>
-      </c>
-      <c r="V17" s="4" t="inlineStr"/>
-      <c r="W17" s="4" t="inlineStr"/>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t>See GitHub Actions logs</t>
-        </is>
-      </c>
-      <c r="Y17" s="4" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+      <c r="X17" s="6" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="Y17" s="6" t="inlineStr">
+        <is>
+          <t>Auth/permission error — check that GH_PAT has the required scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
@@ -2292,12 +2056,12 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>8eaab42012c4f02192c65cf59561b5c261b2cf90</t>
+          <t>5feb9eb868fd9ff9e4a7150d13cb3252d843c106</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Create github_workflow_report.py</t>
+          <t>Update demo.txt</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -2307,7 +2071,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>2026-04-06T09:50:41Z</t>
+          <t>2026-04-06T10:31:56Z</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -2321,79 +2085,155 @@
       <c r="M18" s="6" t="inlineStr"/>
       <c r="N18" s="6" t="inlineStr"/>
       <c r="O18" s="6" t="inlineStr"/>
-      <c r="P18" s="6" t="inlineStr"/>
-      <c r="Q18" s="6" t="inlineStr"/>
-      <c r="R18" s="6" t="inlineStr"/>
-      <c r="S18" s="6" t="inlineStr"/>
-      <c r="T18" s="6" t="inlineStr"/>
-      <c r="U18" s="6" t="inlineStr"/>
-      <c r="V18" s="6" t="inlineStr"/>
-      <c r="W18" s="6" t="inlineStr"/>
-      <c r="X18" s="6" t="inlineStr"/>
-      <c r="Y18" s="6" t="inlineStr"/>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>24028486557</v>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U18" s="6" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="W18" s="6" t="inlineStr">
+        <is>
+          <t>Run GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="X18" s="6" t="inlineStr">
+        <is>
+          <t>Line 39</t>
+        </is>
+      </c>
+      <c r="Y18" s="6" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>a9e73f5e7cd8ea7da7f4969f80034915cc9f302c</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Initial commit</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>2026-04-06T09:48:37Z</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>2fcbd831207ea4821a39ee88d33aa21454ca19e3</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>code changed@v1</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:28:57Z</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr"/>
-      <c r="K19" s="7" t="inlineStr"/>
-      <c r="L19" s="7" t="inlineStr"/>
-      <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
-      <c r="O19" s="7" t="inlineStr"/>
-      <c r="P19" s="7" t="inlineStr"/>
-      <c r="Q19" s="7" t="inlineStr"/>
-      <c r="R19" s="7" t="inlineStr"/>
-      <c r="S19" s="7" t="inlineStr"/>
-      <c r="T19" s="7" t="inlineStr"/>
-      <c r="U19" s="7" t="inlineStr"/>
-      <c r="V19" s="7" t="inlineStr"/>
-      <c r="W19" s="7" t="inlineStr"/>
-      <c r="X19" s="7" t="inlineStr"/>
-      <c r="Y19" s="7" t="inlineStr"/>
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr"/>
+      <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr"/>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v>24028398959</v>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T19" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="W19" s="6" t="inlineStr">
+        <is>
+          <t>Run GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="X19" s="6" t="inlineStr">
+        <is>
+          <t>Line 29</t>
+        </is>
+      </c>
+      <c r="Y19" s="6" t="inlineStr">
+        <is>
+          <t>Auth/permission error — check that GH_PAT has the required scopes and that repository secrets are correctly configured.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2418,12 +2258,12 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>aac0b4a033d6b371042ec3f99a213aa53e5d925f</t>
+          <t>37ddfe095b13b5e65a98ff2072c4bbb77cde7c1b</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>test-198</t>
+          <t>code changed</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -2433,12 +2273,12 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>2026-04-10T09:40:50Z</t>
+          <t>2026-04-06T10:22:31Z</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>git-report-poc2</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr"/>
@@ -2449,11 +2289,11 @@
       <c r="O20" s="6" t="inlineStr"/>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>GitHub Activity Report</t>
+          <t>GitHub Workflow Report</t>
         </is>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>24236872105</v>
+        <v>24028208740</v>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
@@ -2462,648 +2302,960 @@
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="T20" s="6" t="inlineStr"/>
-      <c r="U20" s="6" t="inlineStr"/>
-      <c r="V20" s="6" t="inlineStr"/>
-      <c r="W20" s="6" t="inlineStr"/>
-      <c r="X20" s="6" t="inlineStr"/>
-      <c r="Y20" s="6" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T20" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+        </is>
+      </c>
+      <c r="V20" s="6" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="W20" s="6" t="inlineStr">
+        <is>
+          <t>Install dependencies</t>
+        </is>
+      </c>
+      <c r="X20" s="6" t="inlineStr">
+        <is>
+          <t>Line 22</t>
+        </is>
+      </c>
+      <c r="Y20" s="6" t="inlineStr">
+        <is>
+          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>19b0e6e1eadc37093a80d5aa3b43d47cf52cc739</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>chore: update activity report [2026-04-10 09:36 UTC] via push (run 24236579665)</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>github-actions[bot]</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>2026-04-10T09:36:36Z</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>74dcfb5e2119b07af9671cc4c8396585d44a6fb8</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:21:05Z</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr"/>
+      <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr"/>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>24028171694</v>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U21" s="6" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+        </is>
+      </c>
+      <c r="V21" s="6" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="W21" s="6" t="inlineStr">
+        <is>
+          <t>Install dependencies</t>
+        </is>
+      </c>
+      <c r="X21" s="6" t="inlineStr">
+        <is>
+          <t>Line 21</t>
+        </is>
+      </c>
+      <c r="Y21" s="6" t="inlineStr">
+        <is>
+          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr"/>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr"/>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
-      <c r="O21" s="7" t="inlineStr"/>
-      <c r="P21" s="7" t="inlineStr"/>
-      <c r="Q21" s="7" t="inlineStr"/>
-      <c r="R21" s="7" t="inlineStr"/>
-      <c r="S21" s="7" t="inlineStr"/>
-      <c r="T21" s="7" t="inlineStr"/>
-      <c r="U21" s="7" t="inlineStr"/>
-      <c r="V21" s="7" t="inlineStr"/>
-      <c r="W21" s="7" t="inlineStr"/>
-      <c r="X21" s="7" t="inlineStr"/>
-      <c r="Y21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>5ff73a4b92ec974d47dc4998318d0eb25003ef50</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Enhance workflow with caching and Node.js versioning</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:08:38Z</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr"/>
+      <c r="N22" s="6" t="inlineStr"/>
+      <c r="O22" s="6" t="inlineStr"/>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v>24027807973</v>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U22" s="6" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+        </is>
+      </c>
+      <c r="V22" s="6" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="W22" s="6" t="inlineStr">
+        <is>
+          <t>Install dependencies</t>
+        </is>
+      </c>
+      <c r="X22" s="6" t="inlineStr">
+        <is>
+          <t>Line 08</t>
+        </is>
+      </c>
+      <c r="Y22" s="6" t="inlineStr">
+        <is>
+          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>4246e5f5bdd0c663224514d45c37457253e6806b</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>test-13</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10T09:35:54Z</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>ad002901ed69655717989c4485c2df1f343c5b15</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Fix typo in demo.txt</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:06:00Z</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr"/>
+      <c r="N23" s="6" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr"/>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v>24027735534</v>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U23" s="6" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
+        </is>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="W23" s="6" t="inlineStr">
+        <is>
+          <t>Run GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="X23" s="6" t="inlineStr">
+        <is>
+          <t>Line 06</t>
+        </is>
+      </c>
+      <c r="Y23" s="6" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="n">
-        <v>24236579665</v>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>06a295fe67b6991a6ba3430be5f485beedd7805f</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Update workflow_report.yml</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:05:48Z</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr"/>
+      <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr"/>
+      <c r="N24" s="6" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr"/>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>24027729636</v>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="S24" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr"/>
-      <c r="V22" s="2" t="inlineStr"/>
-      <c r="W22" s="2" t="inlineStr"/>
-      <c r="X22" s="2" t="inlineStr"/>
-      <c r="Y22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="T24" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U24" s="6" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
+        </is>
+      </c>
+      <c r="V24" s="6" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="W24" s="6" t="inlineStr">
+        <is>
+          <t>Run GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="X24" s="6" t="inlineStr">
+        <is>
+          <t>Line 06</t>
+        </is>
+      </c>
+      <c r="Y24" s="6" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>ff12234265b7ed9747283a1b59735ea5ddda19b5</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>test-12</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10T09:21:24Z</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>372cfe624d49eb38f5e8baab2c748007dc54b018</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Update demo.txt</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:04:34Z</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr"/>
+      <c r="N25" s="6" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr"/>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v>24027694141</v>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T25" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U25" s="6" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+        </is>
+      </c>
+      <c r="V25" s="6" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="W25" s="6" t="inlineStr">
+        <is>
+          <t>Set up job</t>
+        </is>
+      </c>
+      <c r="X25" s="6" t="inlineStr">
+        <is>
+          <t>Line 04</t>
+        </is>
+      </c>
+      <c r="Y25" s="6" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="n">
-        <v>24236015736</v>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>e7bf9d94f807df2e25e29ad5d30bc78e1b2fbd25</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Update workflow_report.yml</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:04:22Z</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr"/>
+      <c r="N26" s="6" t="inlineStr"/>
+      <c r="O26" s="6" t="inlineStr"/>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v>24027689526</v>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="S26" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr"/>
-      <c r="V23" s="2" t="inlineStr"/>
-      <c r="W23" s="2" t="inlineStr"/>
-      <c r="X23" s="2" t="inlineStr"/>
-      <c r="Y23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="T26" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U26" s="6" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+        </is>
+      </c>
+      <c r="V26" s="6" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="W26" s="6" t="inlineStr">
+        <is>
+          <t>Set up job</t>
+        </is>
+      </c>
+      <c r="X26" s="6" t="inlineStr">
+        <is>
+          <t>Line 04</t>
+        </is>
+      </c>
+      <c r="Y26" s="6" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>75732834dd766afc090c808510eb71c7693015dd</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>test-8</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10T08:35:13Z</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>3046e3250b6d3bc90634487150d715e566686a47</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Add demo.txt for testing purposes</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:02:10Z</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr"/>
+      <c r="L27" s="6" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr"/>
+      <c r="N27" s="6" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr"/>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>.github/workflows/workflow_report.yml</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v>24027621196</v>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T27" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U27" s="6" t="inlineStr">
+        <is>
+          <t>Failure (see logs)</t>
+        </is>
+      </c>
+      <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
+      <c r="X27" s="6" t="inlineStr">
+        <is>
+          <t>See GitHub Actions logs</t>
+        </is>
+      </c>
+      <c r="Y27" s="6" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="n">
-        <v>24234243976</v>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>32de2be70035a86124e1345187c9ba078e4cf3bf</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Add GitHub Workflow Report YAML configuration</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:01:02Z</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr"/>
+      <c r="K28" s="6" t="inlineStr"/>
+      <c r="L28" s="6" t="inlineStr"/>
+      <c r="M28" s="6" t="inlineStr"/>
+      <c r="N28" s="6" t="inlineStr"/>
+      <c r="O28" s="6" t="inlineStr"/>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>.github/workflows/workflow_report.yml</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v>24027587697</v>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="S28" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr"/>
-      <c r="V24" s="2" t="inlineStr"/>
-      <c r="W24" s="2" t="inlineStr"/>
-      <c r="X24" s="2" t="inlineStr"/>
-      <c r="Y24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="T28" s="7" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="U28" s="6" t="inlineStr">
+        <is>
+          <t>Failure (see logs)</t>
+        </is>
+      </c>
+      <c r="V28" s="6" t="inlineStr"/>
+      <c r="W28" s="6" t="inlineStr"/>
+      <c r="X28" s="6" t="inlineStr">
+        <is>
+          <t>See GitHub Actions logs</t>
+        </is>
+      </c>
+      <c r="Y28" s="6" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>9d220c5657c48c13ca17102c507b756edbba9215</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>test-8</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10T08:32:22Z</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>8eaab42012c4f02192c65cf59561b5c261b2cf90</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Create github_workflow_report.py</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06T09:50:41Z</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr"/>
+      <c r="V29" s="3" t="inlineStr"/>
+      <c r="W29" s="3" t="inlineStr"/>
+      <c r="X29" s="3" t="inlineStr"/>
+      <c r="Y29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="n">
-        <v>24234135440</v>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr"/>
-      <c r="V25" s="2" t="inlineStr"/>
-      <c r="W25" s="2" t="inlineStr"/>
-      <c r="X25" s="2" t="inlineStr"/>
-      <c r="Y25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>981fe60621c98393750f79dd815a0ea7e4aed75e</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>test-8</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10T08:27:06Z</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="n">
-        <v>24233936358</v>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr"/>
-      <c r="V26" s="2" t="inlineStr"/>
-      <c r="W26" s="2" t="inlineStr"/>
-      <c r="X26" s="2" t="inlineStr"/>
-      <c r="Y26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>3cfdf96375ed8ea8c83b95f26b9c87428b8bc8b9</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>test-1</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10T08:18:15Z</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="n">
-        <v>24233616319</v>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr"/>
-      <c r="V27" s="2" t="inlineStr"/>
-      <c r="W27" s="2" t="inlineStr"/>
-      <c r="X27" s="2" t="inlineStr"/>
-      <c r="Y27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>ad211e0513d37204ee54168120dec41978cc6fb4</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>new code change</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-06T15:32:05Z</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="n">
-        <v>24038137070</v>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr"/>
-      <c r="V28" s="2" t="inlineStr"/>
-      <c r="W28" s="2" t="inlineStr"/>
-      <c r="X28" s="2" t="inlineStr"/>
-      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>a9e73f5e7cd8ea7da7f4969f80034915cc9f302c</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Initial commit</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06T09:48:37Z</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr"/>
+      <c r="Y30" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y28"/>
+  <autoFilter ref="A1:Y30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3256,884 +3408,884 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="6" t="n">
         <v>24030846379</v>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>workflow_dispatch</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>generate_report</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Run GitHub Activity Report</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>Line 56</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="6" t="n">
         <v>24030820444</v>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>generate_report</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>Run GitHub Activity Report</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>Line 55</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="6" t="n">
         <v>24029078530</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>generate_report</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Set up job</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Line 52</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="6" t="n">
         <v>24028853853</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Line 45</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>Auth/permission error — check that GH_PAT has the required scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="6" t="n">
         <v>24028486557</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>Line 39</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="6" t="n">
         <v>24028398959</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>Line 29</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>Auth/permission error — check that GH_PAT has the required scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="6" t="n">
         <v>24028208740</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>Install dependencies</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>Line 22</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="6" t="n">
         <v>24028171694</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>Install dependencies</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>Line 21</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="6" t="n">
         <v>24027807973</v>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>Install dependencies</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>Line 08</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="6" t="n">
         <v>24027735534</v>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>Line 06</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="6" t="n">
         <v>24027729636</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>Line 06</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="6" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="6" t="n">
         <v>24027694141</v>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>Set up job</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>Line 04</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="6" t="n">
         <v>24027689526</v>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>Set up job</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>Line 04</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L14" s="6" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>.github/workflows/workflow_report.yml</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="6" t="n">
         <v>24027621196</v>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>Failure (see logs)</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>See GitHub Actions logs</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>.github/workflows/workflow_report.yml</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="6" t="n">
         <v>24027587697</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>Failure (see logs)</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr"/>
-      <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr"/>
+      <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>See GitHub Actions logs</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
@@ -4179,7 +4331,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-10 09:44 UTC</t>
+          <t>Generated: 2026-04-10 14:39 UTC</t>
         </is>
       </c>
     </row>

--- a/github_activity_report.xlsx
+++ b/github_activity_report.xlsx
@@ -4,18 +4,19 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Activity" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Access Control" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Failure Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Failure Alerts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Activity" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Access Control" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Failure Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Failure Alerts" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Activity'!$A$1:$Y$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Failure Summary'!$A$1:$L$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failure Alerts'!$A$3:$L$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Activity'!$A$1:$Z$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failure Summary'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Failure Alerts'!$A$3:$M$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +36,23 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -42,16 +60,31 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="009C5700"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00276221"/>
-    </font>
-    <font>
-      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="009C0006"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -63,11 +96,8 @@
       <color rgb="009C0006"/>
       <sz val="9"/>
     </font>
-    <font>
-      <color rgb="009C0006"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -81,17 +111,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,42 +171,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -540,7 +595,203 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y30"/>
+  <dimension ref="B2:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="44" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>GitHub Activity &amp; Workflow Audit Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 15:17 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Date Range</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 → now</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev/git-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Max Runs</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Maintained by</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>DevOps / Platform Engineering team</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>devops@yourcompany.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Sheets in this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>All commits, PRs, and workflow runs — latest first</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Collaborators and teams with permission levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Failure Summary</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>All failed/timed-out runs with root-cause diagnostics</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Failure Alerts</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Banner + alert table for all failures detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Row colour key</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="6" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>success   — workflow run completed successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="8" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>failure   — workflow run failed or timed out</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="10" t="inlineStr"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>cancelled — workflow run was cancelled or skipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="12" t="inlineStr"/>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>no status — commit / PR row with no associated run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F6B9E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -561,2706 +812,2991 @@
     <col width="39" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="62" customWidth="1" min="21" max="21"/>
-    <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="62" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
+    <col width="62" customWidth="1" min="22" max="22"/>
+    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="28" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="62" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Visibility</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>Default Branch</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Commit ID</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>Commit Message</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>Author</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="14" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="14" t="inlineStr">
         <is>
           <t>PR ID</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="14" t="inlineStr">
         <is>
           <t>PR Title</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="14" t="inlineStr">
         <is>
           <t>PR Author</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="14" t="inlineStr">
         <is>
           <t>PR Status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="14" t="inlineStr">
         <is>
           <t>PR Merged</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="14" t="inlineStr">
         <is>
           <t>PR Merge Date</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="14" t="inlineStr">
         <is>
           <t>Workflow Name</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="14" t="inlineStr">
         <is>
           <t>Workflow Run ID</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="14" t="inlineStr">
         <is>
           <t>Trigger Event</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="14" t="inlineStr">
+        <is>
+          <t>Run Started At</t>
+        </is>
+      </c>
+      <c r="T1" s="14" t="inlineStr">
         <is>
           <t>Workflow Status</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="14" t="inlineStr">
         <is>
           <t>Workflow Conclusion</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="14" t="inlineStr">
         <is>
           <t>Failure Reason</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="14" t="inlineStr">
         <is>
           <t>Failed Job</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="14" t="inlineStr">
         <is>
           <t>Failed Step</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="14" t="inlineStr">
         <is>
           <t>Error Line</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="14" t="inlineStr">
         <is>
           <t>Suggested Fix</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>0bf36a490d78a4819928a11161d34bda33e4f337</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>test-200</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>2026-04-10T15:16:43Z</t>
+        </is>
+      </c>
+      <c r="I2" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J2" s="15" t="inlineStr"/>
+      <c r="K2" s="15" t="inlineStr"/>
+      <c r="L2" s="15" t="inlineStr"/>
+      <c r="M2" s="15" t="inlineStr"/>
+      <c r="N2" s="15" t="inlineStr"/>
+      <c r="O2" s="15" t="inlineStr"/>
+      <c r="P2" s="15" t="inlineStr">
+        <is>
+          <t>GitHub Activity Report</t>
+        </is>
+      </c>
+      <c r="Q2" s="15" t="n">
+        <v>24250086438</v>
+      </c>
+      <c r="R2" s="15" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S2" s="15" t="inlineStr">
+        <is>
+          <t>2026-04-10T15:17:09Z</t>
+        </is>
+      </c>
+      <c r="T2" s="15" t="inlineStr">
+        <is>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="U2" s="15" t="inlineStr"/>
+      <c r="V2" s="15" t="inlineStr"/>
+      <c r="W2" s="15" t="inlineStr"/>
+      <c r="X2" s="15" t="inlineStr"/>
+      <c r="Y2" s="15" t="inlineStr"/>
+      <c r="Z2" s="15" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>4744a63d54822fd75d284791aa8b6524acb33646</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>chore: update activity report [2026-04-10 14:39 UTC] via push (run 24248391662)</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>github-actions[bot]</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10T14:39:22Z</t>
+        </is>
+      </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr"/>
+      <c r="K3" s="16" t="inlineStr"/>
+      <c r="L3" s="16" t="inlineStr"/>
+      <c r="M3" s="16" t="inlineStr"/>
+      <c r="N3" s="16" t="inlineStr"/>
+      <c r="O3" s="16" t="inlineStr"/>
+      <c r="P3" s="16" t="inlineStr"/>
+      <c r="Q3" s="16" t="inlineStr"/>
+      <c r="R3" s="16" t="inlineStr"/>
+      <c r="S3" s="16" t="inlineStr"/>
+      <c r="T3" s="16" t="inlineStr"/>
+      <c r="U3" s="16" t="inlineStr"/>
+      <c r="V3" s="16" t="inlineStr"/>
+      <c r="W3" s="16" t="inlineStr"/>
+      <c r="X3" s="16" t="inlineStr"/>
+      <c r="Y3" s="16" t="inlineStr"/>
+      <c r="Z3" s="16" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>408ddd043c24815f4498a813c6ca81c4e9688b9b</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>test-198</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T14:38:25Z</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr"/>
+      <c r="K4" s="17" t="inlineStr"/>
+      <c r="L4" s="17" t="inlineStr"/>
+      <c r="M4" s="17" t="inlineStr"/>
+      <c r="N4" s="17" t="inlineStr"/>
+      <c r="O4" s="17" t="inlineStr"/>
+      <c r="P4" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q4" s="17" t="n">
         <v>24248391662</v>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R4" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="S4" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T14:38:48Z</t>
+        </is>
+      </c>
+      <c r="T4" s="17" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U4" s="18" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V4" s="17" t="inlineStr"/>
+      <c r="W4" s="17" t="inlineStr"/>
+      <c r="X4" s="17" t="inlineStr"/>
+      <c r="Y4" s="17" t="inlineStr"/>
+      <c r="Z4" s="17" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>37f60b0c23d45eef199630a384945ef73970b8d7</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>chore: update activity report [2026-04-10 09:44 UTC] via push (run 24236872105)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>github-actions[bot]</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T09:44:03Z</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr"/>
-      <c r="V3" s="3" t="inlineStr"/>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr"/>
-      <c r="Y3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr"/>
+      <c r="K5" s="16" t="inlineStr"/>
+      <c r="L5" s="16" t="inlineStr"/>
+      <c r="M5" s="16" t="inlineStr"/>
+      <c r="N5" s="16" t="inlineStr"/>
+      <c r="O5" s="16" t="inlineStr"/>
+      <c r="P5" s="16" t="inlineStr"/>
+      <c r="Q5" s="16" t="inlineStr"/>
+      <c r="R5" s="16" t="inlineStr"/>
+      <c r="S5" s="16" t="inlineStr"/>
+      <c r="T5" s="16" t="inlineStr"/>
+      <c r="U5" s="16" t="inlineStr"/>
+      <c r="V5" s="16" t="inlineStr"/>
+      <c r="W5" s="16" t="inlineStr"/>
+      <c r="X5" s="16" t="inlineStr"/>
+      <c r="Y5" s="16" t="inlineStr"/>
+      <c r="Z5" s="16" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>aac0b4a033d6b371042ec3f99a213aa53e5d925f</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>test-198</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T09:40:50Z</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr"/>
+      <c r="K6" s="17" t="inlineStr"/>
+      <c r="L6" s="17" t="inlineStr"/>
+      <c r="M6" s="17" t="inlineStr"/>
+      <c r="N6" s="17" t="inlineStr"/>
+      <c r="O6" s="17" t="inlineStr"/>
+      <c r="P6" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="Q6" s="17" t="n">
         <v>24236872105</v>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="R6" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="S6" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T09:43:38Z</t>
+        </is>
+      </c>
+      <c r="T6" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="U6" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr"/>
-      <c r="Y4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="V6" s="17" t="inlineStr"/>
+      <c r="W6" s="17" t="inlineStr"/>
+      <c r="X6" s="17" t="inlineStr"/>
+      <c r="Y6" s="17" t="inlineStr"/>
+      <c r="Z6" s="17" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>19b0e6e1eadc37093a80d5aa3b43d47cf52cc739</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>chore: update activity report [2026-04-10 09:36 UTC] via push (run 24236579665)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>github-actions[bot]</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T09:36:36Z</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="3" t="inlineStr"/>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr"/>
-      <c r="Y5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr"/>
+      <c r="K7" s="16" t="inlineStr"/>
+      <c r="L7" s="16" t="inlineStr"/>
+      <c r="M7" s="16" t="inlineStr"/>
+      <c r="N7" s="16" t="inlineStr"/>
+      <c r="O7" s="16" t="inlineStr"/>
+      <c r="P7" s="16" t="inlineStr"/>
+      <c r="Q7" s="16" t="inlineStr"/>
+      <c r="R7" s="16" t="inlineStr"/>
+      <c r="S7" s="16" t="inlineStr"/>
+      <c r="T7" s="16" t="inlineStr"/>
+      <c r="U7" s="16" t="inlineStr"/>
+      <c r="V7" s="16" t="inlineStr"/>
+      <c r="W7" s="16" t="inlineStr"/>
+      <c r="X7" s="16" t="inlineStr"/>
+      <c r="Y7" s="16" t="inlineStr"/>
+      <c r="Z7" s="16" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>4246e5f5bdd0c663224514d45c37457253e6806b</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>test-13</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T09:35:54Z</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr"/>
+      <c r="K8" s="17" t="inlineStr"/>
+      <c r="L8" s="17" t="inlineStr"/>
+      <c r="M8" s="17" t="inlineStr"/>
+      <c r="N8" s="17" t="inlineStr"/>
+      <c r="O8" s="17" t="inlineStr"/>
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="Q8" s="17" t="n">
         <v>24236579665</v>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="R8" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="S8" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T09:36:01Z</t>
+        </is>
+      </c>
+      <c r="T8" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T6" s="5" t="inlineStr">
+      <c r="U8" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="V8" s="17" t="inlineStr"/>
+      <c r="W8" s="17" t="inlineStr"/>
+      <c r="X8" s="17" t="inlineStr"/>
+      <c r="Y8" s="17" t="inlineStr"/>
+      <c r="Z8" s="17" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>ff12234265b7ed9747283a1b59735ea5ddda19b5</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>test-12</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T09:21:24Z</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr"/>
+      <c r="K9" s="17" t="inlineStr"/>
+      <c r="L9" s="17" t="inlineStr"/>
+      <c r="M9" s="17" t="inlineStr"/>
+      <c r="N9" s="17" t="inlineStr"/>
+      <c r="O9" s="17" t="inlineStr"/>
+      <c r="P9" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="n">
+      <c r="Q9" s="17" t="n">
         <v>24236015736</v>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="R9" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="S9" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T09:21:36Z</t>
+        </is>
+      </c>
+      <c r="T9" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr">
+      <c r="U9" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="V9" s="17" t="inlineStr"/>
+      <c r="W9" s="17" t="inlineStr"/>
+      <c r="X9" s="17" t="inlineStr"/>
+      <c r="Y9" s="17" t="inlineStr"/>
+      <c r="Z9" s="17" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>75732834dd766afc090c808510eb71c7693015dd</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>test-8</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T08:35:13Z</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr"/>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr"/>
+      <c r="K10" s="17" t="inlineStr"/>
+      <c r="L10" s="17" t="inlineStr"/>
+      <c r="M10" s="17" t="inlineStr"/>
+      <c r="N10" s="17" t="inlineStr"/>
+      <c r="O10" s="17" t="inlineStr"/>
+      <c r="P10" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="Q10" s="17" t="n">
         <v>24234243976</v>
       </c>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="R10" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr">
+      <c r="S10" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T08:35:20Z</t>
+        </is>
+      </c>
+      <c r="T10" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T8" s="5" t="inlineStr">
+      <c r="U10" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="V10" s="17" t="inlineStr"/>
+      <c r="W10" s="17" t="inlineStr"/>
+      <c r="X10" s="17" t="inlineStr"/>
+      <c r="Y10" s="17" t="inlineStr"/>
+      <c r="Z10" s="17" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>9d220c5657c48c13ca17102c507b756edbba9215</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>test-8</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T08:32:22Z</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr"/>
+      <c r="K11" s="17" t="inlineStr"/>
+      <c r="L11" s="17" t="inlineStr"/>
+      <c r="M11" s="17" t="inlineStr"/>
+      <c r="N11" s="17" t="inlineStr"/>
+      <c r="O11" s="17" t="inlineStr"/>
+      <c r="P11" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="n">
+      <c r="Q11" s="17" t="n">
         <v>24234135440</v>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="R11" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr">
+      <c r="S11" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T08:32:30Z</t>
+        </is>
+      </c>
+      <c r="T11" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T9" s="5" t="inlineStr">
+      <c r="U11" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="V11" s="17" t="inlineStr"/>
+      <c r="W11" s="17" t="inlineStr"/>
+      <c r="X11" s="17" t="inlineStr"/>
+      <c r="Y11" s="17" t="inlineStr"/>
+      <c r="Z11" s="17" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>981fe60621c98393750f79dd815a0ea7e4aed75e</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>test-8</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T08:27:06Z</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="inlineStr"/>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr"/>
+      <c r="K12" s="17" t="inlineStr"/>
+      <c r="L12" s="17" t="inlineStr"/>
+      <c r="M12" s="17" t="inlineStr"/>
+      <c r="N12" s="17" t="inlineStr"/>
+      <c r="O12" s="17" t="inlineStr"/>
+      <c r="P12" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="n">
+      <c r="Q12" s="17" t="n">
         <v>24233936358</v>
       </c>
-      <c r="R10" s="4" t="inlineStr">
+      <c r="R12" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S10" s="4" t="inlineStr">
+      <c r="S12" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T08:27:14Z</t>
+        </is>
+      </c>
+      <c r="T12" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T10" s="5" t="inlineStr">
+      <c r="U12" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="V12" s="17" t="inlineStr"/>
+      <c r="W12" s="17" t="inlineStr"/>
+      <c r="X12" s="17" t="inlineStr"/>
+      <c r="Y12" s="17" t="inlineStr"/>
+      <c r="Z12" s="17" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>3cfdf96375ed8ea8c83b95f26b9c87428b8bc8b9</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>test-1</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T08:18:15Z</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="J13" s="17" t="inlineStr"/>
+      <c r="K13" s="17" t="inlineStr"/>
+      <c r="L13" s="17" t="inlineStr"/>
+      <c r="M13" s="17" t="inlineStr"/>
+      <c r="N13" s="17" t="inlineStr"/>
+      <c r="O13" s="17" t="inlineStr"/>
+      <c r="P13" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="n">
+      <c r="Q13" s="17" t="n">
         <v>24233616319</v>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="R13" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr">
+      <c r="S13" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T08:18:28Z</t>
+        </is>
+      </c>
+      <c r="T13" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T11" s="5" t="inlineStr">
+      <c r="U13" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr"/>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="V13" s="17" t="inlineStr"/>
+      <c r="W13" s="17" t="inlineStr"/>
+      <c r="X13" s="17" t="inlineStr"/>
+      <c r="Y13" s="17" t="inlineStr"/>
+      <c r="Z13" s="17" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>ad211e0513d37204ee54168120dec41978cc6fb4</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>new code change</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>2026-04-06T15:32:05Z</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" s="4" t="inlineStr"/>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="J14" s="17" t="inlineStr"/>
+      <c r="K14" s="17" t="inlineStr"/>
+      <c r="L14" s="17" t="inlineStr"/>
+      <c r="M14" s="17" t="inlineStr"/>
+      <c r="N14" s="17" t="inlineStr"/>
+      <c r="O14" s="17" t="inlineStr"/>
+      <c r="P14" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="n">
+      <c r="Q14" s="17" t="n">
         <v>24038137070</v>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="R14" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S12" s="4" t="inlineStr">
+      <c r="S14" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-06T15:32:18Z</t>
+        </is>
+      </c>
+      <c r="T14" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T12" s="5" t="inlineStr">
+      <c r="U14" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="V14" s="17" t="inlineStr"/>
+      <c r="W14" s="17" t="inlineStr"/>
+      <c r="X14" s="17" t="inlineStr"/>
+      <c r="Y14" s="17" t="inlineStr"/>
+      <c r="Z14" s="17" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>21f8e2bcc8765be2c9dd97d0d839686b7afe3de1</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>new code change</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>2026-04-06T12:24:00Z</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr"/>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="4" t="inlineStr"/>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr"/>
+      <c r="K15" s="17" t="inlineStr"/>
+      <c r="L15" s="17" t="inlineStr"/>
+      <c r="M15" s="17" t="inlineStr"/>
+      <c r="N15" s="17" t="inlineStr"/>
+      <c r="O15" s="17" t="inlineStr"/>
+      <c r="P15" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="n">
+      <c r="Q15" s="17" t="n">
         <v>24031673216</v>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="R15" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="S15" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-06T12:24:13Z</t>
+        </is>
+      </c>
+      <c r="T15" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T13" s="5" t="inlineStr">
+      <c r="U15" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="inlineStr"/>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="V15" s="17" t="inlineStr"/>
+      <c r="W15" s="17" t="inlineStr"/>
+      <c r="X15" s="17" t="inlineStr"/>
+      <c r="Y15" s="17" t="inlineStr"/>
+      <c r="Z15" s="17" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>code changed1</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H16" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T11:54:44Z</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I16" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
-      <c r="L14" s="6" t="inlineStr"/>
-      <c r="M14" s="6" t="inlineStr"/>
-      <c r="N14" s="6" t="inlineStr"/>
-      <c r="O14" s="6" t="inlineStr"/>
-      <c r="P14" s="6" t="inlineStr">
+      <c r="J16" s="19" t="inlineStr"/>
+      <c r="K16" s="19" t="inlineStr"/>
+      <c r="L16" s="19" t="inlineStr"/>
+      <c r="M16" s="19" t="inlineStr"/>
+      <c r="N16" s="19" t="inlineStr"/>
+      <c r="O16" s="19" t="inlineStr"/>
+      <c r="P16" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q16" s="19" t="n">
         <v>24030846379</v>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R16" s="19" t="inlineStr">
         <is>
           <t>workflow_dispatch</t>
         </is>
       </c>
-      <c r="S14" s="6" t="inlineStr">
+      <c r="S16" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T11:55:45Z</t>
+        </is>
+      </c>
+      <c r="T16" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T14" s="7" t="inlineStr">
+      <c r="U16" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
+      <c r="V16" s="19" t="inlineStr">
         <is>
           <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="V14" s="6" t="inlineStr">
+      <c r="W16" s="19" t="inlineStr">
         <is>
           <t>generate_report</t>
         </is>
       </c>
-      <c r="W14" s="6" t="inlineStr">
+      <c r="X16" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Activity Report</t>
         </is>
       </c>
-      <c r="X14" s="6" t="inlineStr">
+      <c r="Y16" s="19" t="inlineStr">
         <is>
           <t>Line 56</t>
         </is>
       </c>
-      <c r="Y14" s="6" t="inlineStr">
+      <c r="Z16" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>code changed1</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H17" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T11:54:44Z</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I17" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
-      <c r="L15" s="6" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr"/>
-      <c r="O15" s="6" t="inlineStr"/>
-      <c r="P15" s="6" t="inlineStr">
+      <c r="J17" s="19" t="inlineStr"/>
+      <c r="K17" s="19" t="inlineStr"/>
+      <c r="L17" s="19" t="inlineStr"/>
+      <c r="M17" s="19" t="inlineStr"/>
+      <c r="N17" s="19" t="inlineStr"/>
+      <c r="O17" s="19" t="inlineStr"/>
+      <c r="P17" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="Q17" s="19" t="n">
         <v>24030820444</v>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R17" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S15" s="6" t="inlineStr">
+      <c r="S17" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T11:54:51Z</t>
+        </is>
+      </c>
+      <c r="T17" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T15" s="7" t="inlineStr">
+      <c r="U17" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
+      <c r="V17" s="19" t="inlineStr">
         <is>
           <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="V15" s="6" t="inlineStr">
+      <c r="W17" s="19" t="inlineStr">
         <is>
           <t>generate_report</t>
         </is>
       </c>
-      <c r="W15" s="6" t="inlineStr">
+      <c r="X17" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Activity Report</t>
         </is>
       </c>
-      <c r="X15" s="6" t="inlineStr">
+      <c r="Y17" s="19" t="inlineStr">
         <is>
           <t>Line 55</t>
         </is>
       </c>
-      <c r="Y15" s="6" t="inlineStr">
+      <c r="Z17" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>733b89967b9b4731953302840f2ddb2c20bedf56</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>code changed</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H18" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:52:40Z</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I18" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr"/>
-      <c r="K16" s="6" t="inlineStr"/>
-      <c r="L16" s="6" t="inlineStr"/>
-      <c r="M16" s="6" t="inlineStr"/>
-      <c r="N16" s="6" t="inlineStr"/>
-      <c r="O16" s="6" t="inlineStr"/>
-      <c r="P16" s="6" t="inlineStr">
+      <c r="J18" s="19" t="inlineStr"/>
+      <c r="K18" s="19" t="inlineStr"/>
+      <c r="L18" s="19" t="inlineStr"/>
+      <c r="M18" s="19" t="inlineStr"/>
+      <c r="N18" s="19" t="inlineStr"/>
+      <c r="O18" s="19" t="inlineStr"/>
+      <c r="P18" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="Q18" s="19" t="n">
         <v>24029078530</v>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R18" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S16" s="6" t="inlineStr">
+      <c r="S18" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:52:49Z</t>
+        </is>
+      </c>
+      <c r="T18" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T16" s="7" t="inlineStr">
+      <c r="U18" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
+      <c r="V18" s="19" t="inlineStr">
         <is>
           <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
-      <c r="V16" s="6" t="inlineStr">
+      <c r="W18" s="19" t="inlineStr">
         <is>
           <t>generate_report</t>
         </is>
       </c>
-      <c r="W16" s="6" t="inlineStr">
+      <c r="X18" s="19" t="inlineStr">
         <is>
           <t>Set up job</t>
         </is>
       </c>
-      <c r="X16" s="6" t="inlineStr">
+      <c r="Y18" s="19" t="inlineStr">
         <is>
           <t>Line 52</t>
         </is>
       </c>
-      <c r="Y16" s="6" t="inlineStr">
+      <c r="Z18" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>aedf77ebc8e0433ebbe37ca97908ee5caf3929d6</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>code changd</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H19" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:44:38Z</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I19" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr"/>
-      <c r="K17" s="6" t="inlineStr"/>
-      <c r="L17" s="6" t="inlineStr"/>
-      <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr"/>
-      <c r="O17" s="6" t="inlineStr"/>
-      <c r="P17" s="6" t="inlineStr">
+      <c r="J19" s="19" t="inlineStr"/>
+      <c r="K19" s="19" t="inlineStr"/>
+      <c r="L19" s="19" t="inlineStr"/>
+      <c r="M19" s="19" t="inlineStr"/>
+      <c r="N19" s="19" t="inlineStr"/>
+      <c r="O19" s="19" t="inlineStr"/>
+      <c r="P19" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="Q19" s="19" t="n">
         <v>24028853853</v>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R19" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S17" s="6" t="inlineStr">
+      <c r="S19" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:44:47Z</t>
+        </is>
+      </c>
+      <c r="T19" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T17" s="7" t="inlineStr">
+      <c r="U19" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
+      <c r="V19" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
         </is>
       </c>
-      <c r="V17" s="6" t="inlineStr">
+      <c r="W19" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="W17" s="6" t="inlineStr">
+      <c r="X19" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="X17" s="6" t="inlineStr">
+      <c r="Y19" s="19" t="inlineStr">
         <is>
           <t>Line 45</t>
         </is>
       </c>
-      <c r="Y17" s="6" t="inlineStr">
-        <is>
-          <t>Auth/permission error — check that GH_PAT has the required scopes and that repository secrets are correctly configured.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="Z19" s="19" t="inlineStr">
+        <is>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>5feb9eb868fd9ff9e4a7150d13cb3252d843c106</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>Update demo.txt</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:31:56Z</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I20" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J18" s="6" t="inlineStr"/>
-      <c r="K18" s="6" t="inlineStr"/>
-      <c r="L18" s="6" t="inlineStr"/>
-      <c r="M18" s="6" t="inlineStr"/>
-      <c r="N18" s="6" t="inlineStr"/>
-      <c r="O18" s="6" t="inlineStr"/>
-      <c r="P18" s="6" t="inlineStr">
+      <c r="J20" s="19" t="inlineStr"/>
+      <c r="K20" s="19" t="inlineStr"/>
+      <c r="L20" s="19" t="inlineStr"/>
+      <c r="M20" s="19" t="inlineStr"/>
+      <c r="N20" s="19" t="inlineStr"/>
+      <c r="O20" s="19" t="inlineStr"/>
+      <c r="P20" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="Q20" s="19" t="n">
         <v>24028486557</v>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R20" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S18" s="6" t="inlineStr">
+      <c r="S20" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:39:17Z</t>
+        </is>
+      </c>
+      <c r="T20" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T18" s="7" t="inlineStr">
+      <c r="U20" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U18" s="6" t="inlineStr">
+      <c r="V20" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="V18" s="6" t="inlineStr">
+      <c r="W20" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="W18" s="6" t="inlineStr">
+      <c r="X20" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="X18" s="6" t="inlineStr">
+      <c r="Y20" s="19" t="inlineStr">
         <is>
           <t>Line 39</t>
         </is>
       </c>
-      <c r="Y18" s="6" t="inlineStr">
+      <c r="Z20" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>2fcbd831207ea4821a39ee88d33aa21454ca19e3</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>code changed@v1</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H21" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:28:57Z</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I21" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
-      <c r="L19" s="6" t="inlineStr"/>
-      <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr"/>
-      <c r="O19" s="6" t="inlineStr"/>
-      <c r="P19" s="6" t="inlineStr">
+      <c r="J21" s="19" t="inlineStr"/>
+      <c r="K21" s="19" t="inlineStr"/>
+      <c r="L21" s="19" t="inlineStr"/>
+      <c r="M21" s="19" t="inlineStr"/>
+      <c r="N21" s="19" t="inlineStr"/>
+      <c r="O21" s="19" t="inlineStr"/>
+      <c r="P21" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="n">
+      <c r="Q21" s="19" t="n">
         <v>24028398959</v>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R21" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S19" s="6" t="inlineStr">
+      <c r="S21" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:29:06Z</t>
+        </is>
+      </c>
+      <c r="T21" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T19" s="7" t="inlineStr">
+      <c r="U21" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U19" s="6" t="inlineStr">
+      <c r="V21" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="V19" s="6" t="inlineStr">
+      <c r="W21" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="W19" s="6" t="inlineStr">
+      <c r="X21" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="X19" s="6" t="inlineStr">
+      <c r="Y21" s="19" t="inlineStr">
         <is>
           <t>Line 29</t>
         </is>
       </c>
-      <c r="Y19" s="6" t="inlineStr">
-        <is>
-          <t>Auth/permission error — check that GH_PAT has the required scopes and that repository secrets are correctly configured.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="Z21" s="19" t="inlineStr">
+        <is>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>37ddfe095b13b5e65a98ff2072c4bbb77cde7c1b</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>code changed</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H22" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:22:31Z</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I22" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
-      <c r="L20" s="6" t="inlineStr"/>
-      <c r="M20" s="6" t="inlineStr"/>
-      <c r="N20" s="6" t="inlineStr"/>
-      <c r="O20" s="6" t="inlineStr"/>
-      <c r="P20" s="6" t="inlineStr">
+      <c r="J22" s="19" t="inlineStr"/>
+      <c r="K22" s="19" t="inlineStr"/>
+      <c r="L22" s="19" t="inlineStr"/>
+      <c r="M22" s="19" t="inlineStr"/>
+      <c r="N22" s="19" t="inlineStr"/>
+      <c r="O22" s="19" t="inlineStr"/>
+      <c r="P22" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="Q22" s="19" t="n">
         <v>24028208740</v>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R22" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S20" s="6" t="inlineStr">
+      <c r="S22" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:22:38Z</t>
+        </is>
+      </c>
+      <c r="T22" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T20" s="7" t="inlineStr">
+      <c r="U22" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U20" s="6" t="inlineStr">
+      <c r="V22" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
-      <c r="V20" s="6" t="inlineStr">
+      <c r="W22" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="W20" s="6" t="inlineStr">
+      <c r="X22" s="19" t="inlineStr">
         <is>
           <t>Install dependencies</t>
         </is>
       </c>
-      <c r="X20" s="6" t="inlineStr">
+      <c r="Y22" s="19" t="inlineStr">
         <is>
           <t>Line 22</t>
         </is>
       </c>
-      <c r="Y20" s="6" t="inlineStr">
+      <c r="Z22" s="19" t="inlineStr">
         <is>
           <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>74dcfb5e2119b07af9671cc4c8396585d44a6fb8</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G23" s="19" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H23" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:21:05Z</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I23" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
-      <c r="L21" s="6" t="inlineStr"/>
-      <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr"/>
-      <c r="O21" s="6" t="inlineStr"/>
-      <c r="P21" s="6" t="inlineStr">
+      <c r="J23" s="19" t="inlineStr"/>
+      <c r="K23" s="19" t="inlineStr"/>
+      <c r="L23" s="19" t="inlineStr"/>
+      <c r="M23" s="19" t="inlineStr"/>
+      <c r="N23" s="19" t="inlineStr"/>
+      <c r="O23" s="19" t="inlineStr"/>
+      <c r="P23" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="Q23" s="19" t="n">
         <v>24028171694</v>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R23" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S21" s="6" t="inlineStr">
+      <c r="S23" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:21:19Z</t>
+        </is>
+      </c>
+      <c r="T23" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T21" s="7" t="inlineStr">
+      <c r="U23" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U21" s="6" t="inlineStr">
+      <c r="V23" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
-      <c r="V21" s="6" t="inlineStr">
+      <c r="W23" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="W21" s="6" t="inlineStr">
+      <c r="X23" s="19" t="inlineStr">
         <is>
           <t>Install dependencies</t>
         </is>
       </c>
-      <c r="X21" s="6" t="inlineStr">
+      <c r="Y23" s="19" t="inlineStr">
         <is>
           <t>Line 21</t>
         </is>
       </c>
-      <c r="Y21" s="6" t="inlineStr">
+      <c r="Z23" s="19" t="inlineStr">
         <is>
           <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E24" s="19" t="inlineStr">
         <is>
           <t>5ff73a4b92ec974d47dc4998318d0eb25003ef50</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>Enhance workflow with caching and Node.js versioning</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H24" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:08:38Z</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I24" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J22" s="6" t="inlineStr"/>
-      <c r="K22" s="6" t="inlineStr"/>
-      <c r="L22" s="6" t="inlineStr"/>
-      <c r="M22" s="6" t="inlineStr"/>
-      <c r="N22" s="6" t="inlineStr"/>
-      <c r="O22" s="6" t="inlineStr"/>
-      <c r="P22" s="6" t="inlineStr">
+      <c r="J24" s="19" t="inlineStr"/>
+      <c r="K24" s="19" t="inlineStr"/>
+      <c r="L24" s="19" t="inlineStr"/>
+      <c r="M24" s="19" t="inlineStr"/>
+      <c r="N24" s="19" t="inlineStr"/>
+      <c r="O24" s="19" t="inlineStr"/>
+      <c r="P24" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="n">
+      <c r="Q24" s="19" t="n">
         <v>24027807973</v>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="R24" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S22" s="6" t="inlineStr">
+      <c r="S24" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:08:40Z</t>
+        </is>
+      </c>
+      <c r="T24" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T22" s="7" t="inlineStr">
+      <c r="U24" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U22" s="6" t="inlineStr">
+      <c r="V24" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
-      <c r="V22" s="6" t="inlineStr">
+      <c r="W24" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="W22" s="6" t="inlineStr">
+      <c r="X24" s="19" t="inlineStr">
         <is>
           <t>Install dependencies</t>
         </is>
       </c>
-      <c r="X22" s="6" t="inlineStr">
+      <c r="Y24" s="19" t="inlineStr">
         <is>
           <t>Line 08</t>
         </is>
       </c>
-      <c r="Y22" s="6" t="inlineStr">
+      <c r="Z24" s="19" t="inlineStr">
         <is>
           <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>ad002901ed69655717989c4485c2df1f343c5b15</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>Fix typo in demo.txt</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="G25" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H25" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:06:00Z</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I25" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr"/>
-      <c r="K23" s="6" t="inlineStr"/>
-      <c r="L23" s="6" t="inlineStr"/>
-      <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr"/>
-      <c r="O23" s="6" t="inlineStr"/>
-      <c r="P23" s="6" t="inlineStr">
+      <c r="J25" s="19" t="inlineStr"/>
+      <c r="K25" s="19" t="inlineStr"/>
+      <c r="L25" s="19" t="inlineStr"/>
+      <c r="M25" s="19" t="inlineStr"/>
+      <c r="N25" s="19" t="inlineStr"/>
+      <c r="O25" s="19" t="inlineStr"/>
+      <c r="P25" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="n">
+      <c r="Q25" s="19" t="n">
         <v>24027735534</v>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R25" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S23" s="6" t="inlineStr">
+      <c r="S25" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:06:01Z</t>
+        </is>
+      </c>
+      <c r="T25" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T23" s="7" t="inlineStr">
+      <c r="U25" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U23" s="6" t="inlineStr">
+      <c r="V25" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="V23" s="6" t="inlineStr">
+      <c r="W25" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="W23" s="6" t="inlineStr">
+      <c r="X25" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="X23" s="6" t="inlineStr">
+      <c r="Y25" s="19" t="inlineStr">
         <is>
           <t>Line 06</t>
         </is>
       </c>
-      <c r="Y23" s="6" t="inlineStr">
+      <c r="Z25" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E26" s="19" t="inlineStr">
         <is>
           <t>06a295fe67b6991a6ba3430be5f485beedd7805f</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>Update workflow_report.yml</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H26" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:05:48Z</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I26" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J24" s="6" t="inlineStr"/>
-      <c r="K24" s="6" t="inlineStr"/>
-      <c r="L24" s="6" t="inlineStr"/>
-      <c r="M24" s="6" t="inlineStr"/>
-      <c r="N24" s="6" t="inlineStr"/>
-      <c r="O24" s="6" t="inlineStr"/>
-      <c r="P24" s="6" t="inlineStr">
+      <c r="J26" s="19" t="inlineStr"/>
+      <c r="K26" s="19" t="inlineStr"/>
+      <c r="L26" s="19" t="inlineStr"/>
+      <c r="M26" s="19" t="inlineStr"/>
+      <c r="N26" s="19" t="inlineStr"/>
+      <c r="O26" s="19" t="inlineStr"/>
+      <c r="P26" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="n">
+      <c r="Q26" s="19" t="n">
         <v>24027729636</v>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R26" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S24" s="6" t="inlineStr">
+      <c r="S26" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:05:49Z</t>
+        </is>
+      </c>
+      <c r="T26" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T24" s="7" t="inlineStr">
+      <c r="U26" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U24" s="6" t="inlineStr">
+      <c r="V26" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="V24" s="6" t="inlineStr">
+      <c r="W26" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="W24" s="6" t="inlineStr">
+      <c r="X26" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="X24" s="6" t="inlineStr">
+      <c r="Y26" s="19" t="inlineStr">
         <is>
           <t>Line 06</t>
         </is>
       </c>
-      <c r="Y24" s="6" t="inlineStr">
+      <c r="Z26" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E27" s="19" t="inlineStr">
         <is>
           <t>372cfe624d49eb38f5e8baab2c748007dc54b018</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>Update demo.txt</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H27" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:04:34Z</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I27" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
-      <c r="L25" s="6" t="inlineStr"/>
-      <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="6" t="inlineStr"/>
-      <c r="O25" s="6" t="inlineStr"/>
-      <c r="P25" s="6" t="inlineStr">
+      <c r="J27" s="19" t="inlineStr"/>
+      <c r="K27" s="19" t="inlineStr"/>
+      <c r="L27" s="19" t="inlineStr"/>
+      <c r="M27" s="19" t="inlineStr"/>
+      <c r="N27" s="19" t="inlineStr"/>
+      <c r="O27" s="19" t="inlineStr"/>
+      <c r="P27" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="n">
+      <c r="Q27" s="19" t="n">
         <v>24027694141</v>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R27" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S25" s="6" t="inlineStr">
+      <c r="S27" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:04:36Z</t>
+        </is>
+      </c>
+      <c r="T27" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T25" s="7" t="inlineStr">
+      <c r="U27" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U25" s="6" t="inlineStr">
+      <c r="V27" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
-      <c r="V25" s="6" t="inlineStr">
+      <c r="W27" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="W25" s="6" t="inlineStr">
+      <c r="X27" s="19" t="inlineStr">
         <is>
           <t>Set up job</t>
         </is>
       </c>
-      <c r="X25" s="6" t="inlineStr">
+      <c r="Y27" s="19" t="inlineStr">
         <is>
           <t>Line 04</t>
         </is>
       </c>
-      <c r="Y25" s="6" t="inlineStr">
+      <c r="Z27" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E28" s="19" t="inlineStr">
         <is>
           <t>e7bf9d94f807df2e25e29ad5d30bc78e1b2fbd25</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>Update workflow_report.yml</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H28" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:04:22Z</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I28" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
-      <c r="L26" s="6" t="inlineStr"/>
-      <c r="M26" s="6" t="inlineStr"/>
-      <c r="N26" s="6" t="inlineStr"/>
-      <c r="O26" s="6" t="inlineStr"/>
-      <c r="P26" s="6" t="inlineStr">
+      <c r="J28" s="19" t="inlineStr"/>
+      <c r="K28" s="19" t="inlineStr"/>
+      <c r="L28" s="19" t="inlineStr"/>
+      <c r="M28" s="19" t="inlineStr"/>
+      <c r="N28" s="19" t="inlineStr"/>
+      <c r="O28" s="19" t="inlineStr"/>
+      <c r="P28" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="n">
+      <c r="Q28" s="19" t="n">
         <v>24027689526</v>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R28" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S26" s="6" t="inlineStr">
+      <c r="S28" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:04:27Z</t>
+        </is>
+      </c>
+      <c r="T28" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T26" s="7" t="inlineStr">
+      <c r="U28" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U26" s="6" t="inlineStr">
+      <c r="V28" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
-      <c r="V26" s="6" t="inlineStr">
+      <c r="W28" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="W26" s="6" t="inlineStr">
+      <c r="X28" s="19" t="inlineStr">
         <is>
           <t>Set up job</t>
         </is>
       </c>
-      <c r="X26" s="6" t="inlineStr">
+      <c r="Y28" s="19" t="inlineStr">
         <is>
           <t>Line 04</t>
         </is>
       </c>
-      <c r="Y26" s="6" t="inlineStr">
+      <c r="Z28" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E29" s="19" t="inlineStr">
         <is>
           <t>3046e3250b6d3bc90634487150d715e566686a47</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>Add demo.txt for testing purposes</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H29" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:02:10Z</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I29" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
-      <c r="L27" s="6" t="inlineStr"/>
-      <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="6" t="inlineStr"/>
-      <c r="O27" s="6" t="inlineStr"/>
-      <c r="P27" s="6" t="inlineStr">
+      <c r="J29" s="19" t="inlineStr"/>
+      <c r="K29" s="19" t="inlineStr"/>
+      <c r="L29" s="19" t="inlineStr"/>
+      <c r="M29" s="19" t="inlineStr"/>
+      <c r="N29" s="19" t="inlineStr"/>
+      <c r="O29" s="19" t="inlineStr"/>
+      <c r="P29" s="19" t="inlineStr">
         <is>
           <t>.github/workflows/workflow_report.yml</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="n">
+      <c r="Q29" s="19" t="n">
         <v>24027621196</v>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R29" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S27" s="6" t="inlineStr">
+      <c r="S29" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:02:12Z</t>
+        </is>
+      </c>
+      <c r="T29" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T27" s="7" t="inlineStr">
+      <c r="U29" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U27" s="6" t="inlineStr">
+      <c r="V29" s="19" t="inlineStr">
         <is>
           <t>Failure (see logs)</t>
         </is>
       </c>
-      <c r="V27" s="6" t="inlineStr"/>
-      <c r="W27" s="6" t="inlineStr"/>
-      <c r="X27" s="6" t="inlineStr">
+      <c r="W29" s="19" t="inlineStr"/>
+      <c r="X29" s="19" t="inlineStr"/>
+      <c r="Y29" s="19" t="inlineStr">
         <is>
           <t>See GitHub Actions logs</t>
         </is>
       </c>
-      <c r="Y27" s="6" t="inlineStr">
+      <c r="Z29" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E30" s="19" t="inlineStr">
         <is>
           <t>32de2be70035a86124e1345187c9ba078e4cf3bf</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>Add GitHub Workflow Report YAML configuration</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H30" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:01:02Z</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I30" s="19" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J28" s="6" t="inlineStr"/>
-      <c r="K28" s="6" t="inlineStr"/>
-      <c r="L28" s="6" t="inlineStr"/>
-      <c r="M28" s="6" t="inlineStr"/>
-      <c r="N28" s="6" t="inlineStr"/>
-      <c r="O28" s="6" t="inlineStr"/>
-      <c r="P28" s="6" t="inlineStr">
+      <c r="J30" s="19" t="inlineStr"/>
+      <c r="K30" s="19" t="inlineStr"/>
+      <c r="L30" s="19" t="inlineStr"/>
+      <c r="M30" s="19" t="inlineStr"/>
+      <c r="N30" s="19" t="inlineStr"/>
+      <c r="O30" s="19" t="inlineStr"/>
+      <c r="P30" s="19" t="inlineStr">
         <is>
           <t>.github/workflows/workflow_report.yml</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="Q30" s="19" t="n">
         <v>24027587697</v>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R30" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S28" s="6" t="inlineStr">
+      <c r="S30" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:01:04Z</t>
+        </is>
+      </c>
+      <c r="T30" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T28" s="7" t="inlineStr">
+      <c r="U30" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="U28" s="6" t="inlineStr">
+      <c r="V30" s="19" t="inlineStr">
         <is>
           <t>Failure (see logs)</t>
         </is>
       </c>
-      <c r="V28" s="6" t="inlineStr"/>
-      <c r="W28" s="6" t="inlineStr"/>
-      <c r="X28" s="6" t="inlineStr">
+      <c r="W30" s="19" t="inlineStr"/>
+      <c r="X30" s="19" t="inlineStr"/>
+      <c r="Y30" s="19" t="inlineStr">
         <is>
           <t>See GitHub Actions logs</t>
         </is>
       </c>
-      <c r="Y28" s="6" t="inlineStr">
+      <c r="Z30" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>8eaab42012c4f02192c65cf59561b5c261b2cf90</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>Create github_workflow_report.py</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
         <is>
           <t>2026-04-06T09:50:41Z</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I31" s="16" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr"/>
-      <c r="P29" s="3" t="inlineStr"/>
-      <c r="Q29" s="3" t="inlineStr"/>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr"/>
-      <c r="T29" s="3" t="inlineStr"/>
-      <c r="U29" s="3" t="inlineStr"/>
-      <c r="V29" s="3" t="inlineStr"/>
-      <c r="W29" s="3" t="inlineStr"/>
-      <c r="X29" s="3" t="inlineStr"/>
-      <c r="Y29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="J31" s="16" t="inlineStr"/>
+      <c r="K31" s="16" t="inlineStr"/>
+      <c r="L31" s="16" t="inlineStr"/>
+      <c r="M31" s="16" t="inlineStr"/>
+      <c r="N31" s="16" t="inlineStr"/>
+      <c r="O31" s="16" t="inlineStr"/>
+      <c r="P31" s="16" t="inlineStr"/>
+      <c r="Q31" s="16" t="inlineStr"/>
+      <c r="R31" s="16" t="inlineStr"/>
+      <c r="S31" s="16" t="inlineStr"/>
+      <c r="T31" s="16" t="inlineStr"/>
+      <c r="U31" s="16" t="inlineStr"/>
+      <c r="V31" s="16" t="inlineStr"/>
+      <c r="W31" s="16" t="inlineStr"/>
+      <c r="X31" s="16" t="inlineStr"/>
+      <c r="Y31" s="16" t="inlineStr"/>
+      <c r="Z31" s="16" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>a9e73f5e7cd8ea7da7f4969f80034915cc9f302c</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="15" t="inlineStr">
         <is>
           <t>Initial commit</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
         <is>
           <t>2026-04-06T09:48:37Z</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I32" s="15" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
-      <c r="V30" s="2" t="inlineStr"/>
-      <c r="W30" s="2" t="inlineStr"/>
-      <c r="X30" s="2" t="inlineStr"/>
-      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="J32" s="15" t="inlineStr"/>
+      <c r="K32" s="15" t="inlineStr"/>
+      <c r="L32" s="15" t="inlineStr"/>
+      <c r="M32" s="15" t="inlineStr"/>
+      <c r="N32" s="15" t="inlineStr"/>
+      <c r="O32" s="15" t="inlineStr"/>
+      <c r="P32" s="15" t="inlineStr"/>
+      <c r="Q32" s="15" t="inlineStr"/>
+      <c r="R32" s="15" t="inlineStr"/>
+      <c r="S32" s="15" t="inlineStr"/>
+      <c r="T32" s="15" t="inlineStr"/>
+      <c r="U32" s="15" t="inlineStr"/>
+      <c r="V32" s="15" t="inlineStr"/>
+      <c r="W32" s="15" t="inlineStr"/>
+      <c r="X32" s="15" t="inlineStr"/>
+      <c r="Y32" s="15" t="inlineStr"/>
+      <c r="Z32" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y30"/>
+  <autoFilter ref="A1:Z32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00375623"/>
@@ -3279,38 +3815,38 @@
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>User/Team Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Permission Level</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>Has Admin</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>Has Delete Access</t>
         </is>
@@ -3321,14 +3857,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009C0006"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3336,975 +3872,1056 @@
     <col width="39" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="62" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="62" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="62" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Workflow Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>Workflow Run ID</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Trigger Event</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>Run Started At</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>Workflow Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>Workflow Conclusion</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="14" t="inlineStr">
         <is>
           <t>Failure Reason</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="14" t="inlineStr">
         <is>
           <t>Failed Job</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="14" t="inlineStr">
         <is>
           <t>Failed Step</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="14" t="inlineStr">
         <is>
           <t>Error Line</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="14" t="inlineStr">
         <is>
           <t>Suggested Fix</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="19" t="n">
         <v>24030846379</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>workflow_dispatch</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T11:55:45Z</t>
+        </is>
+      </c>
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="I2" s="19" t="inlineStr">
         <is>
           <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="J2" s="19" t="inlineStr">
         <is>
           <t>generate_report</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="K2" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Activity Report</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="L2" s="19" t="inlineStr">
         <is>
           <t>Line 56</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="M2" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="19" t="n">
         <v>24030820444</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T11:54:51Z</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>generate_report</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Activity Report</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>Line 55</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="19" t="n">
         <v>24029078530</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:52:49Z</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>generate_report</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>Set up job</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>Line 52</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="19" t="n">
         <v>24028853853</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:44:47Z</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="K5" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="L5" s="19" t="inlineStr">
         <is>
           <t>Line 45</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>Auth/permission error — check that GH_PAT has the required scopes and that repository secrets are correctly configured.</t>
+      <c r="M5" s="19" t="inlineStr">
+        <is>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="19" t="n">
         <v>24028486557</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:39:17Z</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="I6" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="J6" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="K6" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="L6" s="19" t="inlineStr">
         <is>
           <t>Line 39</t>
         </is>
       </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="M6" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="19" t="n">
         <v>24028398959</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:29:06Z</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="K7" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="L7" s="19" t="inlineStr">
         <is>
           <t>Line 29</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>Auth/permission error — check that GH_PAT has the required scopes and that repository secrets are correctly configured.</t>
+      <c r="M7" s="19" t="inlineStr">
+        <is>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="19" t="n">
         <v>24028208740</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:22:38Z</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="J8" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="K8" s="19" t="inlineStr">
         <is>
           <t>Install dependencies</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="L8" s="19" t="inlineStr">
         <is>
           <t>Line 22</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr">
+      <c r="M8" s="19" t="inlineStr">
         <is>
           <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="19" t="n">
         <v>24028171694</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:21:19Z</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="K9" s="19" t="inlineStr">
         <is>
           <t>Install dependencies</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr">
+      <c r="L9" s="19" t="inlineStr">
         <is>
           <t>Line 21</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="M9" s="19" t="inlineStr">
         <is>
           <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="19" t="n">
         <v>24027807973</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:08:40Z</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="J10" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="K10" s="19" t="inlineStr">
         <is>
           <t>Install dependencies</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="L10" s="19" t="inlineStr">
         <is>
           <t>Line 08</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="M10" s="19" t="inlineStr">
         <is>
           <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="19" t="n">
         <v>24027735534</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:06:01Z</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="K11" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="L11" s="19" t="inlineStr">
         <is>
           <t>Line 06</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="M11" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="19" t="n">
         <v>24027729636</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:05:49Z</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="J12" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="K12" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <t>Line 06</t>
         </is>
       </c>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="M12" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="19" t="n">
         <v>24027694141</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:04:36Z</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="J13" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="K13" s="19" t="inlineStr">
         <is>
           <t>Set up job</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="L13" s="19" t="inlineStr">
         <is>
           <t>Line 04</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="M13" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="19" t="n">
         <v>24027689526</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:04:27Z</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="I14" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="J14" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="K14" s="19" t="inlineStr">
         <is>
           <t>Set up job</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr">
+      <c r="L14" s="19" t="inlineStr">
         <is>
           <t>Line 04</t>
         </is>
       </c>
-      <c r="L14" s="6" t="inlineStr">
+      <c r="M14" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>.github/workflows/workflow_report.yml</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="19" t="n">
         <v>24027621196</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:02:12Z</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="I15" s="19" t="inlineStr">
         <is>
           <t>Failure (see logs)</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="J15" s="19" t="inlineStr"/>
+      <c r="K15" s="19" t="inlineStr"/>
+      <c r="L15" s="19" t="inlineStr">
         <is>
           <t>See GitHub Actions logs</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr">
+      <c r="M15" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>.github/workflows/workflow_report.yml</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="19" t="n">
         <v>24027587697</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:01:04Z</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="I16" s="19" t="inlineStr">
         <is>
           <t>Failure (see logs)</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr"/>
-      <c r="J16" s="6" t="inlineStr"/>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="J16" s="19" t="inlineStr"/>
+      <c r="K16" s="19" t="inlineStr"/>
+      <c r="L16" s="19" t="inlineStr">
         <is>
           <t>See GitHub Actions logs</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="M16" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L16"/>
+  <autoFilter ref="A1:M16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00FF0000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4313,949 +4930,1030 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="62" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="62" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="62" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>⚠   15 WORKFLOW FAILURE(S) DETECTED</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Generated: 2026-04-10 14:39 UTC</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Generated: 2026-04-10 15:17 UTC  |  GitHub Activity &amp; Workflow Audit Report</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t>Workflow Name</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t>Run ID</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="23" t="inlineStr">
+        <is>
+          <t>Run Started At</t>
+        </is>
+      </c>
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t>Conclusion</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="I3" s="23" t="inlineStr">
         <is>
           <t>Failure Reason</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t>Failed Job</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="K3" s="23" t="inlineStr">
         <is>
           <t>Failed Step</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t>Error Line</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="M3" s="23" t="inlineStr">
         <is>
           <t>Suggested Fix</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="24" t="n">
         <v>24030846379</v>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>workflow_dispatch</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-06T11:55:45Z</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="J4" s="24" t="inlineStr">
         <is>
           <t>generate_report</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="K4" s="24" t="inlineStr">
         <is>
           <t>Run GitHub Activity Report</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="L4" s="24" t="inlineStr">
         <is>
           <t>Line 56</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="M4" s="24" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="19" t="n">
         <v>24030820444</v>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T11:54:51Z</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>generate_report</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="K5" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Activity Report</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr">
+      <c r="L5" s="19" t="inlineStr">
         <is>
           <t>Line 55</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="M5" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="24" t="n">
         <v>24029078530</v>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:52:49Z</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="J6" s="24" t="inlineStr">
         <is>
           <t>generate_report</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t>Set up job</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="L6" s="24" t="inlineStr">
         <is>
           <t>Line 52</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="M6" s="24" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="A7" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="19" t="n">
         <v>24028853853</v>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:44:47Z</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="K7" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr">
+      <c r="L7" s="19" t="inlineStr">
         <is>
           <t>Line 45</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>Auth/permission error — check that GH_PAT has the required scopes and that repository secrets are correctly configured.</t>
+      <c r="M7" s="19" t="inlineStr">
+        <is>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="24" t="n">
         <v>24028486557</v>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:39:17Z</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="J8" s="24" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="K8" s="24" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="L8" s="24" t="inlineStr">
         <is>
           <t>Line 39</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="M8" s="24" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="19" t="n">
         <v>24028398959</v>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:29:06Z</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="K9" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K9" s="12" t="inlineStr">
+      <c r="L9" s="19" t="inlineStr">
         <is>
           <t>Line 29</t>
         </is>
       </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>Auth/permission error — check that GH_PAT has the required scopes and that repository secrets are correctly configured.</t>
+      <c r="M9" s="19" t="inlineStr">
+        <is>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="24" t="n">
         <v>24028208740</v>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:22:38Z</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="24" t="inlineStr">
         <is>
           <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="24" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="24" t="inlineStr">
         <is>
           <t>Install dependencies</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="24" t="inlineStr">
         <is>
           <t>Line 22</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="24" t="inlineStr">
         <is>
           <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="19" t="n">
         <v>24028171694</v>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:21:19Z</t>
+        </is>
+      </c>
+      <c r="H11" s="19" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="K11" s="19" t="inlineStr">
         <is>
           <t>Install dependencies</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr">
+      <c r="L11" s="19" t="inlineStr">
         <is>
           <t>Line 21</t>
         </is>
       </c>
-      <c r="L11" s="12" t="inlineStr">
+      <c r="M11" s="19" t="inlineStr">
         <is>
           <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="24" t="n">
         <v>24027807973</v>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:08:40Z</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="J12" s="24" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="K12" s="24" t="inlineStr">
         <is>
           <t>Install dependencies</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="L12" s="24" t="inlineStr">
         <is>
           <t>Line 08</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="M12" s="24" t="inlineStr">
         <is>
           <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="19" t="n">
         <v>24027735534</v>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:06:01Z</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="J13" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="K13" s="19" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr">
+      <c r="L13" s="19" t="inlineStr">
         <is>
           <t>Line 06</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
+      <c r="M13" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="24" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="24" t="n">
         <v>24027729636</v>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:05:49Z</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="J14" s="24" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="K14" s="24" t="inlineStr">
         <is>
           <t>Run GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="L14" s="24" t="inlineStr">
         <is>
           <t>Line 06</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="M14" s="24" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="19" t="n">
         <v>24027694141</v>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:04:36Z</t>
+        </is>
+      </c>
+      <c r="H15" s="19" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="I15" s="19" t="inlineStr">
         <is>
           <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="J15" s="19" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="K15" s="19" t="inlineStr">
         <is>
           <t>Set up job</t>
         </is>
       </c>
-      <c r="K15" s="12" t="inlineStr">
+      <c r="L15" s="19" t="inlineStr">
         <is>
           <t>Line 04</t>
         </is>
       </c>
-      <c r="L15" s="12" t="inlineStr">
+      <c r="M15" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="24" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>GitHub Workflow Report</t>
         </is>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="24" t="n">
         <v>24027689526</v>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:04:27Z</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="J16" s="24" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="K16" s="24" t="inlineStr">
         <is>
           <t>Set up job</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="L16" s="24" t="inlineStr">
         <is>
           <t>Line 04</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="M16" s="24" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>.github/workflows/workflow_report.yml</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="19" t="n">
         <v>24027621196</v>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:02:12Z</t>
+        </is>
+      </c>
+      <c r="H17" s="19" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="I17" s="19" t="inlineStr">
         <is>
           <t>Failure (see logs)</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr"/>
-      <c r="K17" s="12" t="inlineStr">
+      <c r="J17" s="19" t="inlineStr"/>
+      <c r="K17" s="19" t="inlineStr"/>
+      <c r="L17" s="19" t="inlineStr">
         <is>
           <t>See GitHub Actions logs</t>
         </is>
       </c>
-      <c r="L17" s="12" t="inlineStr">
+      <c r="M17" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>.github/workflows/workflow_report.yml</t>
         </is>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="24" t="n">
         <v>24027587697</v>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:01:04Z</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>Failure (see logs)</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr"/>
-      <c r="J18" s="11" t="inlineStr"/>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="J18" s="24" t="inlineStr"/>
+      <c r="K18" s="24" t="inlineStr"/>
+      <c r="L18" s="24" t="inlineStr">
         <is>
           <t>See GitHub Actions logs</t>
         </is>
       </c>
-      <c r="L18" s="11" t="inlineStr">
+      <c r="M18" s="24" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L18"/>
+  <autoFilter ref="A3:M18"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_activity_report.xlsx
+++ b/github_activity_report.xlsx
@@ -14,9 +14,9 @@
     <sheet name="Failure Alerts" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Activity'!$A$1:$Z$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failure Summary'!$A$1:$M$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Failure Alerts'!$A$3:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Activity'!$A$1:$Z$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failure Summary'!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Failure Alerts'!$A$3:$M$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -202,13 +202,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -618,7 +618,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10 15:17 UTC</t>
+          <t>2026-04-10 16:37 UTC</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -817,7 +817,7 @@
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="62" customWidth="1" min="22" max="22"/>
     <col width="17" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
+    <col width="38" customWidth="1" min="24" max="24"/>
     <col width="25" customWidth="1" min="25" max="25"/>
     <col width="62" customWidth="1" min="26" max="26"/>
   </cols>
@@ -977,12 +977,12 @@
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>0bf36a490d78a4819928a11161d34bda33e4f337</t>
+          <t>93bdf4123cc644f621cecd131589bff39d5376fe</t>
         </is>
       </c>
       <c r="F2" s="15" t="inlineStr">
         <is>
-          <t>test-200</t>
+          <t>test-249</t>
         </is>
       </c>
       <c r="G2" s="15" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="H2" s="15" t="inlineStr">
         <is>
-          <t>2026-04-10T15:16:43Z</t>
+          <t>2026-04-10T16:36:38Z</t>
         </is>
       </c>
       <c r="I2" s="15" t="inlineStr">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="Q2" s="15" t="n">
-        <v>24250086438</v>
+        <v>24253439879</v>
       </c>
       <c r="R2" s="15" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="S2" s="15" t="inlineStr">
         <is>
-          <t>2026-04-10T15:17:09Z</t>
+          <t>2026-04-10T16:36:56Z</t>
         </is>
       </c>
       <c r="T2" s="15" t="inlineStr">
@@ -1059,22 +1059,22 @@
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>4744a63d54822fd75d284791aa8b6524acb33646</t>
+          <t>b3ea79ed073ed633f20c5321bc134cc65896c901</t>
         </is>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>chore: update activity report [2026-04-10 14:39 UTC] via push (run 24248391662)</t>
+          <t>test-209</t>
         </is>
       </c>
       <c r="G3" s="16" t="inlineStr">
         <is>
-          <t>github-actions[bot]</t>
+          <t>“Vidyakar”</t>
         </is>
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>2026-04-10T14:39:22Z</t>
+          <t>2026-04-10T16:02:48Z</t>
         </is>
       </c>
       <c r="I3" s="16" t="inlineStr">
@@ -1088,12 +1088,34 @@
       <c r="M3" s="16" t="inlineStr"/>
       <c r="N3" s="16" t="inlineStr"/>
       <c r="O3" s="16" t="inlineStr"/>
-      <c r="P3" s="16" t="inlineStr"/>
-      <c r="Q3" s="16" t="inlineStr"/>
-      <c r="R3" s="16" t="inlineStr"/>
-      <c r="S3" s="16" t="inlineStr"/>
-      <c r="T3" s="16" t="inlineStr"/>
-      <c r="U3" s="16" t="inlineStr"/>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>GitHub Activity Report</t>
+        </is>
+      </c>
+      <c r="Q3" s="16" t="n">
+        <v>24252121271</v>
+      </c>
+      <c r="R3" s="16" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S3" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10T16:04:46Z</t>
+        </is>
+      </c>
+      <c r="T3" s="16" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U3" s="17" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
       <c r="V3" s="16" t="inlineStr"/>
       <c r="W3" s="16" t="inlineStr"/>
       <c r="X3" s="16" t="inlineStr"/>
@@ -1101,1416 +1123,1312 @@
       <c r="Z3" s="16" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>25126c83583917e6acf1c55b3b79659ece2e2368</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>test-201</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10T15:26:42Z</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr"/>
+      <c r="K4" s="16" t="inlineStr"/>
+      <c r="L4" s="16" t="inlineStr"/>
+      <c r="M4" s="16" t="inlineStr"/>
+      <c r="N4" s="16" t="inlineStr"/>
+      <c r="O4" s="16" t="inlineStr"/>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>GitHub Activity Report</t>
+        </is>
+      </c>
+      <c r="Q4" s="16" t="n">
+        <v>24250548345</v>
+      </c>
+      <c r="R4" s="16" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S4" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10T15:27:44Z</t>
+        </is>
+      </c>
+      <c r="T4" s="16" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U4" s="17" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V4" s="16" t="inlineStr"/>
+      <c r="W4" s="16" t="inlineStr"/>
+      <c r="X4" s="16" t="inlineStr"/>
+      <c r="Y4" s="16" t="inlineStr"/>
+      <c r="Z4" s="16" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>9e3c7f0f229aff7c1984cec897ef7c43ff34c5e8</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>chore: update activity report [2026-04-10 15:17 UTC] via push (run 24250086438)</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>github-actions[bot]</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>2026-04-10T15:17:35Z</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr"/>
+      <c r="K5" s="18" t="inlineStr"/>
+      <c r="L5" s="18" t="inlineStr"/>
+      <c r="M5" s="18" t="inlineStr"/>
+      <c r="N5" s="18" t="inlineStr"/>
+      <c r="O5" s="18" t="inlineStr"/>
+      <c r="P5" s="18" t="inlineStr"/>
+      <c r="Q5" s="18" t="inlineStr"/>
+      <c r="R5" s="18" t="inlineStr"/>
+      <c r="S5" s="18" t="inlineStr"/>
+      <c r="T5" s="18" t="inlineStr"/>
+      <c r="U5" s="18" t="inlineStr"/>
+      <c r="V5" s="18" t="inlineStr"/>
+      <c r="W5" s="18" t="inlineStr"/>
+      <c r="X5" s="18" t="inlineStr"/>
+      <c r="Y5" s="18" t="inlineStr"/>
+      <c r="Z5" s="18" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>0bf36a490d78a4819928a11161d34bda33e4f337</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>test-200</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-10T15:16:43Z</t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="inlineStr"/>
+      <c r="K6" s="19" t="inlineStr"/>
+      <c r="L6" s="19" t="inlineStr"/>
+      <c r="M6" s="19" t="inlineStr"/>
+      <c r="N6" s="19" t="inlineStr"/>
+      <c r="O6" s="19" t="inlineStr"/>
+      <c r="P6" s="19" t="inlineStr">
+        <is>
+          <t>GitHub Activity Report</t>
+        </is>
+      </c>
+      <c r="Q6" s="19" t="n">
+        <v>24250086438</v>
+      </c>
+      <c r="R6" s="19" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S6" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-10T15:18:50Z</t>
+        </is>
+      </c>
+      <c r="T6" s="19" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U6" s="20" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="V6" s="19" t="inlineStr">
+        <is>
+          <t>Job 'generate_report' step 'Commit and push report to repository' failed — 2026-04-10T15:19:10.4298620Z 15:19:10  WARNING   WORKFLOW FAILURE in vidyakar-whitedev/git-report  (Run ID: 24030846379)</t>
+        </is>
+      </c>
+      <c r="W6" s="19" t="inlineStr">
+        <is>
+          <t>generate_report</t>
+        </is>
+      </c>
+      <c r="X6" s="19" t="inlineStr">
+        <is>
+          <t>Commit and push report to repository</t>
+        </is>
+      </c>
+      <c r="Y6" s="19" t="inlineStr">
+        <is>
+          <t>Line 19</t>
+        </is>
+      </c>
+      <c r="Z6" s="19" t="inlineStr">
+        <is>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>4744a63d54822fd75d284791aa8b6524acb33646</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>chore: update activity report [2026-04-10 14:39 UTC] via push (run 24248391662)</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>github-actions[bot]</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>2026-04-10T14:39:22Z</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr"/>
+      <c r="K7" s="18" t="inlineStr"/>
+      <c r="L7" s="18" t="inlineStr"/>
+      <c r="M7" s="18" t="inlineStr"/>
+      <c r="N7" s="18" t="inlineStr"/>
+      <c r="O7" s="18" t="inlineStr"/>
+      <c r="P7" s="18" t="inlineStr"/>
+      <c r="Q7" s="18" t="inlineStr"/>
+      <c r="R7" s="18" t="inlineStr"/>
+      <c r="S7" s="18" t="inlineStr"/>
+      <c r="T7" s="18" t="inlineStr"/>
+      <c r="U7" s="18" t="inlineStr"/>
+      <c r="V7" s="18" t="inlineStr"/>
+      <c r="W7" s="18" t="inlineStr"/>
+      <c r="X7" s="18" t="inlineStr"/>
+      <c r="Y7" s="18" t="inlineStr"/>
+      <c r="Z7" s="18" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>408ddd043c24815f4498a813c6ca81c4e9688b9b</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>test-198</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T14:38:25Z</t>
         </is>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr"/>
-      <c r="K4" s="17" t="inlineStr"/>
-      <c r="L4" s="17" t="inlineStr"/>
-      <c r="M4" s="17" t="inlineStr"/>
-      <c r="N4" s="17" t="inlineStr"/>
-      <c r="O4" s="17" t="inlineStr"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr"/>
+      <c r="K8" s="16" t="inlineStr"/>
+      <c r="L8" s="16" t="inlineStr"/>
+      <c r="M8" s="16" t="inlineStr"/>
+      <c r="N8" s="16" t="inlineStr"/>
+      <c r="O8" s="16" t="inlineStr"/>
+      <c r="P8" s="16" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q4" s="17" t="n">
+      <c r="Q8" s="16" t="n">
         <v>24248391662</v>
       </c>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="R8" s="16" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S4" s="17" t="inlineStr">
+      <c r="S8" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T14:38:48Z</t>
         </is>
       </c>
-      <c r="T4" s="17" t="inlineStr">
+      <c r="T8" s="16" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U4" s="18" t="inlineStr">
+      <c r="U8" s="17" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V4" s="17" t="inlineStr"/>
-      <c r="W4" s="17" t="inlineStr"/>
-      <c r="X4" s="17" t="inlineStr"/>
-      <c r="Y4" s="17" t="inlineStr"/>
-      <c r="Z4" s="17" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="V8" s="16" t="inlineStr"/>
+      <c r="W8" s="16" t="inlineStr"/>
+      <c r="X8" s="16" t="inlineStr"/>
+      <c r="Y8" s="16" t="inlineStr"/>
+      <c r="Z8" s="16" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>37f60b0c23d45eef199630a384945ef73970b8d7</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>chore: update activity report [2026-04-10 09:44 UTC] via push (run 24236872105)</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>github-actions[bot]</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>2026-04-10T09:44:03Z</t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr"/>
-      <c r="K5" s="16" t="inlineStr"/>
-      <c r="L5" s="16" t="inlineStr"/>
-      <c r="M5" s="16" t="inlineStr"/>
-      <c r="N5" s="16" t="inlineStr"/>
-      <c r="O5" s="16" t="inlineStr"/>
-      <c r="P5" s="16" t="inlineStr"/>
-      <c r="Q5" s="16" t="inlineStr"/>
-      <c r="R5" s="16" t="inlineStr"/>
-      <c r="S5" s="16" t="inlineStr"/>
-      <c r="T5" s="16" t="inlineStr"/>
-      <c r="U5" s="16" t="inlineStr"/>
-      <c r="V5" s="16" t="inlineStr"/>
-      <c r="W5" s="16" t="inlineStr"/>
-      <c r="X5" s="16" t="inlineStr"/>
-      <c r="Y5" s="16" t="inlineStr"/>
-      <c r="Z5" s="16" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr"/>
+      <c r="K9" s="18" t="inlineStr"/>
+      <c r="L9" s="18" t="inlineStr"/>
+      <c r="M9" s="18" t="inlineStr"/>
+      <c r="N9" s="18" t="inlineStr"/>
+      <c r="O9" s="18" t="inlineStr"/>
+      <c r="P9" s="18" t="inlineStr"/>
+      <c r="Q9" s="18" t="inlineStr"/>
+      <c r="R9" s="18" t="inlineStr"/>
+      <c r="S9" s="18" t="inlineStr"/>
+      <c r="T9" s="18" t="inlineStr"/>
+      <c r="U9" s="18" t="inlineStr"/>
+      <c r="V9" s="18" t="inlineStr"/>
+      <c r="W9" s="18" t="inlineStr"/>
+      <c r="X9" s="18" t="inlineStr"/>
+      <c r="Y9" s="18" t="inlineStr"/>
+      <c r="Z9" s="18" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>aac0b4a033d6b371042ec3f99a213aa53e5d925f</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>test-198</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H10" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T09:40:50Z</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr"/>
-      <c r="K6" s="17" t="inlineStr"/>
-      <c r="L6" s="17" t="inlineStr"/>
-      <c r="M6" s="17" t="inlineStr"/>
-      <c r="N6" s="17" t="inlineStr"/>
-      <c r="O6" s="17" t="inlineStr"/>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr"/>
+      <c r="K10" s="16" t="inlineStr"/>
+      <c r="L10" s="16" t="inlineStr"/>
+      <c r="M10" s="16" t="inlineStr"/>
+      <c r="N10" s="16" t="inlineStr"/>
+      <c r="O10" s="16" t="inlineStr"/>
+      <c r="P10" s="16" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q6" s="17" t="n">
+      <c r="Q10" s="16" t="n">
         <v>24236872105</v>
       </c>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="R10" s="16" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S6" s="17" t="inlineStr">
+      <c r="S10" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T09:43:38Z</t>
         </is>
       </c>
-      <c r="T6" s="17" t="inlineStr">
+      <c r="T10" s="16" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U6" s="18" t="inlineStr">
+      <c r="U10" s="17" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V6" s="17" t="inlineStr"/>
-      <c r="W6" s="17" t="inlineStr"/>
-      <c r="X6" s="17" t="inlineStr"/>
-      <c r="Y6" s="17" t="inlineStr"/>
-      <c r="Z6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="V10" s="16" t="inlineStr"/>
+      <c r="W10" s="16" t="inlineStr"/>
+      <c r="X10" s="16" t="inlineStr"/>
+      <c r="Y10" s="16" t="inlineStr"/>
+      <c r="Z10" s="16" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>19b0e6e1eadc37093a80d5aa3b43d47cf52cc739</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>chore: update activity report [2026-04-10 09:36 UTC] via push (run 24236579665)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>github-actions[bot]</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H11" s="18" t="inlineStr">
         <is>
           <t>2026-04-10T09:36:36Z</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr"/>
-      <c r="K7" s="16" t="inlineStr"/>
-      <c r="L7" s="16" t="inlineStr"/>
-      <c r="M7" s="16" t="inlineStr"/>
-      <c r="N7" s="16" t="inlineStr"/>
-      <c r="O7" s="16" t="inlineStr"/>
-      <c r="P7" s="16" t="inlineStr"/>
-      <c r="Q7" s="16" t="inlineStr"/>
-      <c r="R7" s="16" t="inlineStr"/>
-      <c r="S7" s="16" t="inlineStr"/>
-      <c r="T7" s="16" t="inlineStr"/>
-      <c r="U7" s="16" t="inlineStr"/>
-      <c r="V7" s="16" t="inlineStr"/>
-      <c r="W7" s="16" t="inlineStr"/>
-      <c r="X7" s="16" t="inlineStr"/>
-      <c r="Y7" s="16" t="inlineStr"/>
-      <c r="Z7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr"/>
+      <c r="K11" s="18" t="inlineStr"/>
+      <c r="L11" s="18" t="inlineStr"/>
+      <c r="M11" s="18" t="inlineStr"/>
+      <c r="N11" s="18" t="inlineStr"/>
+      <c r="O11" s="18" t="inlineStr"/>
+      <c r="P11" s="18" t="inlineStr"/>
+      <c r="Q11" s="18" t="inlineStr"/>
+      <c r="R11" s="18" t="inlineStr"/>
+      <c r="S11" s="18" t="inlineStr"/>
+      <c r="T11" s="18" t="inlineStr"/>
+      <c r="U11" s="18" t="inlineStr"/>
+      <c r="V11" s="18" t="inlineStr"/>
+      <c r="W11" s="18" t="inlineStr"/>
+      <c r="X11" s="18" t="inlineStr"/>
+      <c r="Y11" s="18" t="inlineStr"/>
+      <c r="Z11" s="18" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>4246e5f5bdd0c663224514d45c37457253e6806b</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>test-13</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T09:35:54Z</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr"/>
-      <c r="K8" s="17" t="inlineStr"/>
-      <c r="L8" s="17" t="inlineStr"/>
-      <c r="M8" s="17" t="inlineStr"/>
-      <c r="N8" s="17" t="inlineStr"/>
-      <c r="O8" s="17" t="inlineStr"/>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr"/>
+      <c r="K12" s="16" t="inlineStr"/>
+      <c r="L12" s="16" t="inlineStr"/>
+      <c r="M12" s="16" t="inlineStr"/>
+      <c r="N12" s="16" t="inlineStr"/>
+      <c r="O12" s="16" t="inlineStr"/>
+      <c r="P12" s="16" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q8" s="17" t="n">
+      <c r="Q12" s="16" t="n">
         <v>24236579665</v>
       </c>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="R12" s="16" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S8" s="17" t="inlineStr">
+      <c r="S12" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T09:36:01Z</t>
         </is>
       </c>
-      <c r="T8" s="17" t="inlineStr">
+      <c r="T12" s="16" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U8" s="18" t="inlineStr">
+      <c r="U12" s="17" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V8" s="17" t="inlineStr"/>
-      <c r="W8" s="17" t="inlineStr"/>
-      <c r="X8" s="17" t="inlineStr"/>
-      <c r="Y8" s="17" t="inlineStr"/>
-      <c r="Z8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="V12" s="16" t="inlineStr"/>
+      <c r="W12" s="16" t="inlineStr"/>
+      <c r="X12" s="16" t="inlineStr"/>
+      <c r="Y12" s="16" t="inlineStr"/>
+      <c r="Z12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>ff12234265b7ed9747283a1b59735ea5ddda19b5</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>test-12</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T09:21:24Z</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr"/>
-      <c r="K9" s="17" t="inlineStr"/>
-      <c r="L9" s="17" t="inlineStr"/>
-      <c r="M9" s="17" t="inlineStr"/>
-      <c r="N9" s="17" t="inlineStr"/>
-      <c r="O9" s="17" t="inlineStr"/>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr"/>
+      <c r="K13" s="16" t="inlineStr"/>
+      <c r="L13" s="16" t="inlineStr"/>
+      <c r="M13" s="16" t="inlineStr"/>
+      <c r="N13" s="16" t="inlineStr"/>
+      <c r="O13" s="16" t="inlineStr"/>
+      <c r="P13" s="16" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q9" s="17" t="n">
+      <c r="Q13" s="16" t="n">
         <v>24236015736</v>
       </c>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="R13" s="16" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S9" s="17" t="inlineStr">
+      <c r="S13" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T09:21:36Z</t>
         </is>
       </c>
-      <c r="T9" s="17" t="inlineStr">
+      <c r="T13" s="16" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U9" s="18" t="inlineStr">
+      <c r="U13" s="17" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V9" s="17" t="inlineStr"/>
-      <c r="W9" s="17" t="inlineStr"/>
-      <c r="X9" s="17" t="inlineStr"/>
-      <c r="Y9" s="17" t="inlineStr"/>
-      <c r="Z9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="V13" s="16" t="inlineStr"/>
+      <c r="W13" s="16" t="inlineStr"/>
+      <c r="X13" s="16" t="inlineStr"/>
+      <c r="Y13" s="16" t="inlineStr"/>
+      <c r="Z13" s="16" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>75732834dd766afc090c808510eb71c7693015dd</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>test-8</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T08:35:13Z</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr"/>
-      <c r="K10" s="17" t="inlineStr"/>
-      <c r="L10" s="17" t="inlineStr"/>
-      <c r="M10" s="17" t="inlineStr"/>
-      <c r="N10" s="17" t="inlineStr"/>
-      <c r="O10" s="17" t="inlineStr"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="J14" s="16" t="inlineStr"/>
+      <c r="K14" s="16" t="inlineStr"/>
+      <c r="L14" s="16" t="inlineStr"/>
+      <c r="M14" s="16" t="inlineStr"/>
+      <c r="N14" s="16" t="inlineStr"/>
+      <c r="O14" s="16" t="inlineStr"/>
+      <c r="P14" s="16" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q10" s="17" t="n">
+      <c r="Q14" s="16" t="n">
         <v>24234243976</v>
       </c>
-      <c r="R10" s="17" t="inlineStr">
+      <c r="R14" s="16" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S10" s="17" t="inlineStr">
+      <c r="S14" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T08:35:20Z</t>
         </is>
       </c>
-      <c r="T10" s="17" t="inlineStr">
+      <c r="T14" s="16" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U10" s="18" t="inlineStr">
+      <c r="U14" s="17" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V10" s="17" t="inlineStr"/>
-      <c r="W10" s="17" t="inlineStr"/>
-      <c r="X10" s="17" t="inlineStr"/>
-      <c r="Y10" s="17" t="inlineStr"/>
-      <c r="Z10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="V14" s="16" t="inlineStr"/>
+      <c r="W14" s="16" t="inlineStr"/>
+      <c r="X14" s="16" t="inlineStr"/>
+      <c r="Y14" s="16" t="inlineStr"/>
+      <c r="Z14" s="16" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>9d220c5657c48c13ca17102c507b756edbba9215</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>test-8</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T08:32:22Z</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr"/>
-      <c r="K11" s="17" t="inlineStr"/>
-      <c r="L11" s="17" t="inlineStr"/>
-      <c r="M11" s="17" t="inlineStr"/>
-      <c r="N11" s="17" t="inlineStr"/>
-      <c r="O11" s="17" t="inlineStr"/>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="J15" s="16" t="inlineStr"/>
+      <c r="K15" s="16" t="inlineStr"/>
+      <c r="L15" s="16" t="inlineStr"/>
+      <c r="M15" s="16" t="inlineStr"/>
+      <c r="N15" s="16" t="inlineStr"/>
+      <c r="O15" s="16" t="inlineStr"/>
+      <c r="P15" s="16" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q11" s="17" t="n">
+      <c r="Q15" s="16" t="n">
         <v>24234135440</v>
       </c>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="R15" s="16" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S11" s="17" t="inlineStr">
+      <c r="S15" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T08:32:30Z</t>
         </is>
       </c>
-      <c r="T11" s="17" t="inlineStr">
+      <c r="T15" s="16" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U11" s="18" t="inlineStr">
+      <c r="U15" s="17" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V11" s="17" t="inlineStr"/>
-      <c r="W11" s="17" t="inlineStr"/>
-      <c r="X11" s="17" t="inlineStr"/>
-      <c r="Y11" s="17" t="inlineStr"/>
-      <c r="Z11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="V15" s="16" t="inlineStr"/>
+      <c r="W15" s="16" t="inlineStr"/>
+      <c r="X15" s="16" t="inlineStr"/>
+      <c r="Y15" s="16" t="inlineStr"/>
+      <c r="Z15" s="16" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>981fe60621c98393750f79dd815a0ea7e4aed75e</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>test-8</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T08:27:06Z</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr"/>
-      <c r="K12" s="17" t="inlineStr"/>
-      <c r="L12" s="17" t="inlineStr"/>
-      <c r="M12" s="17" t="inlineStr"/>
-      <c r="N12" s="17" t="inlineStr"/>
-      <c r="O12" s="17" t="inlineStr"/>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="J16" s="16" t="inlineStr"/>
+      <c r="K16" s="16" t="inlineStr"/>
+      <c r="L16" s="16" t="inlineStr"/>
+      <c r="M16" s="16" t="inlineStr"/>
+      <c r="N16" s="16" t="inlineStr"/>
+      <c r="O16" s="16" t="inlineStr"/>
+      <c r="P16" s="16" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q12" s="17" t="n">
+      <c r="Q16" s="16" t="n">
         <v>24233936358</v>
       </c>
-      <c r="R12" s="17" t="inlineStr">
+      <c r="R16" s="16" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S12" s="17" t="inlineStr">
+      <c r="S16" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T08:27:14Z</t>
         </is>
       </c>
-      <c r="T12" s="17" t="inlineStr">
+      <c r="T16" s="16" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U12" s="18" t="inlineStr">
+      <c r="U16" s="17" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V12" s="17" t="inlineStr"/>
-      <c r="W12" s="17" t="inlineStr"/>
-      <c r="X12" s="17" t="inlineStr"/>
-      <c r="Y12" s="17" t="inlineStr"/>
-      <c r="Z12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="V16" s="16" t="inlineStr"/>
+      <c r="W16" s="16" t="inlineStr"/>
+      <c r="X16" s="16" t="inlineStr"/>
+      <c r="Y16" s="16" t="inlineStr"/>
+      <c r="Z16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>3cfdf96375ed8ea8c83b95f26b9c87428b8bc8b9</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>test-1</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T08:18:15Z</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr"/>
-      <c r="K13" s="17" t="inlineStr"/>
-      <c r="L13" s="17" t="inlineStr"/>
-      <c r="M13" s="17" t="inlineStr"/>
-      <c r="N13" s="17" t="inlineStr"/>
-      <c r="O13" s="17" t="inlineStr"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="J17" s="16" t="inlineStr"/>
+      <c r="K17" s="16" t="inlineStr"/>
+      <c r="L17" s="16" t="inlineStr"/>
+      <c r="M17" s="16" t="inlineStr"/>
+      <c r="N17" s="16" t="inlineStr"/>
+      <c r="O17" s="16" t="inlineStr"/>
+      <c r="P17" s="16" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q13" s="17" t="n">
+      <c r="Q17" s="16" t="n">
         <v>24233616319</v>
       </c>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="R17" s="16" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S13" s="17" t="inlineStr">
+      <c r="S17" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T08:18:28Z</t>
         </is>
       </c>
-      <c r="T13" s="17" t="inlineStr">
+      <c r="T17" s="16" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U13" s="18" t="inlineStr">
+      <c r="U17" s="17" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V13" s="17" t="inlineStr"/>
-      <c r="W13" s="17" t="inlineStr"/>
-      <c r="X13" s="17" t="inlineStr"/>
-      <c r="Y13" s="17" t="inlineStr"/>
-      <c r="Z13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="V17" s="16" t="inlineStr"/>
+      <c r="W17" s="16" t="inlineStr"/>
+      <c r="X17" s="16" t="inlineStr"/>
+      <c r="Y17" s="16" t="inlineStr"/>
+      <c r="Z17" s="16" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>ad211e0513d37204ee54168120dec41978cc6fb4</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>new code change</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>2026-04-06T15:32:05Z</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I18" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr"/>
-      <c r="K14" s="17" t="inlineStr"/>
-      <c r="L14" s="17" t="inlineStr"/>
-      <c r="M14" s="17" t="inlineStr"/>
-      <c r="N14" s="17" t="inlineStr"/>
-      <c r="O14" s="17" t="inlineStr"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="J18" s="16" t="inlineStr"/>
+      <c r="K18" s="16" t="inlineStr"/>
+      <c r="L18" s="16" t="inlineStr"/>
+      <c r="M18" s="16" t="inlineStr"/>
+      <c r="N18" s="16" t="inlineStr"/>
+      <c r="O18" s="16" t="inlineStr"/>
+      <c r="P18" s="16" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q14" s="17" t="n">
+      <c r="Q18" s="16" t="n">
         <v>24038137070</v>
       </c>
-      <c r="R14" s="17" t="inlineStr">
+      <c r="R18" s="16" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S14" s="17" t="inlineStr">
+      <c r="S18" s="16" t="inlineStr">
         <is>
           <t>2026-04-06T15:32:18Z</t>
         </is>
       </c>
-      <c r="T14" s="17" t="inlineStr">
+      <c r="T18" s="16" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U14" s="18" t="inlineStr">
+      <c r="U18" s="17" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V14" s="17" t="inlineStr"/>
-      <c r="W14" s="17" t="inlineStr"/>
-      <c r="X14" s="17" t="inlineStr"/>
-      <c r="Y14" s="17" t="inlineStr"/>
-      <c r="Z14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="V18" s="16" t="inlineStr"/>
+      <c r="W18" s="16" t="inlineStr"/>
+      <c r="X18" s="16" t="inlineStr"/>
+      <c r="Y18" s="16" t="inlineStr"/>
+      <c r="Z18" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>21f8e2bcc8765be2c9dd97d0d839686b7afe3de1</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>new code change</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>2026-04-06T12:24:00Z</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I19" s="16" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr"/>
-      <c r="K15" s="17" t="inlineStr"/>
-      <c r="L15" s="17" t="inlineStr"/>
-      <c r="M15" s="17" t="inlineStr"/>
-      <c r="N15" s="17" t="inlineStr"/>
-      <c r="O15" s="17" t="inlineStr"/>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr"/>
+      <c r="K19" s="16" t="inlineStr"/>
+      <c r="L19" s="16" t="inlineStr"/>
+      <c r="M19" s="16" t="inlineStr"/>
+      <c r="N19" s="16" t="inlineStr"/>
+      <c r="O19" s="16" t="inlineStr"/>
+      <c r="P19" s="16" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q15" s="17" t="n">
+      <c r="Q19" s="16" t="n">
         <v>24031673216</v>
       </c>
-      <c r="R15" s="17" t="inlineStr">
+      <c r="R19" s="16" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S15" s="17" t="inlineStr">
+      <c r="S19" s="16" t="inlineStr">
         <is>
           <t>2026-04-06T12:24:13Z</t>
         </is>
       </c>
-      <c r="T15" s="17" t="inlineStr">
+      <c r="T19" s="16" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U15" s="18" t="inlineStr">
+      <c r="U19" s="17" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V15" s="17" t="inlineStr"/>
-      <c r="W15" s="17" t="inlineStr"/>
-      <c r="X15" s="17" t="inlineStr"/>
-      <c r="Y15" s="17" t="inlineStr"/>
-      <c r="Z15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>code changed1</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H16" s="19" t="inlineStr">
-        <is>
-          <t>2026-04-06T11:54:44Z</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
-        <is>
-          <t>git-report-poc2</t>
-        </is>
-      </c>
-      <c r="J16" s="19" t="inlineStr"/>
-      <c r="K16" s="19" t="inlineStr"/>
-      <c r="L16" s="19" t="inlineStr"/>
-      <c r="M16" s="19" t="inlineStr"/>
-      <c r="N16" s="19" t="inlineStr"/>
-      <c r="O16" s="19" t="inlineStr"/>
-      <c r="P16" s="19" t="inlineStr">
-        <is>
-          <t>GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="Q16" s="19" t="n">
-        <v>24030846379</v>
-      </c>
-      <c r="R16" s="19" t="inlineStr">
-        <is>
-          <t>workflow_dispatch</t>
-        </is>
-      </c>
-      <c r="S16" s="19" t="inlineStr">
-        <is>
-          <t>2026-04-06T11:55:45Z</t>
-        </is>
-      </c>
-      <c r="T16" s="19" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="U16" s="20" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="V16" s="19" t="inlineStr">
-        <is>
-          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
-        </is>
-      </c>
-      <c r="W16" s="19" t="inlineStr">
-        <is>
-          <t>generate_report</t>
-        </is>
-      </c>
-      <c r="X16" s="19" t="inlineStr">
-        <is>
-          <t>Run GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Y16" s="19" t="inlineStr">
-        <is>
-          <t>Line 56</t>
-        </is>
-      </c>
-      <c r="Z16" s="19" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>code changed1</t>
-        </is>
-      </c>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H17" s="19" t="inlineStr">
-        <is>
-          <t>2026-04-06T11:54:44Z</t>
-        </is>
-      </c>
-      <c r="I17" s="19" t="inlineStr">
-        <is>
-          <t>git-report-poc2</t>
-        </is>
-      </c>
-      <c r="J17" s="19" t="inlineStr"/>
-      <c r="K17" s="19" t="inlineStr"/>
-      <c r="L17" s="19" t="inlineStr"/>
-      <c r="M17" s="19" t="inlineStr"/>
-      <c r="N17" s="19" t="inlineStr"/>
-      <c r="O17" s="19" t="inlineStr"/>
-      <c r="P17" s="19" t="inlineStr">
-        <is>
-          <t>GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="Q17" s="19" t="n">
-        <v>24030820444</v>
-      </c>
-      <c r="R17" s="19" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S17" s="19" t="inlineStr">
-        <is>
-          <t>2026-04-06T11:54:51Z</t>
-        </is>
-      </c>
-      <c r="T17" s="19" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="U17" s="20" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="V17" s="19" t="inlineStr">
-        <is>
-          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
-        </is>
-      </c>
-      <c r="W17" s="19" t="inlineStr">
-        <is>
-          <t>generate_report</t>
-        </is>
-      </c>
-      <c r="X17" s="19" t="inlineStr">
-        <is>
-          <t>Run GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Y17" s="19" t="inlineStr">
-        <is>
-          <t>Line 55</t>
-        </is>
-      </c>
-      <c r="Z17" s="19" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>733b89967b9b4731953302840f2ddb2c20bedf56</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>code changed</t>
-        </is>
-      </c>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H18" s="19" t="inlineStr">
-        <is>
-          <t>2026-04-06T10:52:40Z</t>
-        </is>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>git-report-poc2</t>
-        </is>
-      </c>
-      <c r="J18" s="19" t="inlineStr"/>
-      <c r="K18" s="19" t="inlineStr"/>
-      <c r="L18" s="19" t="inlineStr"/>
-      <c r="M18" s="19" t="inlineStr"/>
-      <c r="N18" s="19" t="inlineStr"/>
-      <c r="O18" s="19" t="inlineStr"/>
-      <c r="P18" s="19" t="inlineStr">
-        <is>
-          <t>GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="Q18" s="19" t="n">
-        <v>24029078530</v>
-      </c>
-      <c r="R18" s="19" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S18" s="19" t="inlineStr">
-        <is>
-          <t>2026-04-06T10:52:49Z</t>
-        </is>
-      </c>
-      <c r="T18" s="19" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="U18" s="20" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="V18" s="19" t="inlineStr">
-        <is>
-          <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
-        </is>
-      </c>
-      <c r="W18" s="19" t="inlineStr">
-        <is>
-          <t>generate_report</t>
-        </is>
-      </c>
-      <c r="X18" s="19" t="inlineStr">
-        <is>
-          <t>Set up job</t>
-        </is>
-      </c>
-      <c r="Y18" s="19" t="inlineStr">
-        <is>
-          <t>Line 52</t>
-        </is>
-      </c>
-      <c r="Z18" s="19" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>aedf77ebc8e0433ebbe37ca97908ee5caf3929d6</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>code changd</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>2026-04-06T10:44:38Z</t>
-        </is>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>git-report-poc2</t>
-        </is>
-      </c>
-      <c r="J19" s="19" t="inlineStr"/>
-      <c r="K19" s="19" t="inlineStr"/>
-      <c r="L19" s="19" t="inlineStr"/>
-      <c r="M19" s="19" t="inlineStr"/>
-      <c r="N19" s="19" t="inlineStr"/>
-      <c r="O19" s="19" t="inlineStr"/>
-      <c r="P19" s="19" t="inlineStr">
-        <is>
-          <t>GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="Q19" s="19" t="n">
-        <v>24028853853</v>
-      </c>
-      <c r="R19" s="19" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S19" s="19" t="inlineStr">
-        <is>
-          <t>2026-04-06T10:44:47Z</t>
-        </is>
-      </c>
-      <c r="T19" s="19" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="U19" s="20" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="V19" s="19" t="inlineStr">
-        <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
-        </is>
-      </c>
-      <c r="W19" s="19" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="X19" s="19" t="inlineStr">
-        <is>
-          <t>Run GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="Y19" s="19" t="inlineStr">
-        <is>
-          <t>Line 45</t>
-        </is>
-      </c>
-      <c r="Z19" s="19" t="inlineStr">
-        <is>
-          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
-        </is>
-      </c>
+      <c r="V19" s="16" t="inlineStr"/>
+      <c r="W19" s="16" t="inlineStr"/>
+      <c r="X19" s="16" t="inlineStr"/>
+      <c r="Y19" s="16" t="inlineStr"/>
+      <c r="Z19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
@@ -2535,22 +2453,22 @@
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>5feb9eb868fd9ff9e4a7150d13cb3252d843c106</t>
+          <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>Update demo.txt</t>
+          <t>code changed1</t>
         </is>
       </c>
       <c r="G20" s="19" t="inlineStr">
         <is>
-          <t>vidyakar-whitedev</t>
+          <t>“Vidyakar”</t>
         </is>
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:31:56Z</t>
+          <t>2026-04-06T11:54:44Z</t>
         </is>
       </c>
       <c r="I20" s="19" t="inlineStr">
@@ -2570,16 +2488,16 @@
         </is>
       </c>
       <c r="Q20" s="19" t="n">
-        <v>24028486557</v>
+        <v>24030846379</v>
       </c>
       <c r="R20" s="19" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>workflow_dispatch</t>
         </is>
       </c>
       <c r="S20" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:39:17Z</t>
+          <t>2026-04-06T11:55:45Z</t>
         </is>
       </c>
       <c r="T20" s="19" t="inlineStr">
@@ -2594,22 +2512,22 @@
       </c>
       <c r="V20" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
+          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="W20" s="19" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>generate_report</t>
         </is>
       </c>
       <c r="X20" s="19" t="inlineStr">
         <is>
-          <t>Run GitHub Workflow Report</t>
+          <t>Run GitHub Activity Report</t>
         </is>
       </c>
       <c r="Y20" s="19" t="inlineStr">
         <is>
-          <t>Line 39</t>
+          <t>Line 56</t>
         </is>
       </c>
       <c r="Z20" s="19" t="inlineStr">
@@ -2641,12 +2559,12 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>2fcbd831207ea4821a39ee88d33aa21454ca19e3</t>
+          <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>code changed@v1</t>
+          <t>code changed1</t>
         </is>
       </c>
       <c r="G21" s="19" t="inlineStr">
@@ -2656,7 +2574,7 @@
       </c>
       <c r="H21" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:28:57Z</t>
+          <t>2026-04-06T11:54:44Z</t>
         </is>
       </c>
       <c r="I21" s="19" t="inlineStr">
@@ -2676,7 +2594,7 @@
         </is>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>24028398959</v>
+        <v>24030820444</v>
       </c>
       <c r="R21" s="19" t="inlineStr">
         <is>
@@ -2685,7 +2603,7 @@
       </c>
       <c r="S21" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:29:06Z</t>
+          <t>2026-04-06T11:54:51Z</t>
         </is>
       </c>
       <c r="T21" s="19" t="inlineStr">
@@ -2700,27 +2618,27 @@
       </c>
       <c r="V21" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
+          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="W21" s="19" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>generate_report</t>
         </is>
       </c>
       <c r="X21" s="19" t="inlineStr">
         <is>
-          <t>Run GitHub Workflow Report</t>
+          <t>Run GitHub Activity Report</t>
         </is>
       </c>
       <c r="Y21" s="19" t="inlineStr">
         <is>
-          <t>Line 29</t>
+          <t>Line 55</t>
         </is>
       </c>
       <c r="Z21" s="19" t="inlineStr">
         <is>
-          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2665,7 @@
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>37ddfe095b13b5e65a98ff2072c4bbb77cde7c1b</t>
+          <t>733b89967b9b4731953302840f2ddb2c20bedf56</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
@@ -2762,7 +2680,7 @@
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:22:31Z</t>
+          <t>2026-04-06T10:52:40Z</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
@@ -2782,7 +2700,7 @@
         </is>
       </c>
       <c r="Q22" s="19" t="n">
-        <v>24028208740</v>
+        <v>24029078530</v>
       </c>
       <c r="R22" s="19" t="inlineStr">
         <is>
@@ -2791,7 +2709,7 @@
       </c>
       <c r="S22" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:22:38Z</t>
+          <t>2026-04-06T10:52:49Z</t>
         </is>
       </c>
       <c r="T22" s="19" t="inlineStr">
@@ -2806,27 +2724,27 @@
       </c>
       <c r="V22" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+          <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
       <c r="W22" s="19" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>generate_report</t>
         </is>
       </c>
       <c r="X22" s="19" t="inlineStr">
         <is>
-          <t>Install dependencies</t>
+          <t>Set up job</t>
         </is>
       </c>
       <c r="Y22" s="19" t="inlineStr">
         <is>
-          <t>Line 22</t>
+          <t>Line 52</t>
         </is>
       </c>
       <c r="Z22" s="19" t="inlineStr">
         <is>
-          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2771,12 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>74dcfb5e2119b07af9671cc4c8396585d44a6fb8</t>
+          <t>aedf77ebc8e0433ebbe37ca97908ee5caf3929d6</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>code changd</t>
         </is>
       </c>
       <c r="G23" s="19" t="inlineStr">
@@ -2868,7 +2786,7 @@
       </c>
       <c r="H23" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:21:05Z</t>
+          <t>2026-04-06T10:44:38Z</t>
         </is>
       </c>
       <c r="I23" s="19" t="inlineStr">
@@ -2888,7 +2806,7 @@
         </is>
       </c>
       <c r="Q23" s="19" t="n">
-        <v>24028171694</v>
+        <v>24028853853</v>
       </c>
       <c r="R23" s="19" t="inlineStr">
         <is>
@@ -2897,7 +2815,7 @@
       </c>
       <c r="S23" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:21:19Z</t>
+          <t>2026-04-06T10:44:47Z</t>
         </is>
       </c>
       <c r="T23" s="19" t="inlineStr">
@@ -2912,7 +2830,7 @@
       </c>
       <c r="V23" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
         </is>
       </c>
       <c r="W23" s="19" t="inlineStr">
@@ -2922,17 +2840,17 @@
       </c>
       <c r="X23" s="19" t="inlineStr">
         <is>
-          <t>Install dependencies</t>
+          <t>Run GitHub Workflow Report</t>
         </is>
       </c>
       <c r="Y23" s="19" t="inlineStr">
         <is>
-          <t>Line 21</t>
+          <t>Line 45</t>
         </is>
       </c>
       <c r="Z23" s="19" t="inlineStr">
         <is>
-          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
@@ -2959,12 +2877,12 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>5ff73a4b92ec974d47dc4998318d0eb25003ef50</t>
+          <t>5feb9eb868fd9ff9e4a7150d13cb3252d843c106</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>Enhance workflow with caching and Node.js versioning</t>
+          <t>Update demo.txt</t>
         </is>
       </c>
       <c r="G24" s="19" t="inlineStr">
@@ -2974,7 +2892,7 @@
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:08:38Z</t>
+          <t>2026-04-06T10:31:56Z</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
@@ -2994,7 +2912,7 @@
         </is>
       </c>
       <c r="Q24" s="19" t="n">
-        <v>24027807973</v>
+        <v>24028486557</v>
       </c>
       <c r="R24" s="19" t="inlineStr">
         <is>
@@ -3003,7 +2921,7 @@
       </c>
       <c r="S24" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:08:40Z</t>
+          <t>2026-04-06T10:39:17Z</t>
         </is>
       </c>
       <c r="T24" s="19" t="inlineStr">
@@ -3018,7 +2936,7 @@
       </c>
       <c r="V24" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="W24" s="19" t="inlineStr">
@@ -3028,17 +2946,17 @@
       </c>
       <c r="X24" s="19" t="inlineStr">
         <is>
-          <t>Install dependencies</t>
+          <t>Run GitHub Workflow Report</t>
         </is>
       </c>
       <c r="Y24" s="19" t="inlineStr">
         <is>
-          <t>Line 08</t>
+          <t>Line 39</t>
         </is>
       </c>
       <c r="Z24" s="19" t="inlineStr">
         <is>
-          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
@@ -3065,22 +2983,22 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>ad002901ed69655717989c4485c2df1f343c5b15</t>
+          <t>2fcbd831207ea4821a39ee88d33aa21454ca19e3</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>Fix typo in demo.txt</t>
+          <t>code changed@v1</t>
         </is>
       </c>
       <c r="G25" s="19" t="inlineStr">
         <is>
-          <t>vidyakar-whitedev</t>
+          <t>“Vidyakar”</t>
         </is>
       </c>
       <c r="H25" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:06:00Z</t>
+          <t>2026-04-06T10:28:57Z</t>
         </is>
       </c>
       <c r="I25" s="19" t="inlineStr">
@@ -3100,7 +3018,7 @@
         </is>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>24027735534</v>
+        <v>24028398959</v>
       </c>
       <c r="R25" s="19" t="inlineStr">
         <is>
@@ -3109,7 +3027,7 @@
       </c>
       <c r="S25" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:06:01Z</t>
+          <t>2026-04-06T10:29:06Z</t>
         </is>
       </c>
       <c r="T25" s="19" t="inlineStr">
@@ -3124,7 +3042,7 @@
       </c>
       <c r="V25" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="W25" s="19" t="inlineStr">
@@ -3139,12 +3057,12 @@
       </c>
       <c r="Y25" s="19" t="inlineStr">
         <is>
-          <t>Line 06</t>
+          <t>Line 29</t>
         </is>
       </c>
       <c r="Z25" s="19" t="inlineStr">
         <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
@@ -3171,22 +3089,22 @@
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>06a295fe67b6991a6ba3430be5f485beedd7805f</t>
+          <t>37ddfe095b13b5e65a98ff2072c4bbb77cde7c1b</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>Update workflow_report.yml</t>
+          <t>code changed</t>
         </is>
       </c>
       <c r="G26" s="19" t="inlineStr">
         <is>
-          <t>vidyakar-whitedev</t>
+          <t>“Vidyakar”</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:05:48Z</t>
+          <t>2026-04-06T10:22:31Z</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -3206,7 +3124,7 @@
         </is>
       </c>
       <c r="Q26" s="19" t="n">
-        <v>24027729636</v>
+        <v>24028208740</v>
       </c>
       <c r="R26" s="19" t="inlineStr">
         <is>
@@ -3215,7 +3133,7 @@
       </c>
       <c r="S26" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:05:49Z</t>
+          <t>2026-04-06T10:22:38Z</t>
         </is>
       </c>
       <c r="T26" s="19" t="inlineStr">
@@ -3230,7 +3148,7 @@
       </c>
       <c r="V26" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
       <c r="W26" s="19" t="inlineStr">
@@ -3240,17 +3158,17 @@
       </c>
       <c r="X26" s="19" t="inlineStr">
         <is>
-          <t>Run GitHub Workflow Report</t>
+          <t>Install dependencies</t>
         </is>
       </c>
       <c r="Y26" s="19" t="inlineStr">
         <is>
-          <t>Line 06</t>
+          <t>Line 22</t>
         </is>
       </c>
       <c r="Z26" s="19" t="inlineStr">
         <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
@@ -3277,22 +3195,22 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>372cfe624d49eb38f5e8baab2c748007dc54b018</t>
+          <t>74dcfb5e2119b07af9671cc4c8396585d44a6fb8</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>Update demo.txt</t>
+          <t>code</t>
         </is>
       </c>
       <c r="G27" s="19" t="inlineStr">
         <is>
-          <t>vidyakar-whitedev</t>
+          <t>“Vidyakar”</t>
         </is>
       </c>
       <c r="H27" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:04:34Z</t>
+          <t>2026-04-06T10:21:05Z</t>
         </is>
       </c>
       <c r="I27" s="19" t="inlineStr">
@@ -3312,7 +3230,7 @@
         </is>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>24027694141</v>
+        <v>24028171694</v>
       </c>
       <c r="R27" s="19" t="inlineStr">
         <is>
@@ -3321,7 +3239,7 @@
       </c>
       <c r="S27" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:04:36Z</t>
+          <t>2026-04-06T10:21:19Z</t>
         </is>
       </c>
       <c r="T27" s="19" t="inlineStr">
@@ -3336,7 +3254,7 @@
       </c>
       <c r="V27" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
       <c r="W27" s="19" t="inlineStr">
@@ -3346,17 +3264,17 @@
       </c>
       <c r="X27" s="19" t="inlineStr">
         <is>
-          <t>Set up job</t>
+          <t>Install dependencies</t>
         </is>
       </c>
       <c r="Y27" s="19" t="inlineStr">
         <is>
-          <t>Line 04</t>
+          <t>Line 21</t>
         </is>
       </c>
       <c r="Z27" s="19" t="inlineStr">
         <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3301,12 @@
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>e7bf9d94f807df2e25e29ad5d30bc78e1b2fbd25</t>
+          <t>5ff73a4b92ec974d47dc4998318d0eb25003ef50</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>Update workflow_report.yml</t>
+          <t>Enhance workflow with caching and Node.js versioning</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
@@ -3398,7 +3316,7 @@
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:04:22Z</t>
+          <t>2026-04-06T10:08:38Z</t>
         </is>
       </c>
       <c r="I28" s="19" t="inlineStr">
@@ -3418,7 +3336,7 @@
         </is>
       </c>
       <c r="Q28" s="19" t="n">
-        <v>24027689526</v>
+        <v>24027807973</v>
       </c>
       <c r="R28" s="19" t="inlineStr">
         <is>
@@ -3427,7 +3345,7 @@
       </c>
       <c r="S28" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:04:27Z</t>
+          <t>2026-04-06T10:08:40Z</t>
         </is>
       </c>
       <c r="T28" s="19" t="inlineStr">
@@ -3442,7 +3360,7 @@
       </c>
       <c r="V28" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
       <c r="W28" s="19" t="inlineStr">
@@ -3452,17 +3370,17 @@
       </c>
       <c r="X28" s="19" t="inlineStr">
         <is>
-          <t>Set up job</t>
+          <t>Install dependencies</t>
         </is>
       </c>
       <c r="Y28" s="19" t="inlineStr">
         <is>
-          <t>Line 04</t>
+          <t>Line 08</t>
         </is>
       </c>
       <c r="Z28" s="19" t="inlineStr">
         <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3407,12 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>3046e3250b6d3bc90634487150d715e566686a47</t>
+          <t>ad002901ed69655717989c4485c2df1f343c5b15</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>Add demo.txt for testing purposes</t>
+          <t>Fix typo in demo.txt</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
@@ -3504,7 +3422,7 @@
       </c>
       <c r="H29" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:02:10Z</t>
+          <t>2026-04-06T10:06:00Z</t>
         </is>
       </c>
       <c r="I29" s="19" t="inlineStr">
@@ -3520,11 +3438,11 @@
       <c r="O29" s="19" t="inlineStr"/>
       <c r="P29" s="19" t="inlineStr">
         <is>
-          <t>.github/workflows/workflow_report.yml</t>
+          <t>GitHub Workflow Report</t>
         </is>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>24027621196</v>
+        <v>24027735534</v>
       </c>
       <c r="R29" s="19" t="inlineStr">
         <is>
@@ -3533,7 +3451,7 @@
       </c>
       <c r="S29" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:02:12Z</t>
+          <t>2026-04-06T10:06:01Z</t>
         </is>
       </c>
       <c r="T29" s="19" t="inlineStr">
@@ -3548,14 +3466,22 @@
       </c>
       <c r="V29" s="19" t="inlineStr">
         <is>
-          <t>Failure (see logs)</t>
-        </is>
-      </c>
-      <c r="W29" s="19" t="inlineStr"/>
-      <c r="X29" s="19" t="inlineStr"/>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
+        </is>
+      </c>
+      <c r="W29" s="19" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="X29" s="19" t="inlineStr">
+        <is>
+          <t>Run GitHub Workflow Report</t>
+        </is>
+      </c>
       <c r="Y29" s="19" t="inlineStr">
         <is>
-          <t>See GitHub Actions logs</t>
+          <t>Line 06</t>
         </is>
       </c>
       <c r="Z29" s="19" t="inlineStr">
@@ -3587,12 +3513,12 @@
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>32de2be70035a86124e1345187c9ba078e4cf3bf</t>
+          <t>06a295fe67b6991a6ba3430be5f485beedd7805f</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>Add GitHub Workflow Report YAML configuration</t>
+          <t>Update workflow_report.yml</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
@@ -3602,7 +3528,7 @@
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:01:02Z</t>
+          <t>2026-04-06T10:05:48Z</t>
         </is>
       </c>
       <c r="I30" s="19" t="inlineStr">
@@ -3618,180 +3544,596 @@
       <c r="O30" s="19" t="inlineStr"/>
       <c r="P30" s="19" t="inlineStr">
         <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q30" s="19" t="n">
+        <v>24027729636</v>
+      </c>
+      <c r="R30" s="19" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S30" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:05:49Z</t>
+        </is>
+      </c>
+      <c r="T30" s="19" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U30" s="20" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="V30" s="19" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
+        </is>
+      </c>
+      <c r="W30" s="19" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="X30" s="19" t="inlineStr">
+        <is>
+          <t>Run GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Y30" s="19" t="inlineStr">
+        <is>
+          <t>Line 06</t>
+        </is>
+      </c>
+      <c r="Z30" s="19" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>372cfe624d49eb38f5e8baab2c748007dc54b018</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>Update demo.txt</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:04:34Z</t>
+        </is>
+      </c>
+      <c r="I31" s="19" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J31" s="19" t="inlineStr"/>
+      <c r="K31" s="19" t="inlineStr"/>
+      <c r="L31" s="19" t="inlineStr"/>
+      <c r="M31" s="19" t="inlineStr"/>
+      <c r="N31" s="19" t="inlineStr"/>
+      <c r="O31" s="19" t="inlineStr"/>
+      <c r="P31" s="19" t="inlineStr">
+        <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q31" s="19" t="n">
+        <v>24027694141</v>
+      </c>
+      <c r="R31" s="19" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S31" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:04:36Z</t>
+        </is>
+      </c>
+      <c r="T31" s="19" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U31" s="20" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="V31" s="19" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+        </is>
+      </c>
+      <c r="W31" s="19" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="X31" s="19" t="inlineStr">
+        <is>
+          <t>Set up job</t>
+        </is>
+      </c>
+      <c r="Y31" s="19" t="inlineStr">
+        <is>
+          <t>Line 04</t>
+        </is>
+      </c>
+      <c r="Z31" s="19" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>e7bf9d94f807df2e25e29ad5d30bc78e1b2fbd25</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>Update workflow_report.yml</t>
+        </is>
+      </c>
+      <c r="G32" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H32" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:04:22Z</t>
+        </is>
+      </c>
+      <c r="I32" s="19" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J32" s="19" t="inlineStr"/>
+      <c r="K32" s="19" t="inlineStr"/>
+      <c r="L32" s="19" t="inlineStr"/>
+      <c r="M32" s="19" t="inlineStr"/>
+      <c r="N32" s="19" t="inlineStr"/>
+      <c r="O32" s="19" t="inlineStr"/>
+      <c r="P32" s="19" t="inlineStr">
+        <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q32" s="19" t="n">
+        <v>24027689526</v>
+      </c>
+      <c r="R32" s="19" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S32" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:04:27Z</t>
+        </is>
+      </c>
+      <c r="T32" s="19" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U32" s="20" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="V32" s="19" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+        </is>
+      </c>
+      <c r="W32" s="19" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="X32" s="19" t="inlineStr">
+        <is>
+          <t>Set up job</t>
+        </is>
+      </c>
+      <c r="Y32" s="19" t="inlineStr">
+        <is>
+          <t>Line 04</t>
+        </is>
+      </c>
+      <c r="Z32" s="19" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>3046e3250b6d3bc90634487150d715e566686a47</t>
+        </is>
+      </c>
+      <c r="F33" s="19" t="inlineStr">
+        <is>
+          <t>Add demo.txt for testing purposes</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H33" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:02:10Z</t>
+        </is>
+      </c>
+      <c r="I33" s="19" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J33" s="19" t="inlineStr"/>
+      <c r="K33" s="19" t="inlineStr"/>
+      <c r="L33" s="19" t="inlineStr"/>
+      <c r="M33" s="19" t="inlineStr"/>
+      <c r="N33" s="19" t="inlineStr"/>
+      <c r="O33" s="19" t="inlineStr"/>
+      <c r="P33" s="19" t="inlineStr">
+        <is>
           <t>.github/workflows/workflow_report.yml</t>
         </is>
       </c>
-      <c r="Q30" s="19" t="n">
+      <c r="Q33" s="19" t="n">
+        <v>24027621196</v>
+      </c>
+      <c r="R33" s="19" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S33" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:02:12Z</t>
+        </is>
+      </c>
+      <c r="T33" s="19" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U33" s="20" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="V33" s="19" t="inlineStr">
+        <is>
+          <t>Failure (see logs)</t>
+        </is>
+      </c>
+      <c r="W33" s="19" t="inlineStr"/>
+      <c r="X33" s="19" t="inlineStr"/>
+      <c r="Y33" s="19" t="inlineStr">
+        <is>
+          <t>See GitHub Actions logs</t>
+        </is>
+      </c>
+      <c r="Z33" s="19" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>32de2be70035a86124e1345187c9ba078e4cf3bf</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>Add GitHub Workflow Report YAML configuration</t>
+        </is>
+      </c>
+      <c r="G34" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H34" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:01:02Z</t>
+        </is>
+      </c>
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J34" s="19" t="inlineStr"/>
+      <c r="K34" s="19" t="inlineStr"/>
+      <c r="L34" s="19" t="inlineStr"/>
+      <c r="M34" s="19" t="inlineStr"/>
+      <c r="N34" s="19" t="inlineStr"/>
+      <c r="O34" s="19" t="inlineStr"/>
+      <c r="P34" s="19" t="inlineStr">
+        <is>
+          <t>.github/workflows/workflow_report.yml</t>
+        </is>
+      </c>
+      <c r="Q34" s="19" t="n">
         <v>24027587697</v>
       </c>
-      <c r="R30" s="19" t="inlineStr">
+      <c r="R34" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S30" s="19" t="inlineStr">
+      <c r="S34" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:01:04Z</t>
         </is>
       </c>
-      <c r="T30" s="19" t="inlineStr">
+      <c r="T34" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U30" s="20" t="inlineStr">
+      <c r="U34" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="V30" s="19" t="inlineStr">
+      <c r="V34" s="19" t="inlineStr">
         <is>
           <t>Failure (see logs)</t>
         </is>
       </c>
-      <c r="W30" s="19" t="inlineStr"/>
-      <c r="X30" s="19" t="inlineStr"/>
-      <c r="Y30" s="19" t="inlineStr">
+      <c r="W34" s="19" t="inlineStr"/>
+      <c r="X34" s="19" t="inlineStr"/>
+      <c r="Y34" s="19" t="inlineStr">
         <is>
           <t>See GitHub Actions logs</t>
         </is>
       </c>
-      <c r="Z30" s="19" t="inlineStr">
+      <c r="Z34" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D35" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E35" s="18" t="inlineStr">
         <is>
           <t>8eaab42012c4f02192c65cf59561b5c261b2cf90</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F35" s="18" t="inlineStr">
         <is>
           <t>Create github_workflow_report.py</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H35" s="18" t="inlineStr">
         <is>
           <t>2026-04-06T09:50:41Z</t>
         </is>
       </c>
-      <c r="I31" s="16" t="inlineStr">
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J31" s="16" t="inlineStr"/>
-      <c r="K31" s="16" t="inlineStr"/>
-      <c r="L31" s="16" t="inlineStr"/>
-      <c r="M31" s="16" t="inlineStr"/>
-      <c r="N31" s="16" t="inlineStr"/>
-      <c r="O31" s="16" t="inlineStr"/>
-      <c r="P31" s="16" t="inlineStr"/>
-      <c r="Q31" s="16" t="inlineStr"/>
-      <c r="R31" s="16" t="inlineStr"/>
-      <c r="S31" s="16" t="inlineStr"/>
-      <c r="T31" s="16" t="inlineStr"/>
-      <c r="U31" s="16" t="inlineStr"/>
-      <c r="V31" s="16" t="inlineStr"/>
-      <c r="W31" s="16" t="inlineStr"/>
-      <c r="X31" s="16" t="inlineStr"/>
-      <c r="Y31" s="16" t="inlineStr"/>
-      <c r="Z31" s="16" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="J35" s="18" t="inlineStr"/>
+      <c r="K35" s="18" t="inlineStr"/>
+      <c r="L35" s="18" t="inlineStr"/>
+      <c r="M35" s="18" t="inlineStr"/>
+      <c r="N35" s="18" t="inlineStr"/>
+      <c r="O35" s="18" t="inlineStr"/>
+      <c r="P35" s="18" t="inlineStr"/>
+      <c r="Q35" s="18" t="inlineStr"/>
+      <c r="R35" s="18" t="inlineStr"/>
+      <c r="S35" s="18" t="inlineStr"/>
+      <c r="T35" s="18" t="inlineStr"/>
+      <c r="U35" s="18" t="inlineStr"/>
+      <c r="V35" s="18" t="inlineStr"/>
+      <c r="W35" s="18" t="inlineStr"/>
+      <c r="X35" s="18" t="inlineStr"/>
+      <c r="Y35" s="18" t="inlineStr"/>
+      <c r="Z35" s="18" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>a9e73f5e7cd8ea7da7f4969f80034915cc9f302c</t>
         </is>
       </c>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="F36" s="15" t="inlineStr">
         <is>
           <t>Initial commit</t>
         </is>
       </c>
-      <c r="G32" s="15" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="inlineStr">
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="inlineStr">
         <is>
           <t>2026-04-06T09:48:37Z</t>
         </is>
       </c>
-      <c r="I32" s="15" t="inlineStr">
+      <c r="I36" s="15" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J32" s="15" t="inlineStr"/>
-      <c r="K32" s="15" t="inlineStr"/>
-      <c r="L32" s="15" t="inlineStr"/>
-      <c r="M32" s="15" t="inlineStr"/>
-      <c r="N32" s="15" t="inlineStr"/>
-      <c r="O32" s="15" t="inlineStr"/>
-      <c r="P32" s="15" t="inlineStr"/>
-      <c r="Q32" s="15" t="inlineStr"/>
-      <c r="R32" s="15" t="inlineStr"/>
-      <c r="S32" s="15" t="inlineStr"/>
-      <c r="T32" s="15" t="inlineStr"/>
-      <c r="U32" s="15" t="inlineStr"/>
-      <c r="V32" s="15" t="inlineStr"/>
-      <c r="W32" s="15" t="inlineStr"/>
-      <c r="X32" s="15" t="inlineStr"/>
-      <c r="Y32" s="15" t="inlineStr"/>
-      <c r="Z32" s="15" t="inlineStr"/>
+      <c r="J36" s="15" t="inlineStr"/>
+      <c r="K36" s="15" t="inlineStr"/>
+      <c r="L36" s="15" t="inlineStr"/>
+      <c r="M36" s="15" t="inlineStr"/>
+      <c r="N36" s="15" t="inlineStr"/>
+      <c r="O36" s="15" t="inlineStr"/>
+      <c r="P36" s="15" t="inlineStr"/>
+      <c r="Q36" s="15" t="inlineStr"/>
+      <c r="R36" s="15" t="inlineStr"/>
+      <c r="S36" s="15" t="inlineStr"/>
+      <c r="T36" s="15" t="inlineStr"/>
+      <c r="U36" s="15" t="inlineStr"/>
+      <c r="V36" s="15" t="inlineStr"/>
+      <c r="W36" s="15" t="inlineStr"/>
+      <c r="X36" s="15" t="inlineStr"/>
+      <c r="Y36" s="15" t="inlineStr"/>
+      <c r="Z36" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z32"/>
+  <autoFilter ref="A1:Z36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3864,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3877,7 +4219,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="62" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="62" customWidth="1" min="13" max="13"/>
   </cols>
@@ -3962,20 +4304,20 @@
       </c>
       <c r="C2" s="19" t="inlineStr">
         <is>
-          <t>GitHub Workflow Report</t>
+          <t>GitHub Activity Report</t>
         </is>
       </c>
       <c r="D2" s="19" t="n">
-        <v>24030846379</v>
+        <v>24250086438</v>
       </c>
       <c r="E2" s="19" t="inlineStr">
         <is>
-          <t>workflow_dispatch</t>
+          <t>push</t>
         </is>
       </c>
       <c r="F2" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T11:55:45Z</t>
+          <t>2026-04-10T15:18:50Z</t>
         </is>
       </c>
       <c r="G2" s="19" t="inlineStr">
@@ -3990,7 +4332,7 @@
       </c>
       <c r="I2" s="19" t="inlineStr">
         <is>
-          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
+          <t>Job 'generate_report' step 'Commit and push report to repository' failed — 2026-04-10T15:19:10.4298620Z 15:19:10  WARNING   WORKFLOW FAILURE in vidyakar-whitedev/git-report  (Run ID: 24030846379)</t>
         </is>
       </c>
       <c r="J2" s="19" t="inlineStr">
@@ -4000,17 +4342,17 @@
       </c>
       <c r="K2" s="19" t="inlineStr">
         <is>
-          <t>Run GitHub Activity Report</t>
+          <t>Commit and push report to repository</t>
         </is>
       </c>
       <c r="L2" s="19" t="inlineStr">
         <is>
-          <t>Line 56</t>
+          <t>Line 19</t>
         </is>
       </c>
       <c r="M2" s="19" t="inlineStr">
         <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
@@ -4031,16 +4373,16 @@
         </is>
       </c>
       <c r="D3" s="19" t="n">
-        <v>24030820444</v>
+        <v>24030846379</v>
       </c>
       <c r="E3" s="19" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>workflow_dispatch</t>
         </is>
       </c>
       <c r="F3" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T11:54:51Z</t>
+          <t>2026-04-06T11:55:45Z</t>
         </is>
       </c>
       <c r="G3" s="19" t="inlineStr">
@@ -4055,7 +4397,7 @@
       </c>
       <c r="I3" s="19" t="inlineStr">
         <is>
-          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
+          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="J3" s="19" t="inlineStr">
@@ -4070,7 +4412,7 @@
       </c>
       <c r="L3" s="19" t="inlineStr">
         <is>
-          <t>Line 55</t>
+          <t>Line 56</t>
         </is>
       </c>
       <c r="M3" s="19" t="inlineStr">
@@ -4096,7 +4438,7 @@
         </is>
       </c>
       <c r="D4" s="19" t="n">
-        <v>24029078530</v>
+        <v>24030820444</v>
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
@@ -4105,7 +4447,7 @@
       </c>
       <c r="F4" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:52:49Z</t>
+          <t>2026-04-06T11:54:51Z</t>
         </is>
       </c>
       <c r="G4" s="19" t="inlineStr">
@@ -4120,7 +4462,7 @@
       </c>
       <c r="I4" s="19" t="inlineStr">
         <is>
-          <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="J4" s="19" t="inlineStr">
@@ -4130,12 +4472,12 @@
       </c>
       <c r="K4" s="19" t="inlineStr">
         <is>
-          <t>Set up job</t>
+          <t>Run GitHub Activity Report</t>
         </is>
       </c>
       <c r="L4" s="19" t="inlineStr">
         <is>
-          <t>Line 52</t>
+          <t>Line 55</t>
         </is>
       </c>
       <c r="M4" s="19" t="inlineStr">
@@ -4161,7 +4503,7 @@
         </is>
       </c>
       <c r="D5" s="19" t="n">
-        <v>24028853853</v>
+        <v>24029078530</v>
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
@@ -4170,7 +4512,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:44:47Z</t>
+          <t>2026-04-06T10:52:49Z</t>
         </is>
       </c>
       <c r="G5" s="19" t="inlineStr">
@@ -4185,27 +4527,27 @@
       </c>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
+          <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
       <c r="J5" s="19" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>generate_report</t>
         </is>
       </c>
       <c r="K5" s="19" t="inlineStr">
         <is>
-          <t>Run GitHub Workflow Report</t>
+          <t>Set up job</t>
         </is>
       </c>
       <c r="L5" s="19" t="inlineStr">
         <is>
-          <t>Line 45</t>
+          <t>Line 52</t>
         </is>
       </c>
       <c r="M5" s="19" t="inlineStr">
         <is>
-          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4568,7 @@
         </is>
       </c>
       <c r="D6" s="19" t="n">
-        <v>24028486557</v>
+        <v>24028853853</v>
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
@@ -4235,7 +4577,7 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:39:17Z</t>
+          <t>2026-04-06T10:44:47Z</t>
         </is>
       </c>
       <c r="G6" s="19" t="inlineStr">
@@ -4250,7 +4592,7 @@
       </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
         </is>
       </c>
       <c r="J6" s="19" t="inlineStr">
@@ -4265,12 +4607,12 @@
       </c>
       <c r="L6" s="19" t="inlineStr">
         <is>
-          <t>Line 39</t>
+          <t>Line 45</t>
         </is>
       </c>
       <c r="M6" s="19" t="inlineStr">
         <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4633,7 @@
         </is>
       </c>
       <c r="D7" s="19" t="n">
-        <v>24028398959</v>
+        <v>24028486557</v>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
@@ -4300,7 +4642,7 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:29:06Z</t>
+          <t>2026-04-06T10:39:17Z</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -4315,7 +4657,7 @@
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="J7" s="19" t="inlineStr">
@@ -4330,12 +4672,12 @@
       </c>
       <c r="L7" s="19" t="inlineStr">
         <is>
-          <t>Line 29</t>
+          <t>Line 39</t>
         </is>
       </c>
       <c r="M7" s="19" t="inlineStr">
         <is>
-          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4698,7 @@
         </is>
       </c>
       <c r="D8" s="19" t="n">
-        <v>24028208740</v>
+        <v>24028398959</v>
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
@@ -4365,7 +4707,7 @@
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:22:38Z</t>
+          <t>2026-04-06T10:29:06Z</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
@@ -4380,7 +4722,7 @@
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="J8" s="19" t="inlineStr">
@@ -4390,17 +4732,17 @@
       </c>
       <c r="K8" s="19" t="inlineStr">
         <is>
-          <t>Install dependencies</t>
+          <t>Run GitHub Workflow Report</t>
         </is>
       </c>
       <c r="L8" s="19" t="inlineStr">
         <is>
-          <t>Line 22</t>
+          <t>Line 29</t>
         </is>
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
-          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4763,7 @@
         </is>
       </c>
       <c r="D9" s="19" t="n">
-        <v>24028171694</v>
+        <v>24028208740</v>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
@@ -4430,7 +4772,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:21:19Z</t>
+          <t>2026-04-06T10:22:38Z</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -4445,7 +4787,7 @@
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
       <c r="J9" s="19" t="inlineStr">
@@ -4460,7 +4802,7 @@
       </c>
       <c r="L9" s="19" t="inlineStr">
         <is>
-          <t>Line 21</t>
+          <t>Line 22</t>
         </is>
       </c>
       <c r="M9" s="19" t="inlineStr">
@@ -4486,7 +4828,7 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>24027807973</v>
+        <v>24028171694</v>
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
@@ -4495,7 +4837,7 @@
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:08:40Z</t>
+          <t>2026-04-06T10:21:19Z</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
@@ -4510,7 +4852,7 @@
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
       <c r="J10" s="19" t="inlineStr">
@@ -4525,7 +4867,7 @@
       </c>
       <c r="L10" s="19" t="inlineStr">
         <is>
-          <t>Line 08</t>
+          <t>Line 21</t>
         </is>
       </c>
       <c r="M10" s="19" t="inlineStr">
@@ -4551,7 +4893,7 @@
         </is>
       </c>
       <c r="D11" s="19" t="n">
-        <v>24027735534</v>
+        <v>24027807973</v>
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
@@ -4560,7 +4902,7 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:06:01Z</t>
+          <t>2026-04-06T10:08:40Z</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -4575,7 +4917,7 @@
       </c>
       <c r="I11" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
       <c r="J11" s="19" t="inlineStr">
@@ -4585,17 +4927,17 @@
       </c>
       <c r="K11" s="19" t="inlineStr">
         <is>
-          <t>Run GitHub Workflow Report</t>
+          <t>Install dependencies</t>
         </is>
       </c>
       <c r="L11" s="19" t="inlineStr">
         <is>
-          <t>Line 06</t>
+          <t>Line 08</t>
         </is>
       </c>
       <c r="M11" s="19" t="inlineStr">
         <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4958,7 @@
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>24027729636</v>
+        <v>24027735534</v>
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
@@ -4625,7 +4967,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:05:49Z</t>
+          <t>2026-04-06T10:06:01Z</t>
         </is>
       </c>
       <c r="G12" s="19" t="inlineStr">
@@ -4640,7 +4982,7 @@
       </c>
       <c r="I12" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="J12" s="19" t="inlineStr">
@@ -4681,7 +5023,7 @@
         </is>
       </c>
       <c r="D13" s="19" t="n">
-        <v>24027694141</v>
+        <v>24027729636</v>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
@@ -4690,7 +5032,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:04:36Z</t>
+          <t>2026-04-06T10:05:49Z</t>
         </is>
       </c>
       <c r="G13" s="19" t="inlineStr">
@@ -4705,7 +5047,7 @@
       </c>
       <c r="I13" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="J13" s="19" t="inlineStr">
@@ -4715,12 +5057,12 @@
       </c>
       <c r="K13" s="19" t="inlineStr">
         <is>
-          <t>Set up job</t>
+          <t>Run GitHub Workflow Report</t>
         </is>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
-          <t>Line 04</t>
+          <t>Line 06</t>
         </is>
       </c>
       <c r="M13" s="19" t="inlineStr">
@@ -4746,7 +5088,7 @@
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>24027689526</v>
+        <v>24027694141</v>
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
@@ -4755,7 +5097,7 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:04:27Z</t>
+          <t>2026-04-06T10:04:36Z</t>
         </is>
       </c>
       <c r="G14" s="19" t="inlineStr">
@@ -4770,7 +5112,7 @@
       </c>
       <c r="I14" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
       <c r="J14" s="19" t="inlineStr">
@@ -4807,11 +5149,11 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>.github/workflows/workflow_report.yml</t>
+          <t>GitHub Workflow Report</t>
         </is>
       </c>
       <c r="D15" s="19" t="n">
-        <v>24027621196</v>
+        <v>24027689526</v>
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
@@ -4820,7 +5162,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:02:12Z</t>
+          <t>2026-04-06T10:04:27Z</t>
         </is>
       </c>
       <c r="G15" s="19" t="inlineStr">
@@ -4835,14 +5177,22 @@
       </c>
       <c r="I15" s="19" t="inlineStr">
         <is>
-          <t>Failure (see logs)</t>
-        </is>
-      </c>
-      <c r="J15" s="19" t="inlineStr"/>
-      <c r="K15" s="19" t="inlineStr"/>
+          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+        </is>
+      </c>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="K15" s="19" t="inlineStr">
+        <is>
+          <t>Set up job</t>
+        </is>
+      </c>
       <c r="L15" s="19" t="inlineStr">
         <is>
-          <t>See GitHub Actions logs</t>
+          <t>Line 04</t>
         </is>
       </c>
       <c r="M15" s="19" t="inlineStr">
@@ -4868,7 +5218,7 @@
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>24027587697</v>
+        <v>24027621196</v>
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
@@ -4877,7 +5227,7 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:01:04Z</t>
+          <t>2026-04-06T10:02:12Z</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -4908,8 +5258,65 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>.github/workflows/workflow_report.yml</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>24027587697</v>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:01:04Z</t>
+        </is>
+      </c>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="I17" s="19" t="inlineStr">
+        <is>
+          <t>Failure (see logs)</t>
+        </is>
+      </c>
+      <c r="J17" s="19" t="inlineStr"/>
+      <c r="K17" s="19" t="inlineStr"/>
+      <c r="L17" s="19" t="inlineStr">
+        <is>
+          <t>See GitHub Actions logs</t>
+        </is>
+      </c>
+      <c r="M17" s="19" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M16"/>
+  <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4921,7 +5328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4934,7 +5341,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="62" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="62" customWidth="1" min="13" max="13"/>
   </cols>
@@ -4942,14 +5349,14 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>⚠   15 WORKFLOW FAILURE(S) DETECTED</t>
+          <t>⚠   16 WORKFLOW FAILURE(S) DETECTED</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-10 15:17 UTC  |  GitHub Activity &amp; Workflow Audit Report</t>
+          <t>Generated: 2026-04-10 16:37 UTC  |  GitHub Activity &amp; Workflow Audit Report</t>
         </is>
       </c>
     </row>
@@ -5036,20 +5443,20 @@
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>GitHub Workflow Report</t>
+          <t>GitHub Activity Report</t>
         </is>
       </c>
       <c r="E4" s="24" t="n">
-        <v>24030846379</v>
+        <v>24250086438</v>
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>workflow_dispatch</t>
+          <t>push</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
-          <t>2026-04-06T11:55:45Z</t>
+          <t>2026-04-10T15:18:50Z</t>
         </is>
       </c>
       <c r="H4" s="24" t="inlineStr">
@@ -5059,7 +5466,7 @@
       </c>
       <c r="I4" s="24" t="inlineStr">
         <is>
-          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
+          <t>Job 'generate_report' step 'Commit and push report to repository' failed — 2026-04-10T15:19:10.4298620Z 15:19:10  WARNING   WORKFLOW FAILURE in vidyakar-whitedev/git-report  (Run ID: 24030846379)</t>
         </is>
       </c>
       <c r="J4" s="24" t="inlineStr">
@@ -5069,17 +5476,17 @@
       </c>
       <c r="K4" s="24" t="inlineStr">
         <is>
-          <t>Run GitHub Activity Report</t>
+          <t>Commit and push report to repository</t>
         </is>
       </c>
       <c r="L4" s="24" t="inlineStr">
         <is>
-          <t>Line 56</t>
+          <t>Line 19</t>
         </is>
       </c>
       <c r="M4" s="24" t="inlineStr">
         <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
@@ -5103,16 +5510,16 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>24030820444</v>
+        <v>24030846379</v>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>workflow_dispatch</t>
         </is>
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T11:54:51Z</t>
+          <t>2026-04-06T11:55:45Z</t>
         </is>
       </c>
       <c r="H5" s="19" t="inlineStr">
@@ -5122,7 +5529,7 @@
       </c>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
+          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="J5" s="19" t="inlineStr">
@@ -5137,7 +5544,7 @@
       </c>
       <c r="L5" s="19" t="inlineStr">
         <is>
-          <t>Line 55</t>
+          <t>Line 56</t>
         </is>
       </c>
       <c r="M5" s="19" t="inlineStr">
@@ -5166,7 +5573,7 @@
         </is>
       </c>
       <c r="E6" s="24" t="n">
-        <v>24029078530</v>
+        <v>24030820444</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -5175,7 +5582,7 @@
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>2026-04-06T10:52:49Z</t>
+          <t>2026-04-06T11:54:51Z</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
@@ -5185,7 +5592,7 @@
       </c>
       <c r="I6" s="24" t="inlineStr">
         <is>
-          <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="J6" s="24" t="inlineStr">
@@ -5195,12 +5602,12 @@
       </c>
       <c r="K6" s="24" t="inlineStr">
         <is>
-          <t>Set up job</t>
+          <t>Run GitHub Activity Report</t>
         </is>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>Line 52</t>
+          <t>Line 55</t>
         </is>
       </c>
       <c r="M6" s="24" t="inlineStr">
@@ -5229,7 +5636,7 @@
         </is>
       </c>
       <c r="E7" s="19" t="n">
-        <v>24028853853</v>
+        <v>24029078530</v>
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
@@ -5238,7 +5645,7 @@
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:44:47Z</t>
+          <t>2026-04-06T10:52:49Z</t>
         </is>
       </c>
       <c r="H7" s="19" t="inlineStr">
@@ -5248,27 +5655,27 @@
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
+          <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>generate_report</t>
         </is>
       </c>
       <c r="K7" s="19" t="inlineStr">
         <is>
-          <t>Run GitHub Workflow Report</t>
+          <t>Set up job</t>
         </is>
       </c>
       <c r="L7" s="19" t="inlineStr">
         <is>
-          <t>Line 45</t>
+          <t>Line 52</t>
         </is>
       </c>
       <c r="M7" s="19" t="inlineStr">
         <is>
-          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5699,7 @@
         </is>
       </c>
       <c r="E8" s="24" t="n">
-        <v>24028486557</v>
+        <v>24028853853</v>
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
@@ -5301,7 +5708,7 @@
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>2026-04-06T10:39:17Z</t>
+          <t>2026-04-06T10:44:47Z</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
@@ -5311,7 +5718,7 @@
       </c>
       <c r="I8" s="24" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
         </is>
       </c>
       <c r="J8" s="24" t="inlineStr">
@@ -5326,12 +5733,12 @@
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>Line 39</t>
+          <t>Line 45</t>
         </is>
       </c>
       <c r="M8" s="24" t="inlineStr">
         <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5762,7 @@
         </is>
       </c>
       <c r="E9" s="19" t="n">
-        <v>24028398959</v>
+        <v>24028486557</v>
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
@@ -5364,7 +5771,7 @@
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:29:06Z</t>
+          <t>2026-04-06T10:39:17Z</t>
         </is>
       </c>
       <c r="H9" s="19" t="inlineStr">
@@ -5374,7 +5781,7 @@
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="J9" s="19" t="inlineStr">
@@ -5389,12 +5796,12 @@
       </c>
       <c r="L9" s="19" t="inlineStr">
         <is>
-          <t>Line 29</t>
+          <t>Line 39</t>
         </is>
       </c>
       <c r="M9" s="19" t="inlineStr">
         <is>
-          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5825,7 @@
         </is>
       </c>
       <c r="E10" s="24" t="n">
-        <v>24028208740</v>
+        <v>24028398959</v>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
@@ -5427,7 +5834,7 @@
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>2026-04-06T10:22:38Z</t>
+          <t>2026-04-06T10:29:06Z</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -5437,7 +5844,7 @@
       </c>
       <c r="I10" s="24" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="J10" s="24" t="inlineStr">
@@ -5447,17 +5854,17 @@
       </c>
       <c r="K10" s="24" t="inlineStr">
         <is>
-          <t>Install dependencies</t>
+          <t>Run GitHub Workflow Report</t>
         </is>
       </c>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t>Line 22</t>
+          <t>Line 29</t>
         </is>
       </c>
       <c r="M10" s="24" t="inlineStr">
         <is>
-          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5888,7 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>24028171694</v>
+        <v>24028208740</v>
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
@@ -5490,7 +5897,7 @@
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:21:19Z</t>
+          <t>2026-04-06T10:22:38Z</t>
         </is>
       </c>
       <c r="H11" s="19" t="inlineStr">
@@ -5500,7 +5907,7 @@
       </c>
       <c r="I11" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
       <c r="J11" s="19" t="inlineStr">
@@ -5515,7 +5922,7 @@
       </c>
       <c r="L11" s="19" t="inlineStr">
         <is>
-          <t>Line 21</t>
+          <t>Line 22</t>
         </is>
       </c>
       <c r="M11" s="19" t="inlineStr">
@@ -5544,7 +5951,7 @@
         </is>
       </c>
       <c r="E12" s="24" t="n">
-        <v>24027807973</v>
+        <v>24028171694</v>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
@@ -5553,7 +5960,7 @@
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>2026-04-06T10:08:40Z</t>
+          <t>2026-04-06T10:21:19Z</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -5563,7 +5970,7 @@
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
       <c r="J12" s="24" t="inlineStr">
@@ -5578,7 +5985,7 @@
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>Line 08</t>
+          <t>Line 21</t>
         </is>
       </c>
       <c r="M12" s="24" t="inlineStr">
@@ -5607,7 +6014,7 @@
         </is>
       </c>
       <c r="E13" s="19" t="n">
-        <v>24027735534</v>
+        <v>24027807973</v>
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
@@ -5616,7 +6023,7 @@
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:06:01Z</t>
+          <t>2026-04-06T10:08:40Z</t>
         </is>
       </c>
       <c r="H13" s="19" t="inlineStr">
@@ -5626,7 +6033,7 @@
       </c>
       <c r="I13" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
       <c r="J13" s="19" t="inlineStr">
@@ -5636,17 +6043,17 @@
       </c>
       <c r="K13" s="19" t="inlineStr">
         <is>
-          <t>Run GitHub Workflow Report</t>
+          <t>Install dependencies</t>
         </is>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
-          <t>Line 06</t>
+          <t>Line 08</t>
         </is>
       </c>
       <c r="M13" s="19" t="inlineStr">
         <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
@@ -5670,7 +6077,7 @@
         </is>
       </c>
       <c r="E14" s="24" t="n">
-        <v>24027729636</v>
+        <v>24027735534</v>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
@@ -5679,7 +6086,7 @@
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>2026-04-06T10:05:49Z</t>
+          <t>2026-04-06T10:06:01Z</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -5689,7 +6096,7 @@
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="J14" s="24" t="inlineStr">
@@ -5733,7 +6140,7 @@
         </is>
       </c>
       <c r="E15" s="19" t="n">
-        <v>24027694141</v>
+        <v>24027729636</v>
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
@@ -5742,7 +6149,7 @@
       </c>
       <c r="G15" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:04:36Z</t>
+          <t>2026-04-06T10:05:49Z</t>
         </is>
       </c>
       <c r="H15" s="19" t="inlineStr">
@@ -5752,7 +6159,7 @@
       </c>
       <c r="I15" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="J15" s="19" t="inlineStr">
@@ -5762,12 +6169,12 @@
       </c>
       <c r="K15" s="19" t="inlineStr">
         <is>
-          <t>Set up job</t>
+          <t>Run GitHub Workflow Report</t>
         </is>
       </c>
       <c r="L15" s="19" t="inlineStr">
         <is>
-          <t>Line 04</t>
+          <t>Line 06</t>
         </is>
       </c>
       <c r="M15" s="19" t="inlineStr">
@@ -5796,7 +6203,7 @@
         </is>
       </c>
       <c r="E16" s="24" t="n">
-        <v>24027689526</v>
+        <v>24027694141</v>
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
@@ -5805,7 +6212,7 @@
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>2026-04-06T10:04:27Z</t>
+          <t>2026-04-06T10:04:36Z</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5815,7 +6222,7 @@
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
       <c r="J16" s="24" t="inlineStr">
@@ -5855,11 +6262,11 @@
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>.github/workflows/workflow_report.yml</t>
+          <t>GitHub Workflow Report</t>
         </is>
       </c>
       <c r="E17" s="19" t="n">
-        <v>24027621196</v>
+        <v>24027689526</v>
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
@@ -5868,7 +6275,7 @@
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:02:12Z</t>
+          <t>2026-04-06T10:04:27Z</t>
         </is>
       </c>
       <c r="H17" s="19" t="inlineStr">
@@ -5878,14 +6285,22 @@
       </c>
       <c r="I17" s="19" t="inlineStr">
         <is>
-          <t>Failure (see logs)</t>
-        </is>
-      </c>
-      <c r="J17" s="19" t="inlineStr"/>
-      <c r="K17" s="19" t="inlineStr"/>
+          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+        </is>
+      </c>
+      <c r="J17" s="19" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="K17" s="19" t="inlineStr">
+        <is>
+          <t>Set up job</t>
+        </is>
+      </c>
       <c r="L17" s="19" t="inlineStr">
         <is>
-          <t>See GitHub Actions logs</t>
+          <t>Line 04</t>
         </is>
       </c>
       <c r="M17" s="19" t="inlineStr">
@@ -5914,7 +6329,7 @@
         </is>
       </c>
       <c r="E18" s="24" t="n">
-        <v>24027587697</v>
+        <v>24027621196</v>
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
@@ -5923,7 +6338,7 @@
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>2026-04-06T10:01:04Z</t>
+          <t>2026-04-06T10:02:12Z</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -5949,8 +6364,63 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>.github/workflows/workflow_report.yml</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>24027587697</v>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:01:04Z</t>
+        </is>
+      </c>
+      <c r="H19" s="19" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="I19" s="19" t="inlineStr">
+        <is>
+          <t>Failure (see logs)</t>
+        </is>
+      </c>
+      <c r="J19" s="19" t="inlineStr"/>
+      <c r="K19" s="19" t="inlineStr"/>
+      <c r="L19" s="19" t="inlineStr">
+        <is>
+          <t>See GitHub Actions logs</t>
+        </is>
+      </c>
+      <c r="M19" s="19" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:M18"/>
+  <autoFilter ref="A3:M19"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>

--- a/github_activity_report.xlsx
+++ b/github_activity_report.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Failure Alerts" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Activity'!$A$1:$Z$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Activity'!$A$1:$Z$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failure Summary'!$A$1:$M$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Failure Alerts'!$A$3:$M$19</definedName>
   </definedNames>
@@ -202,13 +202,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -618,7 +618,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10 16:37 UTC</t>
+          <t>2026-04-11 05:18 UTC</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 → now</t>
+          <t>2026-03-12 → now</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:Z38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -977,12 +977,12 @@
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>93bdf4123cc644f621cecd131589bff39d5376fe</t>
+          <t>c68bea9e4038cecbe103d4f97e57de3e9e0b277f</t>
         </is>
       </c>
       <c r="F2" s="15" t="inlineStr">
         <is>
-          <t>test-249</t>
+          <t>fix: correct typo in demo.txt</t>
         </is>
       </c>
       <c r="G2" s="15" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="H2" s="15" t="inlineStr">
         <is>
-          <t>2026-04-10T16:36:38Z</t>
+          <t>2026-04-11T05:17:03Z</t>
         </is>
       </c>
       <c r="I2" s="15" t="inlineStr">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="Q2" s="15" t="n">
-        <v>24253439879</v>
+        <v>24275511539</v>
       </c>
       <c r="R2" s="15" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="S2" s="15" t="inlineStr">
         <is>
-          <t>2026-04-10T16:36:56Z</t>
+          <t>2026-04-11T05:18:13Z</t>
         </is>
       </c>
       <c r="T2" s="15" t="inlineStr">
@@ -1059,22 +1059,22 @@
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>b3ea79ed073ed633f20c5321bc134cc65896c901</t>
+          <t>d8fe1f0413e72ae3882ff6057ee827a33bfc8468</t>
         </is>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>test-209</t>
+          <t>chore: update activity report [2026-04-10 16:37 UTC] (run 24253439879)</t>
         </is>
       </c>
       <c r="G3" s="16" t="inlineStr">
         <is>
-          <t>“Vidyakar”</t>
+          <t>github-actions[bot]</t>
         </is>
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>2026-04-10T16:02:48Z</t>
+          <t>2026-04-10T16:37:21Z</t>
         </is>
       </c>
       <c r="I3" s="16" t="inlineStr">
@@ -1088,34 +1088,12 @@
       <c r="M3" s="16" t="inlineStr"/>
       <c r="N3" s="16" t="inlineStr"/>
       <c r="O3" s="16" t="inlineStr"/>
-      <c r="P3" s="16" t="inlineStr">
-        <is>
-          <t>GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Q3" s="16" t="n">
-        <v>24252121271</v>
-      </c>
-      <c r="R3" s="16" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S3" s="16" t="inlineStr">
-        <is>
-          <t>2026-04-10T16:04:46Z</t>
-        </is>
-      </c>
-      <c r="T3" s="16" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="U3" s="17" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="P3" s="16" t="inlineStr"/>
+      <c r="Q3" s="16" t="inlineStr"/>
+      <c r="R3" s="16" t="inlineStr"/>
+      <c r="S3" s="16" t="inlineStr"/>
+      <c r="T3" s="16" t="inlineStr"/>
+      <c r="U3" s="16" t="inlineStr"/>
       <c r="V3" s="16" t="inlineStr"/>
       <c r="W3" s="16" t="inlineStr"/>
       <c r="X3" s="16" t="inlineStr"/>
@@ -1123,710 +1101,732 @@
       <c r="Z3" s="16" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>93bdf4123cc644f621cecd131589bff39d5376fe</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>test-249</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T16:36:38Z</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="inlineStr"/>
+      <c r="K4" s="17" t="inlineStr"/>
+      <c r="L4" s="17" t="inlineStr"/>
+      <c r="M4" s="17" t="inlineStr"/>
+      <c r="N4" s="17" t="inlineStr"/>
+      <c r="O4" s="17" t="inlineStr"/>
+      <c r="P4" s="17" t="inlineStr">
+        <is>
+          <t>GitHub Activity Report</t>
+        </is>
+      </c>
+      <c r="Q4" s="17" t="n">
+        <v>24253439879</v>
+      </c>
+      <c r="R4" s="17" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S4" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T16:36:56Z</t>
+        </is>
+      </c>
+      <c r="T4" s="17" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U4" s="18" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V4" s="17" t="inlineStr"/>
+      <c r="W4" s="17" t="inlineStr"/>
+      <c r="X4" s="17" t="inlineStr"/>
+      <c r="Y4" s="17" t="inlineStr"/>
+      <c r="Z4" s="17" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>b3ea79ed073ed633f20c5321bc134cc65896c901</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>test-209</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T16:02:48Z</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr"/>
+      <c r="K5" s="17" t="inlineStr"/>
+      <c r="L5" s="17" t="inlineStr"/>
+      <c r="M5" s="17" t="inlineStr"/>
+      <c r="N5" s="17" t="inlineStr"/>
+      <c r="O5" s="17" t="inlineStr"/>
+      <c r="P5" s="17" t="inlineStr">
+        <is>
+          <t>GitHub Activity Report</t>
+        </is>
+      </c>
+      <c r="Q5" s="17" t="n">
+        <v>24252121271</v>
+      </c>
+      <c r="R5" s="17" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S5" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T16:04:46Z</t>
+        </is>
+      </c>
+      <c r="T5" s="17" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U5" s="18" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V5" s="17" t="inlineStr"/>
+      <c r="W5" s="17" t="inlineStr"/>
+      <c r="X5" s="17" t="inlineStr"/>
+      <c r="Y5" s="17" t="inlineStr"/>
+      <c r="Z5" s="17" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>25126c83583917e6acf1c55b3b79659ece2e2368</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>test-201</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T15:26:42Z</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr"/>
-      <c r="K4" s="16" t="inlineStr"/>
-      <c r="L4" s="16" t="inlineStr"/>
-      <c r="M4" s="16" t="inlineStr"/>
-      <c r="N4" s="16" t="inlineStr"/>
-      <c r="O4" s="16" t="inlineStr"/>
-      <c r="P4" s="16" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr"/>
+      <c r="K6" s="17" t="inlineStr"/>
+      <c r="L6" s="17" t="inlineStr"/>
+      <c r="M6" s="17" t="inlineStr"/>
+      <c r="N6" s="17" t="inlineStr"/>
+      <c r="O6" s="17" t="inlineStr"/>
+      <c r="P6" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q4" s="16" t="n">
+      <c r="Q6" s="17" t="n">
         <v>24250548345</v>
       </c>
-      <c r="R4" s="16" t="inlineStr">
+      <c r="R6" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S4" s="16" t="inlineStr">
+      <c r="S6" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T15:27:44Z</t>
         </is>
       </c>
-      <c r="T4" s="16" t="inlineStr">
+      <c r="T6" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U4" s="17" t="inlineStr">
+      <c r="U6" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V4" s="16" t="inlineStr"/>
-      <c r="W4" s="16" t="inlineStr"/>
-      <c r="X4" s="16" t="inlineStr"/>
-      <c r="Y4" s="16" t="inlineStr"/>
-      <c r="Z4" s="16" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="V6" s="17" t="inlineStr"/>
+      <c r="W6" s="17" t="inlineStr"/>
+      <c r="X6" s="17" t="inlineStr"/>
+      <c r="Y6" s="17" t="inlineStr"/>
+      <c r="Z6" s="17" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>9e3c7f0f229aff7c1984cec897ef7c43ff34c5e8</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>chore: update activity report [2026-04-10 15:17 UTC] via push (run 24250086438)</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>github-actions[bot]</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T15:17:35Z</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J5" s="18" t="inlineStr"/>
-      <c r="K5" s="18" t="inlineStr"/>
-      <c r="L5" s="18" t="inlineStr"/>
-      <c r="M5" s="18" t="inlineStr"/>
-      <c r="N5" s="18" t="inlineStr"/>
-      <c r="O5" s="18" t="inlineStr"/>
-      <c r="P5" s="18" t="inlineStr"/>
-      <c r="Q5" s="18" t="inlineStr"/>
-      <c r="R5" s="18" t="inlineStr"/>
-      <c r="S5" s="18" t="inlineStr"/>
-      <c r="T5" s="18" t="inlineStr"/>
-      <c r="U5" s="18" t="inlineStr"/>
-      <c r="V5" s="18" t="inlineStr"/>
-      <c r="W5" s="18" t="inlineStr"/>
-      <c r="X5" s="18" t="inlineStr"/>
-      <c r="Y5" s="18" t="inlineStr"/>
-      <c r="Z5" s="18" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr"/>
+      <c r="K7" s="16" t="inlineStr"/>
+      <c r="L7" s="16" t="inlineStr"/>
+      <c r="M7" s="16" t="inlineStr"/>
+      <c r="N7" s="16" t="inlineStr"/>
+      <c r="O7" s="16" t="inlineStr"/>
+      <c r="P7" s="16" t="inlineStr"/>
+      <c r="Q7" s="16" t="inlineStr"/>
+      <c r="R7" s="16" t="inlineStr"/>
+      <c r="S7" s="16" t="inlineStr"/>
+      <c r="T7" s="16" t="inlineStr"/>
+      <c r="U7" s="16" t="inlineStr"/>
+      <c r="V7" s="16" t="inlineStr"/>
+      <c r="W7" s="16" t="inlineStr"/>
+      <c r="X7" s="16" t="inlineStr"/>
+      <c r="Y7" s="16" t="inlineStr"/>
+      <c r="Z7" s="16" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>0bf36a490d78a4819928a11161d34bda33e4f337</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>test-200</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H6" s="19" t="inlineStr">
+      <c r="H8" s="19" t="inlineStr">
         <is>
           <t>2026-04-10T15:16:43Z</t>
         </is>
       </c>
-      <c r="I6" s="19" t="inlineStr">
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J6" s="19" t="inlineStr"/>
-      <c r="K6" s="19" t="inlineStr"/>
-      <c r="L6" s="19" t="inlineStr"/>
-      <c r="M6" s="19" t="inlineStr"/>
-      <c r="N6" s="19" t="inlineStr"/>
-      <c r="O6" s="19" t="inlineStr"/>
-      <c r="P6" s="19" t="inlineStr">
+      <c r="J8" s="19" t="inlineStr"/>
+      <c r="K8" s="19" t="inlineStr"/>
+      <c r="L8" s="19" t="inlineStr"/>
+      <c r="M8" s="19" t="inlineStr"/>
+      <c r="N8" s="19" t="inlineStr"/>
+      <c r="O8" s="19" t="inlineStr"/>
+      <c r="P8" s="19" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q6" s="19" t="n">
+      <c r="Q8" s="19" t="n">
         <v>24250086438</v>
       </c>
-      <c r="R6" s="19" t="inlineStr">
+      <c r="R8" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S6" s="19" t="inlineStr">
+      <c r="S8" s="19" t="inlineStr">
         <is>
           <t>2026-04-10T15:18:50Z</t>
         </is>
       </c>
-      <c r="T6" s="19" t="inlineStr">
+      <c r="T8" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U6" s="20" t="inlineStr">
+      <c r="U8" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="V6" s="19" t="inlineStr">
+      <c r="V8" s="19" t="inlineStr">
         <is>
           <t>Job 'generate_report' step 'Commit and push report to repository' failed — 2026-04-10T15:19:10.4298620Z 15:19:10  WARNING   WORKFLOW FAILURE in vidyakar-whitedev/git-report  (Run ID: 24030846379)</t>
         </is>
       </c>
-      <c r="W6" s="19" t="inlineStr">
+      <c r="W8" s="19" t="inlineStr">
         <is>
           <t>generate_report</t>
         </is>
       </c>
-      <c r="X6" s="19" t="inlineStr">
+      <c r="X8" s="19" t="inlineStr">
         <is>
           <t>Commit and push report to repository</t>
         </is>
       </c>
-      <c r="Y6" s="19" t="inlineStr">
+      <c r="Y8" s="19" t="inlineStr">
         <is>
           <t>Line 19</t>
         </is>
       </c>
-      <c r="Z6" s="19" t="inlineStr">
+      <c r="Z8" s="19" t="inlineStr">
         <is>
           <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>4744a63d54822fd75d284791aa8b6524acb33646</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>chore: update activity report [2026-04-10 14:39 UTC] via push (run 24248391662)</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>github-actions[bot]</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T14:39:22Z</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr"/>
-      <c r="K7" s="18" t="inlineStr"/>
-      <c r="L7" s="18" t="inlineStr"/>
-      <c r="M7" s="18" t="inlineStr"/>
-      <c r="N7" s="18" t="inlineStr"/>
-      <c r="O7" s="18" t="inlineStr"/>
-      <c r="P7" s="18" t="inlineStr"/>
-      <c r="Q7" s="18" t="inlineStr"/>
-      <c r="R7" s="18" t="inlineStr"/>
-      <c r="S7" s="18" t="inlineStr"/>
-      <c r="T7" s="18" t="inlineStr"/>
-      <c r="U7" s="18" t="inlineStr"/>
-      <c r="V7" s="18" t="inlineStr"/>
-      <c r="W7" s="18" t="inlineStr"/>
-      <c r="X7" s="18" t="inlineStr"/>
-      <c r="Y7" s="18" t="inlineStr"/>
-      <c r="Z7" s="18" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr"/>
+      <c r="K9" s="16" t="inlineStr"/>
+      <c r="L9" s="16" t="inlineStr"/>
+      <c r="M9" s="16" t="inlineStr"/>
+      <c r="N9" s="16" t="inlineStr"/>
+      <c r="O9" s="16" t="inlineStr"/>
+      <c r="P9" s="16" t="inlineStr"/>
+      <c r="Q9" s="16" t="inlineStr"/>
+      <c r="R9" s="16" t="inlineStr"/>
+      <c r="S9" s="16" t="inlineStr"/>
+      <c r="T9" s="16" t="inlineStr"/>
+      <c r="U9" s="16" t="inlineStr"/>
+      <c r="V9" s="16" t="inlineStr"/>
+      <c r="W9" s="16" t="inlineStr"/>
+      <c r="X9" s="16" t="inlineStr"/>
+      <c r="Y9" s="16" t="inlineStr"/>
+      <c r="Z9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>408ddd043c24815f4498a813c6ca81c4e9688b9b</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>test-198</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T14:38:25Z</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr"/>
-      <c r="K8" s="16" t="inlineStr"/>
-      <c r="L8" s="16" t="inlineStr"/>
-      <c r="M8" s="16" t="inlineStr"/>
-      <c r="N8" s="16" t="inlineStr"/>
-      <c r="O8" s="16" t="inlineStr"/>
-      <c r="P8" s="16" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr"/>
+      <c r="K10" s="17" t="inlineStr"/>
+      <c r="L10" s="17" t="inlineStr"/>
+      <c r="M10" s="17" t="inlineStr"/>
+      <c r="N10" s="17" t="inlineStr"/>
+      <c r="O10" s="17" t="inlineStr"/>
+      <c r="P10" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q8" s="16" t="n">
+      <c r="Q10" s="17" t="n">
         <v>24248391662</v>
       </c>
-      <c r="R8" s="16" t="inlineStr">
+      <c r="R10" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S8" s="16" t="inlineStr">
+      <c r="S10" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T14:38:48Z</t>
         </is>
       </c>
-      <c r="T8" s="16" t="inlineStr">
+      <c r="T10" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U8" s="17" t="inlineStr">
+      <c r="U10" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V8" s="16" t="inlineStr"/>
-      <c r="W8" s="16" t="inlineStr"/>
-      <c r="X8" s="16" t="inlineStr"/>
-      <c r="Y8" s="16" t="inlineStr"/>
-      <c r="Z8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="V10" s="17" t="inlineStr"/>
+      <c r="W10" s="17" t="inlineStr"/>
+      <c r="X10" s="17" t="inlineStr"/>
+      <c r="Y10" s="17" t="inlineStr"/>
+      <c r="Z10" s="17" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>37f60b0c23d45eef199630a384945ef73970b8d7</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>chore: update activity report [2026-04-10 09:44 UTC] via push (run 24236872105)</t>
         </is>
       </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>github-actions[bot]</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>2026-04-10T09:44:03Z</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr"/>
-      <c r="K9" s="18" t="inlineStr"/>
-      <c r="L9" s="18" t="inlineStr"/>
-      <c r="M9" s="18" t="inlineStr"/>
-      <c r="N9" s="18" t="inlineStr"/>
-      <c r="O9" s="18" t="inlineStr"/>
-      <c r="P9" s="18" t="inlineStr"/>
-      <c r="Q9" s="18" t="inlineStr"/>
-      <c r="R9" s="18" t="inlineStr"/>
-      <c r="S9" s="18" t="inlineStr"/>
-      <c r="T9" s="18" t="inlineStr"/>
-      <c r="U9" s="18" t="inlineStr"/>
-      <c r="V9" s="18" t="inlineStr"/>
-      <c r="W9" s="18" t="inlineStr"/>
-      <c r="X9" s="18" t="inlineStr"/>
-      <c r="Y9" s="18" t="inlineStr"/>
-      <c r="Z9" s="18" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="J11" s="16" t="inlineStr"/>
+      <c r="K11" s="16" t="inlineStr"/>
+      <c r="L11" s="16" t="inlineStr"/>
+      <c r="M11" s="16" t="inlineStr"/>
+      <c r="N11" s="16" t="inlineStr"/>
+      <c r="O11" s="16" t="inlineStr"/>
+      <c r="P11" s="16" t="inlineStr"/>
+      <c r="Q11" s="16" t="inlineStr"/>
+      <c r="R11" s="16" t="inlineStr"/>
+      <c r="S11" s="16" t="inlineStr"/>
+      <c r="T11" s="16" t="inlineStr"/>
+      <c r="U11" s="16" t="inlineStr"/>
+      <c r="V11" s="16" t="inlineStr"/>
+      <c r="W11" s="16" t="inlineStr"/>
+      <c r="X11" s="16" t="inlineStr"/>
+      <c r="Y11" s="16" t="inlineStr"/>
+      <c r="Z11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>aac0b4a033d6b371042ec3f99a213aa53e5d925f</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>test-198</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T09:40:50Z</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr"/>
-      <c r="K10" s="16" t="inlineStr"/>
-      <c r="L10" s="16" t="inlineStr"/>
-      <c r="M10" s="16" t="inlineStr"/>
-      <c r="N10" s="16" t="inlineStr"/>
-      <c r="O10" s="16" t="inlineStr"/>
-      <c r="P10" s="16" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr"/>
+      <c r="K12" s="17" t="inlineStr"/>
+      <c r="L12" s="17" t="inlineStr"/>
+      <c r="M12" s="17" t="inlineStr"/>
+      <c r="N12" s="17" t="inlineStr"/>
+      <c r="O12" s="17" t="inlineStr"/>
+      <c r="P12" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q10" s="16" t="n">
+      <c r="Q12" s="17" t="n">
         <v>24236872105</v>
       </c>
-      <c r="R10" s="16" t="inlineStr">
+      <c r="R12" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S10" s="16" t="inlineStr">
+      <c r="S12" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T09:43:38Z</t>
         </is>
       </c>
-      <c r="T10" s="16" t="inlineStr">
+      <c r="T12" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U10" s="17" t="inlineStr">
+      <c r="U12" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V10" s="16" t="inlineStr"/>
-      <c r="W10" s="16" t="inlineStr"/>
-      <c r="X10" s="16" t="inlineStr"/>
-      <c r="Y10" s="16" t="inlineStr"/>
-      <c r="Z10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>19b0e6e1eadc37093a80d5aa3b43d47cf52cc739</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>chore: update activity report [2026-04-10 09:36 UTC] via push (run 24236579665)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>github-actions[bot]</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>2026-04-10T09:36:36Z</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="J11" s="18" t="inlineStr"/>
-      <c r="K11" s="18" t="inlineStr"/>
-      <c r="L11" s="18" t="inlineStr"/>
-      <c r="M11" s="18" t="inlineStr"/>
-      <c r="N11" s="18" t="inlineStr"/>
-      <c r="O11" s="18" t="inlineStr"/>
-      <c r="P11" s="18" t="inlineStr"/>
-      <c r="Q11" s="18" t="inlineStr"/>
-      <c r="R11" s="18" t="inlineStr"/>
-      <c r="S11" s="18" t="inlineStr"/>
-      <c r="T11" s="18" t="inlineStr"/>
-      <c r="U11" s="18" t="inlineStr"/>
-      <c r="V11" s="18" t="inlineStr"/>
-      <c r="W11" s="18" t="inlineStr"/>
-      <c r="X11" s="18" t="inlineStr"/>
-      <c r="Y11" s="18" t="inlineStr"/>
-      <c r="Z11" s="18" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>4246e5f5bdd0c663224514d45c37457253e6806b</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>test-13</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>2026-04-10T09:35:54Z</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr"/>
-      <c r="K12" s="16" t="inlineStr"/>
-      <c r="L12" s="16" t="inlineStr"/>
-      <c r="M12" s="16" t="inlineStr"/>
-      <c r="N12" s="16" t="inlineStr"/>
-      <c r="O12" s="16" t="inlineStr"/>
-      <c r="P12" s="16" t="inlineStr">
-        <is>
-          <t>GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Q12" s="16" t="n">
-        <v>24236579665</v>
-      </c>
-      <c r="R12" s="16" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S12" s="16" t="inlineStr">
-        <is>
-          <t>2026-04-10T09:36:01Z</t>
-        </is>
-      </c>
-      <c r="T12" s="16" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="U12" s="17" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="V12" s="16" t="inlineStr"/>
-      <c r="W12" s="16" t="inlineStr"/>
-      <c r="X12" s="16" t="inlineStr"/>
-      <c r="Y12" s="16" t="inlineStr"/>
-      <c r="Z12" s="16" t="inlineStr"/>
+      <c r="V12" s="17" t="inlineStr"/>
+      <c r="W12" s="17" t="inlineStr"/>
+      <c r="X12" s="17" t="inlineStr"/>
+      <c r="Y12" s="17" t="inlineStr"/>
+      <c r="Z12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -1851,22 +1851,22 @@
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>ff12234265b7ed9747283a1b59735ea5ddda19b5</t>
+          <t>19b0e6e1eadc37093a80d5aa3b43d47cf52cc739</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>test-12</t>
+          <t>chore: update activity report [2026-04-10 09:36 UTC] via push (run 24236579665)</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
         <is>
-          <t>“Vidyakar”</t>
+          <t>github-actions[bot]</t>
         </is>
       </c>
       <c r="H13" s="16" t="inlineStr">
         <is>
-          <t>2026-04-10T09:21:24Z</t>
+          <t>2026-04-10T09:36:36Z</t>
         </is>
       </c>
       <c r="I13" s="16" t="inlineStr">
@@ -1880,34 +1880,12 @@
       <c r="M13" s="16" t="inlineStr"/>
       <c r="N13" s="16" t="inlineStr"/>
       <c r="O13" s="16" t="inlineStr"/>
-      <c r="P13" s="16" t="inlineStr">
-        <is>
-          <t>GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Q13" s="16" t="n">
-        <v>24236015736</v>
-      </c>
-      <c r="R13" s="16" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S13" s="16" t="inlineStr">
-        <is>
-          <t>2026-04-10T09:21:36Z</t>
-        </is>
-      </c>
-      <c r="T13" s="16" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="U13" s="17" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="P13" s="16" t="inlineStr"/>
+      <c r="Q13" s="16" t="inlineStr"/>
+      <c r="R13" s="16" t="inlineStr"/>
+      <c r="S13" s="16" t="inlineStr"/>
+      <c r="T13" s="16" t="inlineStr"/>
+      <c r="U13" s="16" t="inlineStr"/>
       <c r="V13" s="16" t="inlineStr"/>
       <c r="W13" s="16" t="inlineStr"/>
       <c r="X13" s="16" t="inlineStr"/>
@@ -1915,732 +1893,692 @@
       <c r="Z13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>4246e5f5bdd0c663224514d45c37457253e6806b</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>test-13</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T09:35:54Z</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J14" s="17" t="inlineStr"/>
+      <c r="K14" s="17" t="inlineStr"/>
+      <c r="L14" s="17" t="inlineStr"/>
+      <c r="M14" s="17" t="inlineStr"/>
+      <c r="N14" s="17" t="inlineStr"/>
+      <c r="O14" s="17" t="inlineStr"/>
+      <c r="P14" s="17" t="inlineStr">
+        <is>
+          <t>GitHub Activity Report</t>
+        </is>
+      </c>
+      <c r="Q14" s="17" t="n">
+        <v>24236579665</v>
+      </c>
+      <c r="R14" s="17" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S14" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T09:36:01Z</t>
+        </is>
+      </c>
+      <c r="T14" s="17" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U14" s="18" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V14" s="17" t="inlineStr"/>
+      <c r="W14" s="17" t="inlineStr"/>
+      <c r="X14" s="17" t="inlineStr"/>
+      <c r="Y14" s="17" t="inlineStr"/>
+      <c r="Z14" s="17" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>ff12234265b7ed9747283a1b59735ea5ddda19b5</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>test-12</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>“Vidyakar”</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T09:21:24Z</t>
+        </is>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="J15" s="17" t="inlineStr"/>
+      <c r="K15" s="17" t="inlineStr"/>
+      <c r="L15" s="17" t="inlineStr"/>
+      <c r="M15" s="17" t="inlineStr"/>
+      <c r="N15" s="17" t="inlineStr"/>
+      <c r="O15" s="17" t="inlineStr"/>
+      <c r="P15" s="17" t="inlineStr">
+        <is>
+          <t>GitHub Activity Report</t>
+        </is>
+      </c>
+      <c r="Q15" s="17" t="n">
+        <v>24236015736</v>
+      </c>
+      <c r="R15" s="17" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S15" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10T09:21:36Z</t>
+        </is>
+      </c>
+      <c r="T15" s="17" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U15" s="18" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V15" s="17" t="inlineStr"/>
+      <c r="W15" s="17" t="inlineStr"/>
+      <c r="X15" s="17" t="inlineStr"/>
+      <c r="Y15" s="17" t="inlineStr"/>
+      <c r="Z15" s="17" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>75732834dd766afc090c808510eb71c7693015dd</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>test-8</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T08:35:13Z</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr"/>
-      <c r="K14" s="16" t="inlineStr"/>
-      <c r="L14" s="16" t="inlineStr"/>
-      <c r="M14" s="16" t="inlineStr"/>
-      <c r="N14" s="16" t="inlineStr"/>
-      <c r="O14" s="16" t="inlineStr"/>
-      <c r="P14" s="16" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr"/>
+      <c r="K16" s="17" t="inlineStr"/>
+      <c r="L16" s="17" t="inlineStr"/>
+      <c r="M16" s="17" t="inlineStr"/>
+      <c r="N16" s="17" t="inlineStr"/>
+      <c r="O16" s="17" t="inlineStr"/>
+      <c r="P16" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q14" s="16" t="n">
+      <c r="Q16" s="17" t="n">
         <v>24234243976</v>
       </c>
-      <c r="R14" s="16" t="inlineStr">
+      <c r="R16" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S14" s="16" t="inlineStr">
+      <c r="S16" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T08:35:20Z</t>
         </is>
       </c>
-      <c r="T14" s="16" t="inlineStr">
+      <c r="T16" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U14" s="17" t="inlineStr">
+      <c r="U16" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V14" s="16" t="inlineStr"/>
-      <c r="W14" s="16" t="inlineStr"/>
-      <c r="X14" s="16" t="inlineStr"/>
-      <c r="Y14" s="16" t="inlineStr"/>
-      <c r="Z14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="V16" s="17" t="inlineStr"/>
+      <c r="W16" s="17" t="inlineStr"/>
+      <c r="X16" s="17" t="inlineStr"/>
+      <c r="Y16" s="17" t="inlineStr"/>
+      <c r="Z16" s="17" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>9d220c5657c48c13ca17102c507b756edbba9215</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>test-8</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T08:32:22Z</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr"/>
-      <c r="M15" s="16" t="inlineStr"/>
-      <c r="N15" s="16" t="inlineStr"/>
-      <c r="O15" s="16" t="inlineStr"/>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="J17" s="17" t="inlineStr"/>
+      <c r="K17" s="17" t="inlineStr"/>
+      <c r="L17" s="17" t="inlineStr"/>
+      <c r="M17" s="17" t="inlineStr"/>
+      <c r="N17" s="17" t="inlineStr"/>
+      <c r="O17" s="17" t="inlineStr"/>
+      <c r="P17" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q15" s="16" t="n">
+      <c r="Q17" s="17" t="n">
         <v>24234135440</v>
       </c>
-      <c r="R15" s="16" t="inlineStr">
+      <c r="R17" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S15" s="16" t="inlineStr">
+      <c r="S17" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T08:32:30Z</t>
         </is>
       </c>
-      <c r="T15" s="16" t="inlineStr">
+      <c r="T17" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U15" s="17" t="inlineStr">
+      <c r="U17" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V15" s="16" t="inlineStr"/>
-      <c r="W15" s="16" t="inlineStr"/>
-      <c r="X15" s="16" t="inlineStr"/>
-      <c r="Y15" s="16" t="inlineStr"/>
-      <c r="Z15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="V17" s="17" t="inlineStr"/>
+      <c r="W17" s="17" t="inlineStr"/>
+      <c r="X17" s="17" t="inlineStr"/>
+      <c r="Y17" s="17" t="inlineStr"/>
+      <c r="Z17" s="17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>981fe60621c98393750f79dd815a0ea7e4aed75e</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>test-8</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T08:27:06Z</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr"/>
-      <c r="K16" s="16" t="inlineStr"/>
-      <c r="L16" s="16" t="inlineStr"/>
-      <c r="M16" s="16" t="inlineStr"/>
-      <c r="N16" s="16" t="inlineStr"/>
-      <c r="O16" s="16" t="inlineStr"/>
-      <c r="P16" s="16" t="inlineStr">
+      <c r="J18" s="17" t="inlineStr"/>
+      <c r="K18" s="17" t="inlineStr"/>
+      <c r="L18" s="17" t="inlineStr"/>
+      <c r="M18" s="17" t="inlineStr"/>
+      <c r="N18" s="17" t="inlineStr"/>
+      <c r="O18" s="17" t="inlineStr"/>
+      <c r="P18" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q16" s="16" t="n">
+      <c r="Q18" s="17" t="n">
         <v>24233936358</v>
       </c>
-      <c r="R16" s="16" t="inlineStr">
+      <c r="R18" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S16" s="16" t="inlineStr">
+      <c r="S18" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T08:27:14Z</t>
         </is>
       </c>
-      <c r="T16" s="16" t="inlineStr">
+      <c r="T18" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U16" s="17" t="inlineStr">
+      <c r="U18" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V16" s="16" t="inlineStr"/>
-      <c r="W16" s="16" t="inlineStr"/>
-      <c r="X16" s="16" t="inlineStr"/>
-      <c r="Y16" s="16" t="inlineStr"/>
-      <c r="Z16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="V18" s="17" t="inlineStr"/>
+      <c r="W18" s="17" t="inlineStr"/>
+      <c r="X18" s="17" t="inlineStr"/>
+      <c r="Y18" s="17" t="inlineStr"/>
+      <c r="Z18" s="17" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>3cfdf96375ed8ea8c83b95f26b9c87428b8bc8b9</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>test-1</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T08:18:15Z</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr"/>
-      <c r="K17" s="16" t="inlineStr"/>
-      <c r="L17" s="16" t="inlineStr"/>
-      <c r="M17" s="16" t="inlineStr"/>
-      <c r="N17" s="16" t="inlineStr"/>
-      <c r="O17" s="16" t="inlineStr"/>
-      <c r="P17" s="16" t="inlineStr">
+      <c r="J19" s="17" t="inlineStr"/>
+      <c r="K19" s="17" t="inlineStr"/>
+      <c r="L19" s="17" t="inlineStr"/>
+      <c r="M19" s="17" t="inlineStr"/>
+      <c r="N19" s="17" t="inlineStr"/>
+      <c r="O19" s="17" t="inlineStr"/>
+      <c r="P19" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q17" s="16" t="n">
+      <c r="Q19" s="17" t="n">
         <v>24233616319</v>
       </c>
-      <c r="R17" s="16" t="inlineStr">
+      <c r="R19" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S17" s="16" t="inlineStr">
+      <c r="S19" s="17" t="inlineStr">
         <is>
           <t>2026-04-10T08:18:28Z</t>
         </is>
       </c>
-      <c r="T17" s="16" t="inlineStr">
+      <c r="T19" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U17" s="17" t="inlineStr">
+      <c r="U19" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V17" s="16" t="inlineStr"/>
-      <c r="W17" s="16" t="inlineStr"/>
-      <c r="X17" s="16" t="inlineStr"/>
-      <c r="Y17" s="16" t="inlineStr"/>
-      <c r="Z17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="V19" s="17" t="inlineStr"/>
+      <c r="W19" s="17" t="inlineStr"/>
+      <c r="X19" s="17" t="inlineStr"/>
+      <c r="Y19" s="17" t="inlineStr"/>
+      <c r="Z19" s="17" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>ad211e0513d37204ee54168120dec41978cc6fb4</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>new code change</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>2026-04-06T15:32:05Z</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr"/>
-      <c r="K18" s="16" t="inlineStr"/>
-      <c r="L18" s="16" t="inlineStr"/>
-      <c r="M18" s="16" t="inlineStr"/>
-      <c r="N18" s="16" t="inlineStr"/>
-      <c r="O18" s="16" t="inlineStr"/>
-      <c r="P18" s="16" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr"/>
+      <c r="K20" s="17" t="inlineStr"/>
+      <c r="L20" s="17" t="inlineStr"/>
+      <c r="M20" s="17" t="inlineStr"/>
+      <c r="N20" s="17" t="inlineStr"/>
+      <c r="O20" s="17" t="inlineStr"/>
+      <c r="P20" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q18" s="16" t="n">
+      <c r="Q20" s="17" t="n">
         <v>24038137070</v>
       </c>
-      <c r="R18" s="16" t="inlineStr">
+      <c r="R20" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S18" s="16" t="inlineStr">
+      <c r="S20" s="17" t="inlineStr">
         <is>
           <t>2026-04-06T15:32:18Z</t>
         </is>
       </c>
-      <c r="T18" s="16" t="inlineStr">
+      <c r="T20" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U18" s="17" t="inlineStr">
+      <c r="U20" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V18" s="16" t="inlineStr"/>
-      <c r="W18" s="16" t="inlineStr"/>
-      <c r="X18" s="16" t="inlineStr"/>
-      <c r="Y18" s="16" t="inlineStr"/>
-      <c r="Z18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="V20" s="17" t="inlineStr"/>
+      <c r="W20" s="17" t="inlineStr"/>
+      <c r="X20" s="17" t="inlineStr"/>
+      <c r="Y20" s="17" t="inlineStr"/>
+      <c r="Z20" s="17" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>21f8e2bcc8765be2c9dd97d0d839686b7afe3de1</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>new code change</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>“Vidyakar”</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>2026-04-06T12:24:00Z</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr"/>
-      <c r="K19" s="16" t="inlineStr"/>
-      <c r="L19" s="16" t="inlineStr"/>
-      <c r="M19" s="16" t="inlineStr"/>
-      <c r="N19" s="16" t="inlineStr"/>
-      <c r="O19" s="16" t="inlineStr"/>
-      <c r="P19" s="16" t="inlineStr">
+      <c r="J21" s="17" t="inlineStr"/>
+      <c r="K21" s="17" t="inlineStr"/>
+      <c r="L21" s="17" t="inlineStr"/>
+      <c r="M21" s="17" t="inlineStr"/>
+      <c r="N21" s="17" t="inlineStr"/>
+      <c r="O21" s="17" t="inlineStr"/>
+      <c r="P21" s="17" t="inlineStr">
         <is>
           <t>GitHub Activity Report</t>
         </is>
       </c>
-      <c r="Q19" s="16" t="n">
+      <c r="Q21" s="17" t="n">
         <v>24031673216</v>
       </c>
-      <c r="R19" s="16" t="inlineStr">
+      <c r="R21" s="17" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S19" s="16" t="inlineStr">
+      <c r="S21" s="17" t="inlineStr">
         <is>
           <t>2026-04-06T12:24:13Z</t>
         </is>
       </c>
-      <c r="T19" s="16" t="inlineStr">
+      <c r="T21" s="17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U19" s="17" t="inlineStr">
+      <c r="U21" s="18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="V19" s="16" t="inlineStr"/>
-      <c r="W19" s="16" t="inlineStr"/>
-      <c r="X19" s="16" t="inlineStr"/>
-      <c r="Y19" s="16" t="inlineStr"/>
-      <c r="Z19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>code changed1</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>2026-04-06T11:54:44Z</t>
-        </is>
-      </c>
-      <c r="I20" s="19" t="inlineStr">
-        <is>
-          <t>git-report-poc2</t>
-        </is>
-      </c>
-      <c r="J20" s="19" t="inlineStr"/>
-      <c r="K20" s="19" t="inlineStr"/>
-      <c r="L20" s="19" t="inlineStr"/>
-      <c r="M20" s="19" t="inlineStr"/>
-      <c r="N20" s="19" t="inlineStr"/>
-      <c r="O20" s="19" t="inlineStr"/>
-      <c r="P20" s="19" t="inlineStr">
-        <is>
-          <t>GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="Q20" s="19" t="n">
-        <v>24030846379</v>
-      </c>
-      <c r="R20" s="19" t="inlineStr">
-        <is>
-          <t>workflow_dispatch</t>
-        </is>
-      </c>
-      <c r="S20" s="19" t="inlineStr">
-        <is>
-          <t>2026-04-06T11:55:45Z</t>
-        </is>
-      </c>
-      <c r="T20" s="19" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="U20" s="20" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="V20" s="19" t="inlineStr">
-        <is>
-          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
-        </is>
-      </c>
-      <c r="W20" s="19" t="inlineStr">
-        <is>
-          <t>generate_report</t>
-        </is>
-      </c>
-      <c r="X20" s="19" t="inlineStr">
-        <is>
-          <t>Run GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Y20" s="19" t="inlineStr">
-        <is>
-          <t>Line 56</t>
-        </is>
-      </c>
-      <c r="Z20" s="19" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>code changed1</t>
-        </is>
-      </c>
-      <c r="G21" s="19" t="inlineStr">
-        <is>
-          <t>“Vidyakar”</t>
-        </is>
-      </c>
-      <c r="H21" s="19" t="inlineStr">
-        <is>
-          <t>2026-04-06T11:54:44Z</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>git-report-poc2</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr"/>
-      <c r="K21" s="19" t="inlineStr"/>
-      <c r="L21" s="19" t="inlineStr"/>
-      <c r="M21" s="19" t="inlineStr"/>
-      <c r="N21" s="19" t="inlineStr"/>
-      <c r="O21" s="19" t="inlineStr"/>
-      <c r="P21" s="19" t="inlineStr">
-        <is>
-          <t>GitHub Workflow Report</t>
-        </is>
-      </c>
-      <c r="Q21" s="19" t="n">
-        <v>24030820444</v>
-      </c>
-      <c r="R21" s="19" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="S21" s="19" t="inlineStr">
-        <is>
-          <t>2026-04-06T11:54:51Z</t>
-        </is>
-      </c>
-      <c r="T21" s="19" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="U21" s="20" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="V21" s="19" t="inlineStr">
-        <is>
-          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
-        </is>
-      </c>
-      <c r="W21" s="19" t="inlineStr">
-        <is>
-          <t>generate_report</t>
-        </is>
-      </c>
-      <c r="X21" s="19" t="inlineStr">
-        <is>
-          <t>Run GitHub Activity Report</t>
-        </is>
-      </c>
-      <c r="Y21" s="19" t="inlineStr">
-        <is>
-          <t>Line 55</t>
-        </is>
-      </c>
-      <c r="Z21" s="19" t="inlineStr">
-        <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
-        </is>
-      </c>
+      <c r="V21" s="17" t="inlineStr"/>
+      <c r="W21" s="17" t="inlineStr"/>
+      <c r="X21" s="17" t="inlineStr"/>
+      <c r="Y21" s="17" t="inlineStr"/>
+      <c r="Z21" s="17" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
@@ -2665,12 +2603,12 @@
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>733b89967b9b4731953302840f2ddb2c20bedf56</t>
+          <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>code changed</t>
+          <t>code changed1</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
@@ -2680,7 +2618,7 @@
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:52:40Z</t>
+          <t>2026-04-06T11:54:44Z</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
@@ -2700,16 +2638,16 @@
         </is>
       </c>
       <c r="Q22" s="19" t="n">
-        <v>24029078530</v>
+        <v>24030846379</v>
       </c>
       <c r="R22" s="19" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>workflow_dispatch</t>
         </is>
       </c>
       <c r="S22" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:52:49Z</t>
+          <t>2026-04-06T11:55:45Z</t>
         </is>
       </c>
       <c r="T22" s="19" t="inlineStr">
@@ -2724,7 +2662,7 @@
       </c>
       <c r="V22" s="19" t="inlineStr">
         <is>
-          <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:56:06.4378556Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="W22" s="19" t="inlineStr">
@@ -2734,12 +2672,12 @@
       </c>
       <c r="X22" s="19" t="inlineStr">
         <is>
-          <t>Set up job</t>
+          <t>Run GitHub Activity Report</t>
         </is>
       </c>
       <c r="Y22" s="19" t="inlineStr">
         <is>
-          <t>Line 52</t>
+          <t>Line 56</t>
         </is>
       </c>
       <c r="Z22" s="19" t="inlineStr">
@@ -2771,12 +2709,12 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>aedf77ebc8e0433ebbe37ca97908ee5caf3929d6</t>
+          <t>5b2c09128fdfda0f63e1f6188832caa277f2af4b</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>code changd</t>
+          <t>code changed1</t>
         </is>
       </c>
       <c r="G23" s="19" t="inlineStr">
@@ -2786,7 +2724,7 @@
       </c>
       <c r="H23" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:44:38Z</t>
+          <t>2026-04-06T11:54:44Z</t>
         </is>
       </c>
       <c r="I23" s="19" t="inlineStr">
@@ -2806,7 +2744,7 @@
         </is>
       </c>
       <c r="Q23" s="19" t="n">
-        <v>24028853853</v>
+        <v>24030820444</v>
       </c>
       <c r="R23" s="19" t="inlineStr">
         <is>
@@ -2815,7 +2753,7 @@
       </c>
       <c r="S23" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:44:47Z</t>
+          <t>2026-04-06T11:54:51Z</t>
         </is>
       </c>
       <c r="T23" s="19" t="inlineStr">
@@ -2830,27 +2768,27 @@
       </c>
       <c r="V23" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
+          <t>Job 'generate_report' step 'Run GitHub Activity Report' failed — 2026-04-06T11:55:12.8179279Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="W23" s="19" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>generate_report</t>
         </is>
       </c>
       <c r="X23" s="19" t="inlineStr">
         <is>
-          <t>Run GitHub Workflow Report</t>
+          <t>Run GitHub Activity Report</t>
         </is>
       </c>
       <c r="Y23" s="19" t="inlineStr">
         <is>
-          <t>Line 45</t>
+          <t>Line 55</t>
         </is>
       </c>
       <c r="Z23" s="19" t="inlineStr">
         <is>
-          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
@@ -2877,22 +2815,22 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>5feb9eb868fd9ff9e4a7150d13cb3252d843c106</t>
+          <t>733b89967b9b4731953302840f2ddb2c20bedf56</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>Update demo.txt</t>
+          <t>code changed</t>
         </is>
       </c>
       <c r="G24" s="19" t="inlineStr">
         <is>
-          <t>vidyakar-whitedev</t>
+          <t>“Vidyakar”</t>
         </is>
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:31:56Z</t>
+          <t>2026-04-06T10:52:40Z</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
@@ -2912,7 +2850,7 @@
         </is>
       </c>
       <c r="Q24" s="19" t="n">
-        <v>24028486557</v>
+        <v>24029078530</v>
       </c>
       <c r="R24" s="19" t="inlineStr">
         <is>
@@ -2921,7 +2859,7 @@
       </c>
       <c r="S24" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:39:17Z</t>
+          <t>2026-04-06T10:52:49Z</t>
         </is>
       </c>
       <c r="T24" s="19" t="inlineStr">
@@ -2936,22 +2874,22 @@
       </c>
       <c r="V24" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
+          <t>Job 'generate_report' step 'Set up job' failed — 2026-04-06T10:52:53.8436108Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
         </is>
       </c>
       <c r="W24" s="19" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>generate_report</t>
         </is>
       </c>
       <c r="X24" s="19" t="inlineStr">
         <is>
-          <t>Run GitHub Workflow Report</t>
+          <t>Set up job</t>
         </is>
       </c>
       <c r="Y24" s="19" t="inlineStr">
         <is>
-          <t>Line 39</t>
+          <t>Line 52</t>
         </is>
       </c>
       <c r="Z24" s="19" t="inlineStr">
@@ -2983,12 +2921,12 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>2fcbd831207ea4821a39ee88d33aa21454ca19e3</t>
+          <t>aedf77ebc8e0433ebbe37ca97908ee5caf3929d6</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>code changed@v1</t>
+          <t>code changd</t>
         </is>
       </c>
       <c r="G25" s="19" t="inlineStr">
@@ -2998,7 +2936,7 @@
       </c>
       <c r="H25" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:28:57Z</t>
+          <t>2026-04-06T10:44:38Z</t>
         </is>
       </c>
       <c r="I25" s="19" t="inlineStr">
@@ -3018,7 +2956,7 @@
         </is>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>24028398959</v>
+        <v>24028853853</v>
       </c>
       <c r="R25" s="19" t="inlineStr">
         <is>
@@ -3027,7 +2965,7 @@
       </c>
       <c r="S25" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:29:06Z</t>
+          <t>2026-04-06T10:44:47Z</t>
         </is>
       </c>
       <c r="T25" s="19" t="inlineStr">
@@ -3042,7 +2980,7 @@
       </c>
       <c r="V25" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:45:06.2894428Z ERROR: No repositories found. Check GH_ORG value and token permissions.</t>
         </is>
       </c>
       <c r="W25" s="19" t="inlineStr">
@@ -3057,7 +2995,7 @@
       </c>
       <c r="Y25" s="19" t="inlineStr">
         <is>
-          <t>Line 29</t>
+          <t>Line 45</t>
         </is>
       </c>
       <c r="Z25" s="19" t="inlineStr">
@@ -3089,22 +3027,22 @@
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>37ddfe095b13b5e65a98ff2072c4bbb77cde7c1b</t>
+          <t>5feb9eb868fd9ff9e4a7150d13cb3252d843c106</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>code changed</t>
+          <t>Update demo.txt</t>
         </is>
       </c>
       <c r="G26" s="19" t="inlineStr">
         <is>
-          <t>“Vidyakar”</t>
+          <t>vidyakar-whitedev</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:22:31Z</t>
+          <t>2026-04-06T10:31:56Z</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -3124,7 +3062,7 @@
         </is>
       </c>
       <c r="Q26" s="19" t="n">
-        <v>24028208740</v>
+        <v>24028486557</v>
       </c>
       <c r="R26" s="19" t="inlineStr">
         <is>
@@ -3133,7 +3071,7 @@
       </c>
       <c r="S26" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:22:38Z</t>
+          <t>2026-04-06T10:39:17Z</t>
         </is>
       </c>
       <c r="T26" s="19" t="inlineStr">
@@ -3148,7 +3086,7 @@
       </c>
       <c r="V26" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:39:35.5521802Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="W26" s="19" t="inlineStr">
@@ -3158,17 +3096,17 @@
       </c>
       <c r="X26" s="19" t="inlineStr">
         <is>
-          <t>Install dependencies</t>
+          <t>Run GitHub Workflow Report</t>
         </is>
       </c>
       <c r="Y26" s="19" t="inlineStr">
         <is>
-          <t>Line 22</t>
+          <t>Line 39</t>
         </is>
       </c>
       <c r="Z26" s="19" t="inlineStr">
         <is>
-          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
@@ -3195,12 +3133,12 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>74dcfb5e2119b07af9671cc4c8396585d44a6fb8</t>
+          <t>2fcbd831207ea4821a39ee88d33aa21454ca19e3</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>code changed@v1</t>
         </is>
       </c>
       <c r="G27" s="19" t="inlineStr">
@@ -3210,7 +3148,7 @@
       </c>
       <c r="H27" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:21:05Z</t>
+          <t>2026-04-06T10:28:57Z</t>
         </is>
       </c>
       <c r="I27" s="19" t="inlineStr">
@@ -3230,7 +3168,7 @@
         </is>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>24028171694</v>
+        <v>24028398959</v>
       </c>
       <c r="R27" s="19" t="inlineStr">
         <is>
@@ -3239,7 +3177,7 @@
       </c>
       <c r="S27" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:21:19Z</t>
+          <t>2026-04-06T10:29:06Z</t>
         </is>
       </c>
       <c r="T27" s="19" t="inlineStr">
@@ -3254,7 +3192,7 @@
       </c>
       <c r="V27" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:29:24.4401300Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="W27" s="19" t="inlineStr">
@@ -3264,17 +3202,17 @@
       </c>
       <c r="X27" s="19" t="inlineStr">
         <is>
-          <t>Install dependencies</t>
+          <t>Run GitHub Workflow Report</t>
         </is>
       </c>
       <c r="Y27" s="19" t="inlineStr">
         <is>
-          <t>Line 21</t>
+          <t>Line 29</t>
         </is>
       </c>
       <c r="Z27" s="19" t="inlineStr">
         <is>
-          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
+          <t>Auth/permission error — verify GH_PAT scopes and that repository secrets are correctly configured.</t>
         </is>
       </c>
     </row>
@@ -3301,22 +3239,22 @@
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>5ff73a4b92ec974d47dc4998318d0eb25003ef50</t>
+          <t>37ddfe095b13b5e65a98ff2072c4bbb77cde7c1b</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>Enhance workflow with caching and Node.js versioning</t>
+          <t>code changed</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>vidyakar-whitedev</t>
+          <t>“Vidyakar”</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:08:38Z</t>
+          <t>2026-04-06T10:22:31Z</t>
         </is>
       </c>
       <c r="I28" s="19" t="inlineStr">
@@ -3336,7 +3274,7 @@
         </is>
       </c>
       <c r="Q28" s="19" t="n">
-        <v>24027807973</v>
+        <v>24028208740</v>
       </c>
       <c r="R28" s="19" t="inlineStr">
         <is>
@@ -3345,7 +3283,7 @@
       </c>
       <c r="S28" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:08:40Z</t>
+          <t>2026-04-06T10:22:38Z</t>
         </is>
       </c>
       <c r="T28" s="19" t="inlineStr">
@@ -3360,7 +3298,7 @@
       </c>
       <c r="V28" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:22:44.0853785Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
       <c r="W28" s="19" t="inlineStr">
@@ -3375,7 +3313,7 @@
       </c>
       <c r="Y28" s="19" t="inlineStr">
         <is>
-          <t>Line 08</t>
+          <t>Line 22</t>
         </is>
       </c>
       <c r="Z28" s="19" t="inlineStr">
@@ -3407,22 +3345,22 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>ad002901ed69655717989c4485c2df1f343c5b15</t>
+          <t>74dcfb5e2119b07af9671cc4c8396585d44a6fb8</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>Fix typo in demo.txt</t>
+          <t>code</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>vidyakar-whitedev</t>
+          <t>“Vidyakar”</t>
         </is>
       </c>
       <c r="H29" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:06:00Z</t>
+          <t>2026-04-06T10:21:05Z</t>
         </is>
       </c>
       <c r="I29" s="19" t="inlineStr">
@@ -3442,7 +3380,7 @@
         </is>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>24027735534</v>
+        <v>24028171694</v>
       </c>
       <c r="R29" s="19" t="inlineStr">
         <is>
@@ -3451,7 +3389,7 @@
       </c>
       <c r="S29" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:06:01Z</t>
+          <t>2026-04-06T10:21:19Z</t>
         </is>
       </c>
       <c r="T29" s="19" t="inlineStr">
@@ -3466,7 +3404,7 @@
       </c>
       <c r="V29" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:21:26.0154829Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
       <c r="W29" s="19" t="inlineStr">
@@ -3476,17 +3414,17 @@
       </c>
       <c r="X29" s="19" t="inlineStr">
         <is>
-          <t>Run GitHub Workflow Report</t>
+          <t>Install dependencies</t>
         </is>
       </c>
       <c r="Y29" s="19" t="inlineStr">
         <is>
-          <t>Line 06</t>
+          <t>Line 21</t>
         </is>
       </c>
       <c r="Z29" s="19" t="inlineStr">
         <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
@@ -3513,12 +3451,12 @@
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>06a295fe67b6991a6ba3430be5f485beedd7805f</t>
+          <t>5ff73a4b92ec974d47dc4998318d0eb25003ef50</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>Update workflow_report.yml</t>
+          <t>Enhance workflow with caching and Node.js versioning</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
@@ -3528,7 +3466,7 @@
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:05:48Z</t>
+          <t>2026-04-06T10:08:38Z</t>
         </is>
       </c>
       <c r="I30" s="19" t="inlineStr">
@@ -3548,7 +3486,7 @@
         </is>
       </c>
       <c r="Q30" s="19" t="n">
-        <v>24027729636</v>
+        <v>24027807973</v>
       </c>
       <c r="R30" s="19" t="inlineStr">
         <is>
@@ -3557,7 +3495,7 @@
       </c>
       <c r="S30" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:05:49Z</t>
+          <t>2026-04-06T10:08:40Z</t>
         </is>
       </c>
       <c r="T30" s="19" t="inlineStr">
@@ -3572,7 +3510,7 @@
       </c>
       <c r="V30" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
+          <t>Job 'report' step 'Install dependencies' failed — 2026-04-06T10:08:48.9456340Z ERROR: Could not open requirements file: [Errno 2] No such file or directory: 'requirements</t>
         </is>
       </c>
       <c r="W30" s="19" t="inlineStr">
@@ -3582,17 +3520,17 @@
       </c>
       <c r="X30" s="19" t="inlineStr">
         <is>
-          <t>Run GitHub Workflow Report</t>
+          <t>Install dependencies</t>
         </is>
       </c>
       <c r="Y30" s="19" t="inlineStr">
         <is>
-          <t>Line 06</t>
+          <t>Line 08</t>
         </is>
       </c>
       <c r="Z30" s="19" t="inlineStr">
         <is>
-          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+          <t>Dependency error — run `pip install -r requirements.txt` or `npm install` and verify package versions.</t>
         </is>
       </c>
     </row>
@@ -3619,12 +3557,12 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>372cfe624d49eb38f5e8baab2c748007dc54b018</t>
+          <t>ad002901ed69655717989c4485c2df1f343c5b15</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>Update demo.txt</t>
+          <t>Fix typo in demo.txt</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
@@ -3634,7 +3572,7 @@
       </c>
       <c r="H31" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:04:34Z</t>
+          <t>2026-04-06T10:06:00Z</t>
         </is>
       </c>
       <c r="I31" s="19" t="inlineStr">
@@ -3654,7 +3592,7 @@
         </is>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>24027694141</v>
+        <v>24027735534</v>
       </c>
       <c r="R31" s="19" t="inlineStr">
         <is>
@@ -3663,7 +3601,7 @@
       </c>
       <c r="S31" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:04:36Z</t>
+          <t>2026-04-06T10:06:01Z</t>
         </is>
       </c>
       <c r="T31" s="19" t="inlineStr">
@@ -3678,7 +3616,7 @@
       </c>
       <c r="V31" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:18.4738139Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="W31" s="19" t="inlineStr">
@@ -3688,12 +3626,12 @@
       </c>
       <c r="X31" s="19" t="inlineStr">
         <is>
-          <t>Set up job</t>
+          <t>Run GitHub Workflow Report</t>
         </is>
       </c>
       <c r="Y31" s="19" t="inlineStr">
         <is>
-          <t>Line 04</t>
+          <t>Line 06</t>
         </is>
       </c>
       <c r="Z31" s="19" t="inlineStr">
@@ -3725,7 +3663,7 @@
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>e7bf9d94f807df2e25e29ad5d30bc78e1b2fbd25</t>
+          <t>06a295fe67b6991a6ba3430be5f485beedd7805f</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
@@ -3740,7 +3678,7 @@
       </c>
       <c r="H32" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:04:22Z</t>
+          <t>2026-04-06T10:05:48Z</t>
         </is>
       </c>
       <c r="I32" s="19" t="inlineStr">
@@ -3760,7 +3698,7 @@
         </is>
       </c>
       <c r="Q32" s="19" t="n">
-        <v>24027689526</v>
+        <v>24027729636</v>
       </c>
       <c r="R32" s="19" t="inlineStr">
         <is>
@@ -3769,7 +3707,7 @@
       </c>
       <c r="S32" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:04:27Z</t>
+          <t>2026-04-06T10:05:49Z</t>
         </is>
       </c>
       <c r="T32" s="19" t="inlineStr">
@@ -3784,7 +3722,7 @@
       </c>
       <c r="V32" s="19" t="inlineStr">
         <is>
-          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+          <t>Job 'report' step 'Run GitHub Workflow Report' failed — 2026-04-06T10:06:03.7190307Z Traceback (most recent call last):</t>
         </is>
       </c>
       <c r="W32" s="19" t="inlineStr">
@@ -3794,12 +3732,12 @@
       </c>
       <c r="X32" s="19" t="inlineStr">
         <is>
-          <t>Set up job</t>
+          <t>Run GitHub Workflow Report</t>
         </is>
       </c>
       <c r="Y32" s="19" t="inlineStr">
         <is>
-          <t>Line 04</t>
+          <t>Line 06</t>
         </is>
       </c>
       <c r="Z32" s="19" t="inlineStr">
@@ -3831,12 +3769,12 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>3046e3250b6d3bc90634487150d715e566686a47</t>
+          <t>372cfe624d49eb38f5e8baab2c748007dc54b018</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>Add demo.txt for testing purposes</t>
+          <t>Update demo.txt</t>
         </is>
       </c>
       <c r="G33" s="19" t="inlineStr">
@@ -3846,7 +3784,7 @@
       </c>
       <c r="H33" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:02:10Z</t>
+          <t>2026-04-06T10:04:34Z</t>
         </is>
       </c>
       <c r="I33" s="19" t="inlineStr">
@@ -3862,11 +3800,11 @@
       <c r="O33" s="19" t="inlineStr"/>
       <c r="P33" s="19" t="inlineStr">
         <is>
-          <t>.github/workflows/workflow_report.yml</t>
+          <t>GitHub Workflow Report</t>
         </is>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>24027621196</v>
+        <v>24027694141</v>
       </c>
       <c r="R33" s="19" t="inlineStr">
         <is>
@@ -3875,7 +3813,7 @@
       </c>
       <c r="S33" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:02:12Z</t>
+          <t>2026-04-06T10:04:36Z</t>
         </is>
       </c>
       <c r="T33" s="19" t="inlineStr">
@@ -3890,14 +3828,22 @@
       </c>
       <c r="V33" s="19" t="inlineStr">
         <is>
-          <t>Failure (see logs)</t>
-        </is>
-      </c>
-      <c r="W33" s="19" t="inlineStr"/>
-      <c r="X33" s="19" t="inlineStr"/>
+          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:40.5244711Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+        </is>
+      </c>
+      <c r="W33" s="19" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="X33" s="19" t="inlineStr">
+        <is>
+          <t>Set up job</t>
+        </is>
+      </c>
       <c r="Y33" s="19" t="inlineStr">
         <is>
-          <t>See GitHub Actions logs</t>
+          <t>Line 04</t>
         </is>
       </c>
       <c r="Z33" s="19" t="inlineStr">
@@ -3929,12 +3875,12 @@
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>32de2be70035a86124e1345187c9ba078e4cf3bf</t>
+          <t>e7bf9d94f807df2e25e29ad5d30bc78e1b2fbd25</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>Add GitHub Workflow Report YAML configuration</t>
+          <t>Update workflow_report.yml</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
@@ -3944,7 +3890,7 @@
       </c>
       <c r="H34" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06T10:01:02Z</t>
+          <t>2026-04-06T10:04:22Z</t>
         </is>
       </c>
       <c r="I34" s="19" t="inlineStr">
@@ -3960,180 +3906,384 @@
       <c r="O34" s="19" t="inlineStr"/>
       <c r="P34" s="19" t="inlineStr">
         <is>
+          <t>GitHub Workflow Report</t>
+        </is>
+      </c>
+      <c r="Q34" s="19" t="n">
+        <v>24027689526</v>
+      </c>
+      <c r="R34" s="19" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S34" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:04:27Z</t>
+        </is>
+      </c>
+      <c r="T34" s="19" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U34" s="20" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="V34" s="19" t="inlineStr">
+        <is>
+          <t>Job 'report' step 'Set up job' failed — 2026-04-06T10:04:31.3428173Z ##[error]This request has been automatically failed because it uses a deprecated version of</t>
+        </is>
+      </c>
+      <c r="W34" s="19" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="X34" s="19" t="inlineStr">
+        <is>
+          <t>Set up job</t>
+        </is>
+      </c>
+      <c r="Y34" s="19" t="inlineStr">
+        <is>
+          <t>Line 04</t>
+        </is>
+      </c>
+      <c r="Z34" s="19" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>3046e3250b6d3bc90634487150d715e566686a47</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>Add demo.txt for testing purposes</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H35" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:02:10Z</t>
+        </is>
+      </c>
+      <c r="I35" s="19" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J35" s="19" t="inlineStr"/>
+      <c r="K35" s="19" t="inlineStr"/>
+      <c r="L35" s="19" t="inlineStr"/>
+      <c r="M35" s="19" t="inlineStr"/>
+      <c r="N35" s="19" t="inlineStr"/>
+      <c r="O35" s="19" t="inlineStr"/>
+      <c r="P35" s="19" t="inlineStr">
+        <is>
           <t>.github/workflows/workflow_report.yml</t>
         </is>
       </c>
-      <c r="Q34" s="19" t="n">
+      <c r="Q35" s="19" t="n">
+        <v>24027621196</v>
+      </c>
+      <c r="R35" s="19" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="S35" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:02:12Z</t>
+        </is>
+      </c>
+      <c r="T35" s="19" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="U35" s="20" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="V35" s="19" t="inlineStr">
+        <is>
+          <t>Failure (see logs)</t>
+        </is>
+      </c>
+      <c r="W35" s="19" t="inlineStr"/>
+      <c r="X35" s="19" t="inlineStr"/>
+      <c r="Y35" s="19" t="inlineStr">
+        <is>
+          <t>See GitHub Actions logs</t>
+        </is>
+      </c>
+      <c r="Z35" s="19" t="inlineStr">
+        <is>
+          <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>32de2be70035a86124e1345187c9ba078e4cf3bf</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
+        <is>
+          <t>Add GitHub Workflow Report YAML configuration</t>
+        </is>
+      </c>
+      <c r="G36" s="19" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H36" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-06T10:01:02Z</t>
+        </is>
+      </c>
+      <c r="I36" s="19" t="inlineStr">
+        <is>
+          <t>git-report-poc2</t>
+        </is>
+      </c>
+      <c r="J36" s="19" t="inlineStr"/>
+      <c r="K36" s="19" t="inlineStr"/>
+      <c r="L36" s="19" t="inlineStr"/>
+      <c r="M36" s="19" t="inlineStr"/>
+      <c r="N36" s="19" t="inlineStr"/>
+      <c r="O36" s="19" t="inlineStr"/>
+      <c r="P36" s="19" t="inlineStr">
+        <is>
+          <t>.github/workflows/workflow_report.yml</t>
+        </is>
+      </c>
+      <c r="Q36" s="19" t="n">
         <v>24027587697</v>
       </c>
-      <c r="R34" s="19" t="inlineStr">
+      <c r="R36" s="19" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="S34" s="19" t="inlineStr">
+      <c r="S36" s="19" t="inlineStr">
         <is>
           <t>2026-04-06T10:01:04Z</t>
         </is>
       </c>
-      <c r="T34" s="19" t="inlineStr">
+      <c r="T36" s="19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="U34" s="20" t="inlineStr">
+      <c r="U36" s="20" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="V34" s="19" t="inlineStr">
+      <c r="V36" s="19" t="inlineStr">
         <is>
           <t>Failure (see logs)</t>
         </is>
       </c>
-      <c r="W34" s="19" t="inlineStr"/>
-      <c r="X34" s="19" t="inlineStr"/>
-      <c r="Y34" s="19" t="inlineStr">
+      <c r="W36" s="19" t="inlineStr"/>
+      <c r="X36" s="19" t="inlineStr"/>
+      <c r="Y36" s="19" t="inlineStr">
         <is>
           <t>See GitHub Actions logs</t>
         </is>
       </c>
-      <c r="Z34" s="19" t="inlineStr">
+      <c r="Z36" s="19" t="inlineStr">
         <is>
           <t>Review the full workflow log in GitHub Actions for the specific error message.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>8eaab42012c4f02192c65cf59561b5c261b2cf90</t>
         </is>
       </c>
-      <c r="F35" s="18" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>Create github_workflow_report.py</t>
         </is>
       </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H35" s="18" t="inlineStr">
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
         <is>
           <t>2026-04-06T09:50:41Z</t>
         </is>
       </c>
-      <c r="I35" s="18" t="inlineStr">
+      <c r="I37" s="16" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J35" s="18" t="inlineStr"/>
-      <c r="K35" s="18" t="inlineStr"/>
-      <c r="L35" s="18" t="inlineStr"/>
-      <c r="M35" s="18" t="inlineStr"/>
-      <c r="N35" s="18" t="inlineStr"/>
-      <c r="O35" s="18" t="inlineStr"/>
-      <c r="P35" s="18" t="inlineStr"/>
-      <c r="Q35" s="18" t="inlineStr"/>
-      <c r="R35" s="18" t="inlineStr"/>
-      <c r="S35" s="18" t="inlineStr"/>
-      <c r="T35" s="18" t="inlineStr"/>
-      <c r="U35" s="18" t="inlineStr"/>
-      <c r="V35" s="18" t="inlineStr"/>
-      <c r="W35" s="18" t="inlineStr"/>
-      <c r="X35" s="18" t="inlineStr"/>
-      <c r="Y35" s="18" t="inlineStr"/>
-      <c r="Z35" s="18" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>git-report</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="J37" s="16" t="inlineStr"/>
+      <c r="K37" s="16" t="inlineStr"/>
+      <c r="L37" s="16" t="inlineStr"/>
+      <c r="M37" s="16" t="inlineStr"/>
+      <c r="N37" s="16" t="inlineStr"/>
+      <c r="O37" s="16" t="inlineStr"/>
+      <c r="P37" s="16" t="inlineStr"/>
+      <c r="Q37" s="16" t="inlineStr"/>
+      <c r="R37" s="16" t="inlineStr"/>
+      <c r="S37" s="16" t="inlineStr"/>
+      <c r="T37" s="16" t="inlineStr"/>
+      <c r="U37" s="16" t="inlineStr"/>
+      <c r="V37" s="16" t="inlineStr"/>
+      <c r="W37" s="16" t="inlineStr"/>
+      <c r="X37" s="16" t="inlineStr"/>
+      <c r="Y37" s="16" t="inlineStr"/>
+      <c r="Z37" s="16" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>git-report</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>a9e73f5e7cd8ea7da7f4969f80034915cc9f302c</t>
         </is>
       </c>
-      <c r="F36" s="15" t="inlineStr">
+      <c r="F38" s="15" t="inlineStr">
         <is>
           <t>Initial commit</t>
         </is>
       </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>vidyakar-whitedev</t>
-        </is>
-      </c>
-      <c r="H36" s="15" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>vidyakar-whitedev</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="inlineStr">
         <is>
           <t>2026-04-06T09:48:37Z</t>
         </is>
       </c>
-      <c r="I36" s="15" t="inlineStr">
+      <c r="I38" s="15" t="inlineStr">
         <is>
           <t>git-report-poc2</t>
         </is>
       </c>
-      <c r="J36" s="15" t="inlineStr"/>
-      <c r="K36" s="15" t="inlineStr"/>
-      <c r="L36" s="15" t="inlineStr"/>
-      <c r="M36" s="15" t="inlineStr"/>
-      <c r="N36" s="15" t="inlineStr"/>
-      <c r="O36" s="15" t="inlineStr"/>
-      <c r="P36" s="15" t="inlineStr"/>
-      <c r="Q36" s="15" t="inlineStr"/>
-      <c r="R36" s="15" t="inlineStr"/>
-      <c r="S36" s="15" t="inlineStr"/>
-      <c r="T36" s="15" t="inlineStr"/>
-      <c r="U36" s="15" t="inlineStr"/>
-      <c r="V36" s="15" t="inlineStr"/>
-      <c r="W36" s="15" t="inlineStr"/>
-      <c r="X36" s="15" t="inlineStr"/>
-      <c r="Y36" s="15" t="inlineStr"/>
-      <c r="Z36" s="15" t="inlineStr"/>
+      <c r="J38" s="15" t="inlineStr"/>
+      <c r="K38" s="15" t="inlineStr"/>
+      <c r="L38" s="15" t="inlineStr"/>
+      <c r="M38" s="15" t="inlineStr"/>
+      <c r="N38" s="15" t="inlineStr"/>
+      <c r="O38" s="15" t="inlineStr"/>
+      <c r="P38" s="15" t="inlineStr"/>
+      <c r="Q38" s="15" t="inlineStr"/>
+      <c r="R38" s="15" t="inlineStr"/>
+      <c r="S38" s="15" t="inlineStr"/>
+      <c r="T38" s="15" t="inlineStr"/>
+      <c r="U38" s="15" t="inlineStr"/>
+      <c r="V38" s="15" t="inlineStr"/>
+      <c r="W38" s="15" t="inlineStr"/>
+      <c r="X38" s="15" t="inlineStr"/>
+      <c r="Y38" s="15" t="inlineStr"/>
+      <c r="Z38" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z36"/>
+  <autoFilter ref="A1:Z38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5356,7 +5506,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-10 16:37 UTC  |  GitHub Activity &amp; Workflow Audit Report</t>
+          <t>Generated: 2026-04-11 05:18 UTC  |  GitHub Activity &amp; Workflow Audit Report</t>
         </is>
       </c>
     </row>
